--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
@@ -1310,7 +1310,7 @@
       <c r="I11" s="43" t="n"/>
       <c r="J11" s="43" t="inlineStr">
         <is>
-          <t>Cubierto por PMOInformatica_Plantilla_de_Product_Backlog.xlsx y la priorización por 100 puntos en Artefactos Fase Inicio. Al 23-09-2026 el Product Backlog tiene 20 historias (FS-HU-15 a FS-HU-20 agregadas en el Sprint 2). Al 24-09-2026 FS-HU-16 (acceso con Google) pasó a En Proceso: el ID de cliente OAuth quedó creado con la cuenta fitsearchoficial@gmail.com y la funcionalidad está implementada. El 24-09-2026 el Product Owner cambió el flujo de registro: el tipo de cuenta (rol) se elige en el asistente de perfil y no al registrarse, lo que ajustó FS-HU-02, FS-HU-16 y FS-HU-17.</t>
+          <t>Cubierto por PMOInformatica_Plantilla_de_Product_Backlog.xlsx y la priorización por 100 puntos en Artefactos Fase Inicio. Al 03-10-2026 el Product Backlog tiene 24 historias (FS-HU-15 a FS-HU-20 agregadas en el Sprint 2 y FS-HU-21 a FS-HU-24 el 03-10-2026).</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1687,7 @@
       <c r="F5" s="43" t="n"/>
       <c r="G5" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.11: Vista Física como diagrama de despliegue UML (Ilustración 10) y Vista Lógica por capas.</t>
+          <t>DAS v1.14: Vista Física como diagrama de despliegue UML (Ilustración 10) y Vista Lógica por capas.</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       <c r="F6" s="43" t="n"/>
       <c r="G6" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.11, Vista Física: tabla de nodos y diagrama de despliegue UML (Nginx, Node.js/Express, MySQL 8, Google Maps, API de Claude, Google Identity Services y servidor SMTP).</t>
+          <t>DAS v1.14, Vista Física: tabla de nodos y diagrama de despliegue UML (Nginx, Node.js/Express, MySQL 8, Google Maps, API de Claude, Google Identity Services y servidor SMTP).</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
       <c r="F7" s="43" t="n"/>
       <c r="G7" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.11, Vista Física: tabla de comunicación y rutas del diagrama de despliegue (HTTPS/REST/JSON, JWT, TCP 3306, proxy Nginx, verificación de Google y SMTP con TLS).</t>
+          <t>DAS v1.14, Vista Física: tabla de comunicación y rutas del diagrama de despliegue (HTTPS/REST/JSON, JWT, TCP 3306, proxy Nginx, verificación de Google y SMTP con TLS).</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       <c r="F8" s="43" t="n"/>
       <c r="G8" s="43" t="inlineStr">
         <is>
-          <t>Diagrama entidad-relación de las tablas del Sprint 1 (DER_FitSearch.png) incorporado al DAS como Ilustración 3; el modelo completo de diez tablas está en el diccionario de datos.</t>
+          <t>Diagrama entidad-relación de las nueve tablas implementadas al Sprint 3 (Ilustración 4 del DAS v1.14, generado desde Diagramas (Miro)/Actualización Sprint 3); el modelo completo de catorce tablas está en el diccionario de datos.</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       <c r="F9" s="43" t="n"/>
       <c r="G9" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.11, Vista Lógica &gt; Diccionario de datos: 12 tablas con tipos, PK, FK, restricciones e índices.</t>
+          <t>DAS v1.14, Vista Lógica &gt; Diccionario de datos: 14 tablas con tipos, PK, FK, restricciones e índices.</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
       <c r="F10" s="43" t="n"/>
       <c r="G10" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.11, Ilustración 1 (casos de uso CU-01 a CU-09 con «include» y «extend») y tabla de casos de uso.</t>
+          <t>DAS v1.14, Ilustración 1 (casos de uso CU-01 a CU-09 con «include» y «extend») y tabla de casos de uso (CU-01 y CU-03 actualizados el 03-10-2026).</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       <c r="F11" s="43" t="n"/>
       <c r="G11" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.11, Vista de Procesos: secuencias del registro de comida (Ilustración 5), del asistente de perfil (Ilustración 6), de la reserva con reservas simultáneas (Ilustración 7) y de la recuperación de contraseña (Ilustración 8).</t>
+          <t>DAS v1.14, Vista de Procesos: secuencias del registro de comida (Ilustración 5), del asistente de perfil (Ilustración 6), de la reserva con reservas simultáneas (Ilustración 7) y de la recuperación de contraseña (Ilustración 8). Desde la v1.14 incluye el flujo de búsqueda de profesionales, favoritos y reseñas.</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       <c r="F13" s="43" t="n"/>
       <c r="G13" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.11, Ilustración 2: diagrama de clases del dominio (12 clases alineadas con el modelo de datos) y diagrama de estados de la reserva (Ilustración 3).</t>
+          <t>DAS v1.14, Ilustración 2: diagrama de clases del dominio (14 clases alineadas con el modelo de datos, con Favorito y Resena) y diagrama de estados de la reserva (Ilustración 3).</t>
         </is>
       </c>
     </row>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
@@ -719,7 +719,7 @@
       </c>
       <c r="F6" s="29" t="n"/>
       <c r="G6" s="31">
-        <f>COUNTIF('Lista de Entregables'!B5:B17, B8) + COUNTIF('Lista de Entregables'!B5:B17, "Común")</f>
+        <f>COUNTIF('Lista de Entregables'!B5:B19, B8) + COUNTIF('Lista de Entregables'!B5:B19, "Común")</f>
         <v/>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="F7" s="29" t="n"/>
       <c r="G7" s="31">
-        <f>COUNTIFS('Lista de Entregables'!$B$5:$B$17, $B$8, 'Lista de Entregables'!$H$5:$H$17, "Completado") + COUNTIFS('Lista de Entregables'!$B$5:$B$17, "Común", 'Lista de Entregables'!$H$5:$H$17, "Completado")</f>
+        <f>COUNTIFS('Lista de Entregables'!$B$5:$B$19, $B$8, 'Lista de Entregables'!$H$5:$H$19, "Completado") + COUNTIFS('Lista de Entregables'!$B$5:$B$19, "Común", 'Lista de Entregables'!$H$5:$H$19, "Completado")</f>
         <v/>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="F8" s="29" t="n"/>
       <c r="G8" s="31">
-        <f>COUNTIFS('Lista de Entregables'!$B$5:$B$17, $B$8, 'Lista de Entregables'!$H$5:$H$17, "En Proceso") + COUNTIFS('Lista de Entregables'!$B$5:$B$17, "Común", 'Lista de Entregables'!$H$5:$H$17, "En Proceso")</f>
+        <f>COUNTIFS('Lista de Entregables'!$B$5:$B$19, $B$8, 'Lista de Entregables'!$H$5:$H$19, "En Proceso") + COUNTIFS('Lista de Entregables'!$B$5:$B$19, "Común", 'Lista de Entregables'!$H$5:$H$19, "En Proceso")</f>
         <v/>
       </c>
     </row>
@@ -928,7 +928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A4:J17"/>
+  <dimension ref="A4:J19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.1484375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="22" min="1" max="2"/>
@@ -1358,7 +1358,7 @@
       <c r="I12" s="43" t="n"/>
       <c r="J12" s="43" t="inlineStr">
         <is>
-          <t>Sprint 1: 11 tareas, 43 h estimadas y 43 h reales (Luis 15, Rodrigo 14, Nicolás 14). Documento Validando Sprint 1 completo con avances día a día, gráfico de avance y pila del producto actualizada; el Product Owner aceptó FS-HU-01 y FS-HU-02 el 24-09-2026 (columna A/R, con observaciones) y la retrospectiva quedó registrada el 24-09-2026; Luis Méndez aprobó la revisión posterior del código (PR #6) el 24-09-2026; Sprint 1 cerrado. Sprint 2: borrador con 23 tareas en 'Sprint 2/PMOInformatica_Plantilla_de_Sprint_Backlog.xlsx'; horas estimadas y responsables pendientes de la planificación del equipo.</t>
+          <t>Sprint 1: 11 tareas, 43 h estimadas y 43 h reales (Luis 15, Rodrigo 14, Nicolás 14). Documento Validando Sprint 1 completo con avances día a día, gráfico de avance y pila del producto actualizada; el Product Owner aceptó FS-HU-01 y FS-HU-02 el 24-09-2026 (columna A/R, con observaciones) y la retrospectiva quedó registrada el 24-09-2026; Luis Méndez aprobó la revisión posterior del código (PR #6) el 24-09-2026; Sprint 1 cerrado. Sprint 2: borrador con 23 tareas en 'Sprint 2/PMOInformatica_Plantilla_de_Sprint_Backlog.xlsx'; horas estimadas y responsables pendientes de la planificación del equipo. Sprint 2: el 03-10-2026 Luis Méndez aprobó la revisión de código de FS-HU-02 y FS-HU-15 a FS-HU-20 (PR #9; 2 h junto con el PR #10) y el Product Owner aceptó esas historias; falta que el equipo registre sus horas reales del sprint y el Documento Validando Sprint 2.</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       <c r="I16" s="43" t="n"/>
       <c r="J16" s="43" t="inlineStr">
         <is>
-          <t>Planilla de Casos de Prueba: 7 casos del Sprint 1 ejecutados y aprobados (CP-001 a CP-007). Registro de Defectos con 2 defectos corregidos. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint 1/Capturas del sistema.</t>
+          <t>Planilla de Casos de Prueba: 49 casos (CP-001 a CP-049), 47 aprobados y 2 sin ejecutar (CP-024 y CP-025, acceso con Google). Registro de Defectos con 14 defectos, todos corregidos. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema.</t>
         </is>
       </c>
     </row>
@@ -1594,9 +1594,105 @@
         </is>
       </c>
     </row>
+    <row r="18" ht="42" customHeight="1" s="23">
+      <c r="A18" s="40" t="inlineStr">
+        <is>
+          <t>Fase 2 (50%)</t>
+        </is>
+      </c>
+      <c r="B18" s="46" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="C18" s="42" t="inlineStr">
+        <is>
+          <t>Matriz de Control de Cambio</t>
+        </is>
+      </c>
+      <c r="D18" s="42" t="inlineStr">
+        <is>
+          <t>Registro de cada solicitud de cambio del proyecto: solicitante, tipo (solicitud del cliente o corrección), urgencia, importancia, requerimiento y caso de uso relacionados, fase, impacto y aprobación.</t>
+        </is>
+      </c>
+      <c r="E18" s="40" t="inlineStr">
+        <is>
+          <t>Formato planilla</t>
+        </is>
+      </c>
+      <c r="F18" s="43" t="inlineStr">
+        <is>
+          <t>Rodrigo Cárcamo Rojas</t>
+        </is>
+      </c>
+      <c r="G18" s="44" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="H18" s="44" t="inlineStr">
+        <is>
+          <t>En Proceso</t>
+        </is>
+      </c>
+      <c r="I18" s="43" t="n"/>
+      <c r="J18" s="43" t="inlineStr">
+        <is>
+          <t>FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx. Al 03-10-2026 registra 11 solicitudes (SC-01 a SC-11): 10 aceptadas y 1 rechazada (Google Places en FS-HU-03). Se actualiza con cada cambio de alcance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1" s="23">
+      <c r="A19" s="40" t="inlineStr">
+        <is>
+          <t>Fase 2 (50%)</t>
+        </is>
+      </c>
+      <c r="B19" s="46" t="inlineStr">
+        <is>
+          <t>Común</t>
+        </is>
+      </c>
+      <c r="C19" s="42" t="inlineStr">
+        <is>
+          <t>EDT y Análisis de Ingresos</t>
+        </is>
+      </c>
+      <c r="D19" s="42" t="inlineStr">
+        <is>
+          <t>Estructura de descomposición de tareas por fase con horas por rol, diccionario de roles y costo de las horas-hombre según el análisis de ingresos del mercado.</t>
+        </is>
+      </c>
+      <c r="E19" s="40" t="inlineStr">
+        <is>
+          <t>Formato planilla</t>
+        </is>
+      </c>
+      <c r="F19" s="43" t="inlineStr">
+        <is>
+          <t>Equipo completo</t>
+        </is>
+      </c>
+      <c r="G19" s="44" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="H19" s="44" t="inlineStr">
+        <is>
+          <t>En Proceso</t>
+        </is>
+      </c>
+      <c r="I19" s="43" t="n"/>
+      <c r="J19" s="43" t="inlineStr">
+        <is>
+          <t>FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/EDT_Analisis_Ingresos_FitSearch.xlsx. Primera versión al 03-10-2026: 48 actividades, 957 HH y costo estimado de $3.773.056. Horas reales solo del Sprint 1; el resto son estimaciones que el equipo debe revisar.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="H5:H19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"No Iniciado,En Proceso,Completado,Bloqueado"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
@@ -1358,7 +1358,7 @@
       <c r="I12" s="43" t="n"/>
       <c r="J12" s="43" t="inlineStr">
         <is>
-          <t>Sprint 1: 11 tareas, 43 h estimadas y 43 h reales (Luis 15, Rodrigo 14, Nicolás 14). Documento Validando Sprint 1 completo con avances día a día, gráfico de avance y pila del producto actualizada; el Product Owner aceptó FS-HU-01 y FS-HU-02 el 24-09-2026 (columna A/R, con observaciones) y la retrospectiva quedó registrada el 24-09-2026; Luis Méndez aprobó la revisión posterior del código (PR #6) el 24-09-2026; Sprint 1 cerrado. Sprint 2: borrador con 23 tareas en 'Sprint 2/PMOInformatica_Plantilla_de_Sprint_Backlog.xlsx'; horas estimadas y responsables pendientes de la planificación del equipo. Sprint 2: el 03-10-2026 Luis Méndez aprobó la revisión de código de FS-HU-02 y FS-HU-15 a FS-HU-20 (PR #9; 2 h junto con el PR #10) y el Product Owner aceptó esas historias; falta que el equipo registre sus horas reales del sprint y el Documento Validando Sprint 2.</t>
+          <t>Sprint 1: 11 tareas, 43 h estimadas y 43 h reales (Luis 15, Rodrigo 14, Nicolás 14). Documento Validando Sprint 1 completo con avances día a día, gráfico de avance y pila del producto actualizada; el Product Owner aceptó FS-HU-01 y FS-HU-02 el 24-09-2026 (columna A/R, con observaciones) y la retrospectiva quedó registrada el 24-09-2026; Luis Méndez aprobó la revisión posterior del código (PR #6) el 24-09-2026; Sprint 1 cerrado. Sprint 2: borrador con 23 tareas en 'Sprint 2/PMOInformatica_Plantilla_de_Sprint_Backlog.xlsx'; horas estimadas y responsables pendientes de la planificación del equipo. Sprint 2: el 03-10-2026 Luis Méndez aprobó la revisión de código de FS-HU-02 y FS-HU-15 a FS-HU-20 (PR #9; 2 h junto con el PR #10) y el Product Owner aceptó esas historias y FS-HU-03 (revisada en el PR #8); falta que el equipo registre sus horas reales del sprint y el Documento Validando Sprint 2.</t>
         </is>
       </c>
     </row>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
@@ -928,7 +928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A4:J19"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.1484375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="22" min="1" max="2"/>
@@ -942,6 +942,9 @@
     <col width="35" customWidth="1" style="22" min="10" max="10"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="23">
       <c r="A4" s="39" t="inlineStr">
         <is>
@@ -1358,7 +1361,7 @@
       <c r="I12" s="43" t="n"/>
       <c r="J12" s="43" t="inlineStr">
         <is>
-          <t>Sprint 1: 11 tareas, 43 h estimadas y 43 h reales (Luis 15, Rodrigo 14, Nicolás 14). Documento Validando Sprint 1 completo con avances día a día, gráfico de avance y pila del producto actualizada; el Product Owner aceptó FS-HU-01 y FS-HU-02 el 24-09-2026 (columna A/R, con observaciones) y la retrospectiva quedó registrada el 24-09-2026; Luis Méndez aprobó la revisión posterior del código (PR #6) el 24-09-2026; Sprint 1 cerrado. Sprint 2: borrador con 23 tareas en 'Sprint 2/PMOInformatica_Plantilla_de_Sprint_Backlog.xlsx'; horas estimadas y responsables pendientes de la planificación del equipo. Sprint 2: el 03-10-2026 Luis Méndez aprobó la revisión de código de FS-HU-02 y FS-HU-15 a FS-HU-20 (PR #9; 2 h junto con el PR #10) y el Product Owner aceptó esas historias y FS-HU-03 (revisada en el PR #8); falta que el equipo registre sus horas reales del sprint y el Documento Validando Sprint 2.</t>
+          <t>Sprint 1: 11 tareas, 43 h estimadas y 43 h reales (Luis 15, Rodrigo 14, Nicolás 14). Documento Validando Sprint 1 completo con avances día a día, gráfico de avance y pila del producto actualizada; el Product Owner aceptó FS-HU-01 y FS-HU-02 el 24-09-2026 (columna A/R, con observaciones) y la retrospectiva quedó registrada el 24-09-2026; Luis Méndez aprobó la revisión posterior del código (PR #6) el 24-09-2026; Sprint 1 cerrado. Sprint 2: cerrado el 04-10-2026 con 30 tareas, 110 h estimadas y 92 h reales (Rodrigo Cárcamo Rojas 51, Nicolás Silva 23 y Luis Méndez 18), registradas al cierre según el trabajo entregado en GitHub; Documento Sprint Backlog 2, Documento Validando Sprint 2 y burndown del Sprint 2 en 'Sprint 2/'. El Product Owner aceptó FS-HU-02 (tipo de cuenta), FS-HU-03 y FS-HU-15 a FS-HU-20 el 03-10-2026; FS-HU-04 (PR #11 en corrección) y FS-HU-13 pasan al Sprint 3. Sprint 3: borrador en 'Sprint 3/', planificación pendiente.</t>
         </is>
       </c>
     </row>
@@ -1496,13 +1499,13 @@
       </c>
       <c r="H15" s="44" t="inlineStr">
         <is>
-          <t>No Iniciado</t>
+          <t>En Proceso</t>
         </is>
       </c>
       <c r="I15" s="43" t="n"/>
       <c r="J15" s="43" t="inlineStr">
         <is>
-          <t>Plantilla lista con la identificación del Sprint 1; la completan Luis Méndez y Nicolás Silva en la reunión retrospectiva (el Product Owner no asiste).</t>
+          <t>Sprint 1: retrospectiva escrita (asíncrona) registrada el 24-09-2026 en 'Sprint 1/Plantilla_Resumen_Reunion_Retrospectiva.docx', con las respuestas de los tres integrantes. Sprint 2: pendiente de las respuestas del equipo.</t>
         </is>
       </c>
     </row>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
@@ -928,7 +928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A4:J19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.1484375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="22" min="1" max="2"/>
@@ -942,9 +942,6 @@
     <col width="35" customWidth="1" style="22" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="23">
       <c r="A4" s="39" t="inlineStr">
         <is>
@@ -1361,7 +1358,7 @@
       <c r="I12" s="43" t="n"/>
       <c r="J12" s="43" t="inlineStr">
         <is>
-          <t>Sprint 1: 11 tareas, 43 h estimadas y 43 h reales (Luis 15, Rodrigo 14, Nicolás 14). Documento Validando Sprint 1 completo con avances día a día, gráfico de avance y pila del producto actualizada; el Product Owner aceptó FS-HU-01 y FS-HU-02 el 24-09-2026 (columna A/R, con observaciones) y la retrospectiva quedó registrada el 24-09-2026; Luis Méndez aprobó la revisión posterior del código (PR #6) el 24-09-2026; Sprint 1 cerrado. Sprint 2: cerrado el 04-10-2026 con 30 tareas, 110 h estimadas y 92 h reales (Rodrigo Cárcamo Rojas 51, Nicolás Silva 23 y Luis Méndez 18), registradas al cierre según el trabajo entregado en GitHub; Documento Sprint Backlog 2, Documento Validando Sprint 2 y burndown del Sprint 2 en 'Sprint 2/'. El Product Owner aceptó FS-HU-02 (tipo de cuenta), FS-HU-03 y FS-HU-15 a FS-HU-20 el 03-10-2026; FS-HU-04 (PR #11 en corrección) y FS-HU-13 pasan al Sprint 3. Sprint 3: borrador en 'Sprint 3/', planificación pendiente.</t>
+          <t>Sprint 1: 11 tareas, 43 h estimadas y 43 h reales (Luis 15, Rodrigo 14, Nicolás 14). Documento Validando Sprint 1 completo con avances día a día, gráfico de avance y pila del producto actualizada; el Product Owner aceptó FS-HU-01 y FS-HU-02 el 24-09-2026 (columna A/R, con observaciones) y la retrospectiva quedó registrada el 24-09-2026; Luis Méndez aprobó la revisión posterior del código (PR #6) el 24-09-2026; Sprint 1 cerrado. Sprint 2: cerrado el 04-10-2026 con 30 tareas, 110 h estimadas y 92 h reales (Rodrigo Cárcamo Rojas 51, Nicolás Silva 23 y Luis Méndez 18), registradas al cierre según el trabajo entregado en GitHub; Documento Sprint Backlog 2, Documento Validando Sprint 2 y burndown del Sprint 2 en 'Sprint 2/'. El Product Owner aceptó FS-HU-02 (tipo de cuenta), FS-HU-03 y FS-HU-15 a FS-HU-20 el 03-10-2026; FS-HU-04 (PR #11 en corrección) y FS-HU-13 pasan al Sprint 3. Sprint 3 (desde el 05-10-2026): el Sprint Backlog 3 registra las tareas implementadas de FS-HU-04, FS-HU-05, FS-HU-06, FS-HU-12, FS-HU-13, FS-HU-14 y FS-HU-21 a FS-HU-24, y la configuración del SMTP de FS-HU-15. El Product Owner aceptó FS-HU-04 el 12-10-2026; las demás siguen pendientes de aceptación. Las horas reales del Sprint 3 aún no se registran.</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1454,7 @@
       <c r="I14" s="43" t="n"/>
       <c r="J14" s="43" t="inlineStr">
         <is>
-          <t>Semana correcta: 9 (según rúbrica oficial 2_5_APT122_Sumativa_Avance_Fase2.pdf, no semana 10). Se compone de 2 piezas: (1) Guía 2.4 GuiaEstudiante_Fase_2 (resumen de avance, monitoreo plan de trabajo, ajustes) y (2) el Documento de Arquitectura del Sistema (DAS, modelo 4+1) como evidencia adjunta — ya tenemos las 4 vistas hechas en Miro. | 14-09-2026: DAS v1.0 completado con las vistas 4+1 (imágenes insertadas), modelo de datos, diccionario de datos con índices, escenarios de calidad, decisiones de diseño y reutilización. Pendiente: diagrama ER gráfico, alinear el diagrama de clases con el modelo de datos y completar la Guía 2.4.</t>
+          <t>Semana correcta: 9 (según rúbrica oficial 2_5_APT122_Sumativa_Avance_Fase2.pdf, no semana 10). Se compone de 2 piezas: (1) Guía 2.4 GuiaEstudiante_Fase_2 (resumen de avance, monitoreo plan de trabajo, ajustes) y (2) el Documento de Arquitectura del Sistema (DAS, modelo 4+1) como evidencia adjunta — ya tenemos las 4 vistas hechas en Miro. | 14-09-2026: DAS v1.0 completado con las vistas 4+1 (imágenes insertadas), modelo de datos, diccionario de datos con índices, escenarios de calidad, decisiones de diseño y reutilización. Pendiente: diagrama ER gráfico, alinear el diagrama de clases con el modelo de datos y completar la Guía 2.4. | 12-10-2026: DAS v1.21 en main (15 tablas, 12 implementadas; 12 ilustraciones, decisiones hasta D30 y escenarios QS1 a QS7). La v1.22, con el diagrama UML de componentes, está en revisión (PR #22). Guía 2.4 actualizada al 12-10-2026.</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1546,7 @@
       <c r="I16" s="43" t="n"/>
       <c r="J16" s="43" t="inlineStr">
         <is>
-          <t>Planilla de Casos de Prueba: 49 casos (CP-001 a CP-049), 47 aprobados y 2 sin ejecutar (CP-024 y CP-025, acceso con Google). Registro de Defectos con 14 defectos, todos corregidos. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema.</t>
+          <t>Planilla de Casos de Prueba: 78 casos (CP-001 a CP-078), 75 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 26 defectos: 25 corregidos y 1 abierto (defecto 26, límite de reservas en el PR #22). Comprobaciones con MySQL real: npm run test:mysql:agenda, 39/39 el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema.</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1638,7 @@
       <c r="I18" s="43" t="n"/>
       <c r="J18" s="43" t="inlineStr">
         <is>
-          <t>FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx. Al 03-10-2026 registra 11 solicitudes (SC-01 a SC-11): 10 aceptadas y 1 rechazada (Google Places en FS-HU-03). Se actualiza con cada cambio de alcance.</t>
+          <t>FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx. Al 03-10-2026 registra 11 solicitudes (SC-01 a SC-11): 10 aceptadas y 1 rechazada (Google Places en FS-HU-03). Se actualiza con cada cambio de alcance. Pendiente registrar los cambios del 05 al 12-10-2026: elección del perfil y espacio del profesional, FS-HU-12 adelantada al Sprint 3 y límite de una reserva activa por usuario con cada profesional.</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1783,7 @@
       <c r="F5" s="43" t="n"/>
       <c r="G5" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.14: Vista Física como diagrama de despliegue UML (Ilustración 10) y Vista Lógica por capas.</t>
+          <t>DAS v1.21: Vista Física como diagrama de despliegue UML (Ilustración 10) y Vista Lógica por capas.</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1812,7 @@
       <c r="F6" s="43" t="n"/>
       <c r="G6" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.14, Vista Física: tabla de nodos y diagrama de despliegue UML (Nginx, Node.js/Express, MySQL 8, Google Maps, API de Claude, Google Identity Services y servidor SMTP).</t>
+          <t>DAS v1.21, Vista Física: tabla de nodos y diagrama de despliegue UML (Nginx, Node.js/Express, MySQL 8, Google Maps, API de Claude, Google Identity Services y servidor SMTP).</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1841,7 @@
       <c r="F7" s="43" t="n"/>
       <c r="G7" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.14, Vista Física: tabla de comunicación y rutas del diagrama de despliegue (HTTPS/REST/JSON, JWT, TCP 3306, proxy Nginx, verificación de Google y SMTP con TLS).</t>
+          <t>DAS v1.21, Vista Física: tabla de comunicación y rutas del diagrama de despliegue (HTTPS/REST/JSON, JWT, TCP 3306, proxy Nginx, verificación de Google y SMTP con TLS).</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1870,7 @@
       <c r="F8" s="43" t="n"/>
       <c r="G8" s="43" t="inlineStr">
         <is>
-          <t>Diagrama entidad-relación de las nueve tablas implementadas al Sprint 3 (Ilustración 4 del DAS v1.14, generado desde Diagramas (Miro)/Actualización Sprint 3); el modelo completo de catorce tablas está en el diccionario de datos.</t>
+          <t>Diagrama entidad-relación de las doce tablas implementadas al 12-10-2026 (Ilustración 4 del DAS v1.21, generado desde Diagramas (Miro)/Actualización Sprint 3); el modelo completo de quince tablas está en el diccionario de datos.</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1899,7 @@
       <c r="F9" s="43" t="n"/>
       <c r="G9" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.14, Vista Lógica &gt; Diccionario de datos: 14 tablas con tipos, PK, FK, restricciones e índices.</t>
+          <t>DAS v1.21, Vista Lógica &gt; Diccionario de datos: 15 tablas con tipos, PK, FK, restricciones e índices.</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1928,7 @@
       <c r="F10" s="43" t="n"/>
       <c r="G10" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.14, Ilustración 1 (casos de uso CU-01 a CU-09 con «include» y «extend») y tabla de casos de uso (CU-01 y CU-03 actualizados el 03-10-2026).</t>
+          <t>DAS v1.21, Ilustración 1 (casos de uso CU-01 a CU-09 con «include» y «extend», actualizada al 10-10-2026) y tabla de casos de uso.</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1957,7 @@
       <c r="F11" s="43" t="n"/>
       <c r="G11" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.14, Vista de Procesos: secuencias del registro de comida (Ilustración 5), del asistente de perfil (Ilustración 6), de la reserva con reservas simultáneas (Ilustración 7) y de la recuperación de contraseña (Ilustración 8). Desde la v1.14 incluye el flujo de búsqueda de profesionales, favoritos y reseñas.</t>
+          <t>DAS v1.21, Vista de Procesos: secuencias del registro de comida (Ilustración 5), de la elección del perfil y el asistente (Ilustración 6, en tres partes), de la reserva con reservas simultáneas (Ilustración 7) y de la recuperación de contraseña (Ilustración 8); flujos de la verificación administrativa (Ilustración 11) y de la disponibilidad y las reservas (Ilustración 12).</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1986,7 @@
       <c r="F12" s="43" t="n"/>
       <c r="G12" s="43" t="inlineStr">
         <is>
-          <t>Vista de Desarrollo muestra los módulos; falta un diagrama UML de componentes formal.</t>
+          <t>Vista de Desarrollo muestra los módulos; falta un diagrama UML de componentes formal. El diagrama UML de componentes formal (13_Componentes_UML) está en el PR #22, en revisión.</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2015,7 @@
       <c r="F13" s="43" t="n"/>
       <c r="G13" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.14, Ilustración 2: diagrama de clases del dominio (14 clases alineadas con el modelo de datos, con Favorito y Resena) y diagrama de estados de la reserva (Ilustración 3).</t>
+          <t>DAS v1.21, Ilustración 2: asociaciones del modelo de clases del dominio (los atributos están en el diccionario de datos) y diagrama de estados de la reserva (Ilustración 3).</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2256,7 @@
       <c r="F22" s="43" t="n"/>
       <c r="G22" s="43" t="inlineStr">
         <is>
-          <t>Sprint 1: pruebas unitarias y de componentes con Jest (backend) y Vitest (frontend), todas aprobadas.</t>
+          <t>Sprint 1: pruebas unitarias y de componentes con Jest (backend) y Vitest (frontend), todas aprobadas. Al 12-10-2026: 231 pruebas en el backend y 173 en el frontend, todas aprobadas.</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2285,7 @@
       <c r="F23" s="43" t="n"/>
       <c r="G23" s="43" t="inlineStr">
         <is>
-          <t>Pruebas de integración de la API con Supertest (datos simulados) y verificación de extremo a extremo con MySQL real: registro de usuario con hash bcrypt y guardado del perfil con su estimación calórica.</t>
+          <t>Pruebas de integración de la API con Supertest (datos simulados) y verificación de extremo a extremo con MySQL real: registro de usuario con hash bcrypt y guardado del perfil con su estimación calórica. Al 12-10-2026: comprobaciones de agenda y reservas contra MySQL real (npm run test:mysql:agenda, 39/39), incluidas las reservas simultáneas.</t>
         </is>
       </c>
     </row>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
@@ -1454,7 +1454,7 @@
       <c r="I14" s="43" t="n"/>
       <c r="J14" s="43" t="inlineStr">
         <is>
-          <t>Semana correcta: 9 (según rúbrica oficial 2_5_APT122_Sumativa_Avance_Fase2.pdf, no semana 10). Se compone de 2 piezas: (1) Guía 2.4 GuiaEstudiante_Fase_2 (resumen de avance, monitoreo plan de trabajo, ajustes) y (2) el Documento de Arquitectura del Sistema (DAS, modelo 4+1) como evidencia adjunta — ya tenemos las 4 vistas hechas en Miro. | 14-09-2026: DAS v1.0 completado con las vistas 4+1 (imágenes insertadas), modelo de datos, diccionario de datos con índices, escenarios de calidad, decisiones de diseño y reutilización. Pendiente: diagrama ER gráfico, alinear el diagrama de clases con el modelo de datos y completar la Guía 2.4. | 12-10-2026: DAS v1.21 en main (15 tablas, 12 implementadas; 12 ilustraciones, decisiones hasta D30 y escenarios QS1 a QS7). La v1.22, con el diagrama UML de componentes, está en revisión (PR #22). Guía 2.4 actualizada al 12-10-2026.</t>
+          <t>Semana correcta: 9 (según rúbrica oficial 2_5_APT122_Sumativa_Avance_Fase2.pdf, no semana 10). Se compone de 2 piezas: (1) Guía 2.4 GuiaEstudiante_Fase_2 (resumen de avance, monitoreo plan de trabajo, ajustes) y (2) el Documento de Arquitectura del Sistema (DAS, modelo 4+1) como evidencia adjunta — ya tenemos las 4 vistas hechas en Miro. | 14-09-2026: DAS v1.0 completado con las vistas 4+1 (imágenes insertadas), modelo de datos, diccionario de datos con índices, escenarios de calidad, decisiones de diseño y reutilización. Pendiente: diagrama ER gráfico, alinear el diagrama de clases con el modelo de datos y completar la Guía 2.4. | 12-10-2026: DAS v1.22 en main (15 tablas, 12 implementadas; 12 ilustraciones, decisiones hasta D30 y escenarios QS1 a QS7). Incluye el diagrama UML de componentes (Ilustración 13) y el límite de reservas, fusionados con el PR #22. Guía 2.4 actualizada al 12-10-2026.</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       <c r="I16" s="43" t="n"/>
       <c r="J16" s="43" t="inlineStr">
         <is>
-          <t>Planilla de Casos de Prueba: 78 casos (CP-001 a CP-078), 75 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 26 defectos: 25 corregidos y 1 abierto (defecto 26, límite de reservas en el PR #22). Comprobaciones con MySQL real: npm run test:mysql:agenda, 39/39 el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema.</t>
+          <t>Planilla de Casos de Prueba: 80 casos (CP-001 a CP-080), 77 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 26 defectos, todos corregidos. Comprobaciones con MySQL real: npm run test:mysql:agenda, 55/55 sobre main 662e79c el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema.</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       <c r="F5" s="43" t="n"/>
       <c r="G5" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.21: Vista Física como diagrama de despliegue UML (Ilustración 10) y Vista Lógica por capas.</t>
+          <t>DAS v1.22: Vista Física como diagrama de despliegue UML (Ilustración 10) y Vista Lógica por capas.</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1812,7 @@
       <c r="F6" s="43" t="n"/>
       <c r="G6" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.21, Vista Física: tabla de nodos y diagrama de despliegue UML (Nginx, Node.js/Express, MySQL 8, Google Maps, API de Claude, Google Identity Services y servidor SMTP).</t>
+          <t>DAS v1.22, Vista Física: tabla de nodos y diagrama de despliegue UML (Nginx, Node.js/Express, MySQL 8, Google Maps, API de Claude, Google Identity Services y servidor SMTP).</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       <c r="F7" s="43" t="n"/>
       <c r="G7" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.21, Vista Física: tabla de comunicación y rutas del diagrama de despliegue (HTTPS/REST/JSON, JWT, TCP 3306, proxy Nginx, verificación de Google y SMTP con TLS).</t>
+          <t>DAS v1.22, Vista Física: tabla de comunicación y rutas del diagrama de despliegue (HTTPS/REST/JSON, JWT, TCP 3306, proxy Nginx, verificación de Google y SMTP con TLS).</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       <c r="F8" s="43" t="n"/>
       <c r="G8" s="43" t="inlineStr">
         <is>
-          <t>Diagrama entidad-relación de las doce tablas implementadas al 12-10-2026 (Ilustración 4 del DAS v1.21, generado desde Diagramas (Miro)/Actualización Sprint 3); el modelo completo de quince tablas está en el diccionario de datos.</t>
+          <t>Diagrama entidad-relación de las doce tablas implementadas al 12-10-2026 (Ilustración 4 del DAS v1.22, generado desde Diagramas (Miro)/Actualización Sprint 3); el modelo completo de quince tablas está en el diccionario de datos.</t>
         </is>
       </c>
     </row>
@@ -1899,7 +1899,7 @@
       <c r="F9" s="43" t="n"/>
       <c r="G9" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.21, Vista Lógica &gt; Diccionario de datos: 15 tablas con tipos, PK, FK, restricciones e índices.</t>
+          <t>DAS v1.22, Vista Lógica &gt; Diccionario de datos: 15 tablas con tipos, PK, FK, restricciones e índices.</t>
         </is>
       </c>
     </row>
@@ -1928,7 +1928,7 @@
       <c r="F10" s="43" t="n"/>
       <c r="G10" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.21, Ilustración 1 (casos de uso CU-01 a CU-09 con «include» y «extend», actualizada al 10-10-2026) y tabla de casos de uso.</t>
+          <t>DAS v1.22, Ilustración 1 (casos de uso CU-01 a CU-09 con «include» y «extend», actualizada al 10-10-2026) y tabla de casos de uso.</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="F11" s="43" t="n"/>
       <c r="G11" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.21, Vista de Procesos: secuencias del registro de comida (Ilustración 5), de la elección del perfil y el asistente (Ilustración 6, en tres partes), de la reserva con reservas simultáneas (Ilustración 7) y de la recuperación de contraseña (Ilustración 8); flujos de la verificación administrativa (Ilustración 11) y de la disponibilidad y las reservas (Ilustración 12).</t>
+          <t>DAS v1.22, Vista de Procesos: secuencias del registro de comida (Ilustración 5), de la elección del perfil y el asistente (Ilustración 6, en tres partes), de la reserva con reservas simultáneas (Ilustración 7) y de la recuperación de contraseña (Ilustración 8); flujos de la verificación administrativa (Ilustración 11) y de la disponibilidad y las reservas (Ilustración 12).</t>
         </is>
       </c>
     </row>
@@ -1980,13 +1980,13 @@
       <c r="D12" s="43" t="n"/>
       <c r="E12" s="44" t="inlineStr">
         <is>
-          <t>En Desarrollo</t>
+          <t>Implementado</t>
         </is>
       </c>
       <c r="F12" s="43" t="n"/>
       <c r="G12" s="43" t="inlineStr">
         <is>
-          <t>Vista de Desarrollo muestra los módulos; falta un diagrama UML de componentes formal. El diagrama UML de componentes formal (13_Componentes_UML) está en el PR #22, en revisión.</t>
+          <t>DAS v1.22, Ilustración 13: diagrama UML de componentes e interfaces (13_Componentes_UML), fusionado el 12-10-2026 (PR #22); complementa la Vista de Desarrollo (Ilustración 9).</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       <c r="F13" s="43" t="n"/>
       <c r="G13" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.21, Ilustración 2: asociaciones del modelo de clases del dominio (los atributos están en el diccionario de datos) y diagrama de estados de la reserva (Ilustración 3).</t>
+          <t>DAS v1.22, Ilustración 2: asociaciones del modelo de clases del dominio (los atributos están en el diccionario de datos) y diagrama de estados de la reserva (Ilustración 3).</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       <c r="F22" s="43" t="n"/>
       <c r="G22" s="43" t="inlineStr">
         <is>
-          <t>Sprint 1: pruebas unitarias y de componentes con Jest (backend) y Vitest (frontend), todas aprobadas. Al 12-10-2026: 231 pruebas en el backend y 173 en el frontend, todas aprobadas.</t>
+          <t>Sprint 1: pruebas unitarias y de componentes con Jest (backend) y Vitest (frontend), todas aprobadas. Al 12-10-2026: 233 pruebas en el backend y 183 en el frontend, todas aprobadas.</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2285,7 @@
       <c r="F23" s="43" t="n"/>
       <c r="G23" s="43" t="inlineStr">
         <is>
-          <t>Pruebas de integración de la API con Supertest (datos simulados) y verificación de extremo a extremo con MySQL real: registro de usuario con hash bcrypt y guardado del perfil con su estimación calórica. Al 12-10-2026: comprobaciones de agenda y reservas contra MySQL real (npm run test:mysql:agenda, 39/39), incluidas las reservas simultáneas.</t>
+          <t>Pruebas de integración de la API con Supertest (datos simulados) y verificación de extremo a extremo con MySQL real: registro de usuario con hash bcrypt y guardado del perfil con su estimación calórica. Al 12-10-2026: comprobaciones de agenda y reservas contra MySQL real (npm run test:mysql:agenda, 55/55, incluido el límite de reservas), incluidas las reservas simultáneas.</t>
         </is>
       </c>
     </row>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
@@ -1358,7 +1358,7 @@
       <c r="I12" s="43" t="n"/>
       <c r="J12" s="43" t="inlineStr">
         <is>
-          <t>Sprint 1: 11 tareas, 43 h estimadas y 43 h reales (Luis 15, Rodrigo 14, Nicolás 14). Documento Validando Sprint 1 completo con avances día a día, gráfico de avance y pila del producto actualizada; el Product Owner aceptó FS-HU-01 y FS-HU-02 el 24-09-2026 (columna A/R, con observaciones) y la retrospectiva quedó registrada el 24-09-2026; Luis Méndez aprobó la revisión posterior del código (PR #6) el 24-09-2026; Sprint 1 cerrado. Sprint 2: cerrado el 04-10-2026 con 30 tareas, 110 h estimadas y 92 h reales (Rodrigo Cárcamo Rojas 51, Nicolás Silva 23 y Luis Méndez 18), registradas al cierre según el trabajo entregado en GitHub; Documento Sprint Backlog 2, Documento Validando Sprint 2 y burndown del Sprint 2 en 'Sprint 2/'. El Product Owner aceptó FS-HU-02 (tipo de cuenta), FS-HU-03 y FS-HU-15 a FS-HU-20 el 03-10-2026; FS-HU-04 (PR #11 en corrección) y FS-HU-13 pasan al Sprint 3. Sprint 3 (desde el 05-10-2026): el Sprint Backlog 3 registra las tareas implementadas de FS-HU-04, FS-HU-05, FS-HU-06, FS-HU-12, FS-HU-13, FS-HU-14 y FS-HU-21 a FS-HU-24, y la configuración del SMTP de FS-HU-15. El Product Owner aceptó FS-HU-04 el 12-10-2026; las demás siguen pendientes de aceptación. Las horas reales del Sprint 3 aún no se registran.</t>
+          <t>Sprint 1: 11 tareas, 43 h estimadas y 43 h reales (Luis 15, Rodrigo 14, Nicolás 14). Documento Validando Sprint 1 completo con avances día a día, gráfico de avance y pila del producto actualizada; el Product Owner aceptó FS-HU-01 y FS-HU-02 el 24-09-2026 (columna A/R, con observaciones) y la retrospectiva quedó registrada el 24-09-2026; Luis Méndez aprobó la revisión posterior del código (PR #6) el 24-09-2026; Sprint 1 cerrado. Sprint 2: cerrado el 04-10-2026 con 30 tareas, 110 h estimadas y 92 h reales (Rodrigo Cárcamo Rojas 51, Nicolás Silva 23 y Luis Méndez 18), registradas al cierre según el trabajo entregado en GitHub; Documento Sprint Backlog 2, Documento Validando Sprint 2 y burndown del Sprint 2 en 'Sprint 2/'. El Product Owner aceptó FS-HU-02 (tipo de cuenta), FS-HU-03 y FS-HU-15 a FS-HU-20 el 03-10-2026; FS-HU-04 (PR #11 en corrección) y FS-HU-13 pasan al Sprint 3. Sprint 3 (desde el 05-10-2026): el Sprint Backlog 3 registra las tareas implementadas de FS-HU-04, FS-HU-05, FS-HU-06, FS-HU-12, FS-HU-13, FS-HU-14 y FS-HU-21 a FS-HU-24, y la configuración del SMTP de FS-HU-15. El Product Owner aceptó FS-HU-04 el 12-10-2026; las demás siguen pendientes de aceptación. Horas del Sprint 3 registradas el 12-10-2026 según el trabajo entregado en GitHub: 32 tareas, 97 h estimadas y 95 h registradas al día 8 (Rodrigo Cárcamo Rojas 52, Luis Méndez 40 y Nicolás Silva 3); Documento Sprint Backlog 3 y burndown del Sprint 3 en 'Sprint 3/'.</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       <c r="I15" s="43" t="n"/>
       <c r="J15" s="43" t="inlineStr">
         <is>
-          <t>Sprint 1: retrospectiva escrita (asíncrona) registrada el 24-09-2026 en 'Sprint 1/Plantilla_Resumen_Reunion_Retrospectiva.docx', con las respuestas de los tres integrantes. Sprint 2: pendiente de las respuestas del equipo.</t>
+          <t>Sprint 1: retrospectiva escrita (asíncrona) registrada el 24-09-2026 en 'Sprint 1/Plantilla_Resumen_Reunion_Retrospectiva.docx', con las respuestas de los tres integrantes. Sprint 2: retrospectiva escrita (asíncrona) registrada el 12-10-2026 en 'Sprint 2/Plantilla_Resumen_Reunion_Retrospectiva.docx', con las respuestas de los tres integrantes.</t>
         </is>
       </c>
     </row>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
@@ -1358,7 +1358,7 @@
       <c r="I12" s="43" t="n"/>
       <c r="J12" s="43" t="inlineStr">
         <is>
-          <t>Sprint 1: 11 tareas, 43 h estimadas y 43 h reales (Luis 15, Rodrigo 14, Nicolás 14). Documento Validando Sprint 1 completo con avances día a día, gráfico de avance y pila del producto actualizada; el Product Owner aceptó FS-HU-01 y FS-HU-02 el 24-09-2026 (columna A/R, con observaciones) y la retrospectiva quedó registrada el 24-09-2026; Luis Méndez aprobó la revisión posterior del código (PR #6) el 24-09-2026; Sprint 1 cerrado. Sprint 2: cerrado el 04-10-2026 con 30 tareas, 110 h estimadas y 92 h reales (Rodrigo Cárcamo Rojas 51, Nicolás Silva 23 y Luis Méndez 18), registradas al cierre según el trabajo entregado en GitHub; Documento Sprint Backlog 2, Documento Validando Sprint 2 y burndown del Sprint 2 en 'Sprint 2/'. El Product Owner aceptó FS-HU-02 (tipo de cuenta), FS-HU-03 y FS-HU-15 a FS-HU-20 el 03-10-2026; FS-HU-04 (PR #11 en corrección) y FS-HU-13 pasan al Sprint 3. Sprint 3 (desde el 05-10-2026): el Sprint Backlog 3 registra las tareas implementadas de FS-HU-04, FS-HU-05, FS-HU-06, FS-HU-12, FS-HU-13, FS-HU-14 y FS-HU-21 a FS-HU-24, y la configuración del SMTP de FS-HU-15. El Product Owner aceptó FS-HU-04 el 12-10-2026; las demás siguen pendientes de aceptación. Horas del Sprint 3 registradas el 12-10-2026 según el trabajo entregado en GitHub: 32 tareas, 97 h estimadas y 95 h registradas al día 8 (Rodrigo Cárcamo Rojas 52, Luis Méndez 40 y Nicolás Silva 3); Documento Sprint Backlog 3 y burndown del Sprint 3 en 'Sprint 3/'.</t>
+          <t>Sprint 1: 11 tareas, 43 h estimadas y 43 h reales (Luis 15, Rodrigo 14, Nicolás 14). Documento Validando Sprint 1 completo con avances día a día, gráfico de avance y pila del producto actualizada; el Product Owner aceptó FS-HU-01 y FS-HU-02 el 24-09-2026 (columna A/R, con observaciones) y la retrospectiva quedó registrada el 24-09-2026; Luis Méndez aprobó la revisión posterior del código (PR #6) el 24-09-2026; Sprint 1 cerrado. Sprint 2: cerrado el 04-10-2026 con 30 tareas, 110 h estimadas y 92 h reales (Rodrigo Cárcamo Rojas 51, Nicolás Silva 23 y Luis Méndez 18), registradas al cierre según el trabajo entregado en GitHub; Documento Sprint Backlog 2, Documento Validando Sprint 2 y burndown del Sprint 2 en 'Sprint 2/'. El Product Owner aceptó FS-HU-02 (tipo de cuenta), FS-HU-03 y FS-HU-15 a FS-HU-20 el 03-10-2026; FS-HU-04 (PR #11 en corrección) y FS-HU-13 pasan al Sprint 3. Sprint 3 (desde el 05-10-2026): el Sprint Backlog 3 registra las tareas implementadas de FS-HU-04, FS-HU-05, FS-HU-06, FS-HU-12, FS-HU-13, FS-HU-14 y FS-HU-21 a FS-HU-24, y la configuración del SMTP de FS-HU-15. El Product Owner aceptó el 12-10-2026 FS-HU-04, FS-HU-05, FS-HU-12, FS-HU-13, FS-HU-14 y FS-HU-21 a FS-HU-24 (FS-HU-12 y FS-HU-14 con observaciones); FS-HU-06 queda pendiente de CP-078. Horas del Sprint 3 registradas el 12-10-2026 según el trabajo entregado en GitHub, con un máximo de 5 h por persona y día: 33 tareas, 65 h estimadas y 63 h registradas al día 8 (Rodrigo Cárcamo Rojas 37, Luis Méndez 23 y Nicolás Silva 3); Documento Sprint Backlog 3 y burndown del Sprint 3 en 'Sprint 3/'.</t>
         </is>
       </c>
     </row>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
@@ -1262,7 +1262,8 @@
       <c r="I10" s="43" t="n"/>
       <c r="J10" s="43" t="inlineStr">
         <is>
-          <t>Cubierto por documento_de_visión_y_roles_scrum.docx y el Product Vision Board en FitSearch_Artefactos_Fase_Inicio.</t>
+          <t>Cubierto por documento_de_visión_y_roles_scrum.docx y el Product Vision Board en FitSearch_Artefactos_Fase_Inicio.
+12-10-2026: versión 1.1 de la visión, que incorpora la reserva básica de horas (E7) y la verificación de perfiles profesionales (FS-HU-12).</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1311,8 @@
       <c r="I11" s="43" t="n"/>
       <c r="J11" s="43" t="inlineStr">
         <is>
-          <t>Cubierto por PMOInformatica_Plantilla_de_Product_Backlog.xlsx y la priorización por 100 puntos en Artefactos Fase Inicio. Al 03-10-2026 el Product Backlog tiene 24 historias (FS-HU-15 a FS-HU-20 agregadas en el Sprint 2 y FS-HU-21 a FS-HU-24 el 03-10-2026).</t>
+          <t>Cubierto por PMOInformatica_Plantilla_de_Product_Backlog.xlsx y la priorización por 100 puntos en Artefactos Fase Inicio. Al 03-10-2026 el Product Backlog tiene 24 historias (FS-HU-15 a FS-HU-20 agregadas en el Sprint 2 y FS-HU-21 a FS-HU-24 el 03-10-2026).
+12-10-2026: el Documento Product Backlog (carpeta Sprint 1) pasa a la versión 1.1 con las 24 historias (117 puntos) y el Documento de Épicas e Historias de Usuario a la versión 1.6, con la imagen de cada una de las 24 historias.</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1640,7 @@
       <c r="I18" s="43" t="n"/>
       <c r="J18" s="43" t="inlineStr">
         <is>
-          <t>FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx. Al 03-10-2026 registra 11 solicitudes (SC-01 a SC-11): 10 aceptadas y 1 rechazada (Google Places en FS-HU-03). Se actualiza con cada cambio de alcance. Pendiente registrar los cambios del 05 al 12-10-2026: elección del perfil y espacio del profesional, FS-HU-12 adelantada al Sprint 3 y límite de una reserva activa por usuario con cada profesional.</t>
+          <t>FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx. Al 12-10-2026 registra 17 solicitudes (SC-01 a SC-17): 16 aceptadas y 1 rechazada (Google Places en FS-HU-03). Las SC-12 a SC-17 cubren el flujo y el espacio del profesional, el clima en su Inicio, el menú del usuario, la elección del perfil en una pantalla propia, el panel del administrador con FS-HU-12 en el Sprint 3 y el límite de una reserva activa por usuario con cada profesional. Se actualiza con cada cambio de alcance.</t>
         </is>
       </c>
     </row>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
@@ -1456,7 +1456,8 @@
       <c r="I14" s="43" t="n"/>
       <c r="J14" s="43" t="inlineStr">
         <is>
-          <t>Semana correcta: 9 (según rúbrica oficial 2_5_APT122_Sumativa_Avance_Fase2.pdf, no semana 10). Se compone de 2 piezas: (1) Guía 2.4 GuiaEstudiante_Fase_2 (resumen de avance, monitoreo plan de trabajo, ajustes) y (2) el Documento de Arquitectura del Sistema (DAS, modelo 4+1) como evidencia adjunta — ya tenemos las 4 vistas hechas en Miro. | 14-09-2026: DAS v1.0 completado con las vistas 4+1 (imágenes insertadas), modelo de datos, diccionario de datos con índices, escenarios de calidad, decisiones de diseño y reutilización. Pendiente: diagrama ER gráfico, alinear el diagrama de clases con el modelo de datos y completar la Guía 2.4. | 12-10-2026: DAS v1.22 en main (15 tablas, 12 implementadas; 12 ilustraciones, decisiones hasta D30 y escenarios QS1 a QS7). Incluye el diagrama UML de componentes (Ilustración 13) y el límite de reservas, fusionados con el PR #22. Guía 2.4 actualizada al 12-10-2026.</t>
+          <t>Semana correcta: 9 (según rúbrica oficial 2_5_APT122_Sumativa_Avance_Fase2.pdf, no semana 10). Se compone de 2 piezas: (1) Guía 2.4 GuiaEstudiante_Fase_2 (resumen de avance, monitoreo plan de trabajo, ajustes) y (2) el Documento de Arquitectura del Sistema (DAS, modelo 4+1) como evidencia adjunta — ya tenemos las 4 vistas hechas en Miro. | 14-09-2026: DAS v1.0 completado con las vistas 4+1 (imágenes insertadas), modelo de datos, diccionario de datos con índices, escenarios de calidad, decisiones de diseño y reutilización. Pendiente: diagrama ER gráfico, alinear el diagrama de clases con el modelo de datos y completar la Guía 2.4. | 12-10-2026: DAS v1.22 en main (15 tablas, 12 implementadas; 12 ilustraciones, decisiones hasta D30 y escenarios QS1 a QS7). Incluye el diagrama UML de componentes (Ilustración 13) y el límite de reservas, fusionados con el PR #22. Guía 2.4 actualizada al 12-10-2026.
+15-10-2026: DAS 1.23 con la SC-18 (decisión D31, que reemplaza a D8, e Ilustraciones 1, 9, 10 y 13 regeneradas) y Guía 2.4 actualizada con los PR #25 y #27.</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1549,7 @@
       <c r="I16" s="43" t="n"/>
       <c r="J16" s="43" t="inlineStr">
         <is>
-          <t>Planilla de Casos de Prueba: 80 casos (CP-001 a CP-080), 77 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 26 defectos, todos corregidos. Comprobaciones con MySQL real: npm run test:mysql:agenda, 55/55 sobre main 662e79c el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema.</t>
+          <t>Planilla de Casos de Prueba: 80 casos (CP-001 a CP-080), 77 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 29 defectos: 26 corregidos y 3 abiertos (27 a 29, del mapa nuevo del PR #27). El 15-10-2026 se repitieron CP-076 y CP-077 con MapLibre (189/189 en el frontend); CP-078 sigue pendiente con el mapa nuevo. Comprobaciones con MySQL real: npm run test:mysql:agenda, 55/55 sobre main 662e79c el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema.</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1641,7 @@
       <c r="I18" s="43" t="n"/>
       <c r="J18" s="43" t="inlineStr">
         <is>
-          <t>FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx. Al 12-10-2026 registra 17 solicitudes (SC-01 a SC-17): 16 aceptadas y 1 rechazada (Google Places en FS-HU-03). Las SC-12 a SC-17 cubren el flujo y el espacio del profesional, el clima en su Inicio, el menú del usuario, la elección del perfil en una pantalla propia, el panel del administrador con FS-HU-12 en el Sprint 3 y el límite de una reserva activa por usuario con cada profesional. Se actualiza con cada cambio de alcance.</t>
+          <t>FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx. Al 15-10-2026 registra 18 solicitudes (SC-01 a SC-18): 17 aceptadas y 1 rechazada (Google Places en FS-HU-03). Las SC-12 a SC-17 cubren el flujo y el espacio del profesional, el clima en su Inicio, el menú del usuario, la elección del perfil en una pantalla propia, el panel del administrador con FS-HU-12 en el Sprint 3 el límite de una reserva activa por usuario con cada profesional y el cambio del mapa a MapLibre GL JS con OpenFreeMap (SC-18, PR #27). Se actualiza con cada cambio de alcance.</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1786,7 @@
       <c r="F5" s="43" t="n"/>
       <c r="G5" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.22: Vista Física como diagrama de despliegue UML (Ilustración 10) y Vista Lógica por capas.</t>
+          <t>DAS v1.23: Vista Física como diagrama de despliegue UML (Ilustración 10) y Vista Lógica por capas.</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1815,7 @@
       <c r="F6" s="43" t="n"/>
       <c r="G6" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.22, Vista Física: tabla de nodos y diagrama de despliegue UML (Nginx, Node.js/Express, MySQL 8, Google Maps, API de Claude, Google Identity Services y servidor SMTP).</t>
+          <t>DAS v1.23, Vista Física: tabla de nodos y diagrama de despliegue UML (Nginx, Node.js/Express, MySQL 8, MapLibre GL JS con OpenFreeMap, API de Claude, Google Identity Services y servidor SMTP).</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1844,7 @@
       <c r="F7" s="43" t="n"/>
       <c r="G7" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.22, Vista Física: tabla de comunicación y rutas del diagrama de despliegue (HTTPS/REST/JSON, JWT, TCP 3306, proxy Nginx, verificación de Google y SMTP con TLS).</t>
+          <t>DAS v1.23, Vista Física: tabla de comunicación y rutas del diagrama de despliegue (HTTPS/REST/JSON, JWT, TCP 3306, proxy Nginx, verificación de Google y SMTP con TLS).</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1873,7 @@
       <c r="F8" s="43" t="n"/>
       <c r="G8" s="43" t="inlineStr">
         <is>
-          <t>Diagrama entidad-relación de las doce tablas implementadas al 12-10-2026 (Ilustración 4 del DAS v1.22, generado desde Diagramas (Miro)/Actualización Sprint 3); el modelo completo de quince tablas está en el diccionario de datos.</t>
+          <t>Diagrama entidad-relación de las doce tablas implementadas al 12-10-2026 (Ilustración 4 del DAS v1.23, generado desde Diagramas (Miro)/Actualización Sprint 3); el modelo completo de quince tablas está en el diccionario de datos.</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1902,7 @@
       <c r="F9" s="43" t="n"/>
       <c r="G9" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.22, Vista Lógica &gt; Diccionario de datos: 15 tablas con tipos, PK, FK, restricciones e índices.</t>
+          <t>DAS v1.23, Vista Lógica &gt; Diccionario de datos: 15 tablas con tipos, PK, FK, restricciones e índices.</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1931,7 @@
       <c r="F10" s="43" t="n"/>
       <c r="G10" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.22, Ilustración 1 (casos de uso CU-01 a CU-09 con «include» y «extend», actualizada al 10-10-2026) y tabla de casos de uso.</t>
+          <t>DAS v1.23, Ilustración 1 (casos de uso CU-01 a CU-09 con «include» y «extend», actualizada al 15-10-2026) y tabla de casos de uso.</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1960,7 @@
       <c r="F11" s="43" t="n"/>
       <c r="G11" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.22, Vista de Procesos: secuencias del registro de comida (Ilustración 5), de la elección del perfil y el asistente (Ilustración 6, en tres partes), de la reserva con reservas simultáneas (Ilustración 7) y de la recuperación de contraseña (Ilustración 8); flujos de la verificación administrativa (Ilustración 11) y de la disponibilidad y las reservas (Ilustración 12).</t>
+          <t>DAS v1.23, Vista de Procesos: secuencias del registro de comida (Ilustración 5), de la elección del perfil y el asistente (Ilustración 6, en tres partes), de la reserva con reservas simultáneas (Ilustración 7) y de la recuperación de contraseña (Ilustración 8); flujos de la verificación administrativa (Ilustración 11) y de la disponibilidad y las reservas (Ilustración 12).</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1989,7 @@
       <c r="F12" s="43" t="n"/>
       <c r="G12" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.22, Ilustración 13: diagrama UML de componentes e interfaces (13_Componentes_UML), fusionado el 12-10-2026 (PR #22); complementa la Vista de Desarrollo (Ilustración 9).</t>
+          <t>DAS v1.23, Ilustración 13: diagrama UML de componentes e interfaces (13_Componentes_UML), fusionado el 12-10-2026 (PR #22); complementa la Vista de Desarrollo (Ilustración 9).</t>
         </is>
       </c>
     </row>
@@ -2017,7 +2018,7 @@
       <c r="F13" s="43" t="n"/>
       <c r="G13" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.22, Ilustración 2: asociaciones del modelo de clases del dominio (los atributos están en el diccionario de datos) y diagrama de estados de la reserva (Ilustración 3).</t>
+          <t>DAS v1.23, Ilustración 2: asociaciones del modelo de clases del dominio (los atributos están en el diccionario de datos) y diagrama de estados de la reserva (Ilustración 3).</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2259,7 @@
       <c r="F22" s="43" t="n"/>
       <c r="G22" s="43" t="inlineStr">
         <is>
-          <t>Sprint 1: pruebas unitarias y de componentes con Jest (backend) y Vitest (frontend), todas aprobadas. Al 12-10-2026: 233 pruebas en el backend y 183 en el frontend, todas aprobadas.</t>
+          <t>Sprint 1: pruebas unitarias y de componentes con Jest (backend) y Vitest (frontend), todas aprobadas. Al 15-10-2026: 233 pruebas en el backend y 189 en el frontend, todas aprobadas.</t>
         </is>
       </c>
     </row>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
@@ -1549,7 +1549,7 @@
       <c r="I16" s="43" t="n"/>
       <c r="J16" s="43" t="inlineStr">
         <is>
-          <t>Planilla de Casos de Prueba: 80 casos (CP-001 a CP-080), 77 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 29 defectos: 26 corregidos y 3 abiertos (27 a 29, del mapa nuevo del PR #27). El 15-10-2026 se repitieron CP-076 y CP-077 con MapLibre (189/189 en el frontend); CP-078 sigue pendiente con el mapa nuevo. Comprobaciones con MySQL real: npm run test:mysql:agenda, 55/55 sobre main 662e79c el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema.</t>
+          <t>Planilla de Casos de Prueba: 80 casos (CP-001 a CP-080), 77 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 29 defectos: 26 corregidos y 3 abiertos (27 a 29, del mapa nuevo del PR #27). El 15-10-2026 se repitieron CP-076 y CP-077 con MapLibre (189/189 en el frontend); CP-078 sigue pendiente con el mapa nuevo. Comprobaciones con MySQL real: npm run test:mysql:agenda, 55/55 sobre main 662e79c el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema. 19-10-2026: CP-081 a CP-087 (mejoras de interfaz, SC-19), todos aprobados → 87 casos, 84 aprobados y 3 sin ejecutar (CP-024, CP-025 y CP-078); defectos 30 a 34 corregidos → 34 defectos: 31 corregidos y 3 abiertos (27 a 29). Evidencias en Plan de Pruebas/Mejoras_Interfaz_2026-10-19*.</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       <c r="I18" s="43" t="n"/>
       <c r="J18" s="43" t="inlineStr">
         <is>
-          <t>FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx. Al 15-10-2026 registra 18 solicitudes (SC-01 a SC-18): 17 aceptadas y 1 rechazada (Google Places en FS-HU-03). Las SC-12 a SC-17 cubren el flujo y el espacio del profesional, el clima en su Inicio, el menú del usuario, la elección del perfil en una pantalla propia, el panel del administrador con FS-HU-12 en el Sprint 3 el límite de una reserva activa por usuario con cada profesional y el cambio del mapa a MapLibre GL JS con OpenFreeMap (SC-18, PR #27). Se actualiza con cada cambio de alcance.</t>
+          <t>FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx. Al 15-10-2026 registra 18 solicitudes (SC-01 a SC-18): 17 aceptadas y 1 rechazada (Google Places en FS-HU-03). Las SC-12 a SC-17 cubren el flujo y el espacio del profesional, el clima en su Inicio, el menú del usuario, la elección del perfil en una pantalla propia, el panel del administrador con FS-HU-12 en el Sprint 3 el límite de una reserva activa por usuario con cada profesional y el cambio del mapa a MapLibre GL JS con OpenFreeMap (SC-18, PR #27). El 19-10-2026 se agregó la SC-19 (mejoras de respuesta y movimiento de la interfaz, con los defectos 30 a 34): 19 solicitudes, 18 aceptadas y 1 rechazada. Se actualiza con cada cambio de alcance.</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
       <c r="F22" s="43" t="n"/>
       <c r="G22" s="43" t="inlineStr">
         <is>
-          <t>Sprint 1: pruebas unitarias y de componentes con Jest (backend) y Vitest (frontend), todas aprobadas. Al 15-10-2026: 233 pruebas en el backend y 189 en el frontend, todas aprobadas.</t>
+          <t>Sprint 1: pruebas unitarias y de componentes con Jest (backend) y Vitest (frontend), todas aprobadas. Al 15-10-2026: 233 pruebas en el backend y 189 en el frontend, todas aprobadas. Al 19-10-2026: 233 en el backend y 195 en el frontend (mejoras de interfaz, SC-19), todas aprobadas.</t>
         </is>
       </c>
     </row>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
@@ -1549,7 +1549,7 @@
       <c r="I16" s="43" t="n"/>
       <c r="J16" s="43" t="inlineStr">
         <is>
-          <t>Planilla de Casos de Prueba: 80 casos (CP-001 a CP-080), 77 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 29 defectos: 26 corregidos y 3 abiertos (27 a 29, del mapa nuevo del PR #27). El 15-10-2026 se repitieron CP-076 y CP-077 con MapLibre (189/189 en el frontend); CP-078 sigue pendiente con el mapa nuevo. Comprobaciones con MySQL real: npm run test:mysql:agenda, 55/55 sobre main 662e79c el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema. 19-10-2026: CP-081 a CP-087 (mejoras de interfaz, SC-19), todos aprobados → 87 casos, 84 aprobados y 3 sin ejecutar (CP-024, CP-025 y CP-078); defectos 30 a 34 corregidos → 34 defectos: 31 corregidos y 3 abiertos (27 a 29). Evidencias en Plan de Pruebas/Mejoras_Interfaz_2026-10-19*.</t>
+          <t>Planilla de Casos de Prueba: 80 casos (CP-001 a CP-080), 77 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 29 defectos: 26 corregidos y 3 abiertos (27 a 29, del mapa nuevo del PR #27). El 15-10-2026 se repitieron CP-076 y CP-077 con MapLibre (189/189 en el frontend); CP-078 sigue pendiente con el mapa nuevo. Comprobaciones con MySQL real: npm run test:mysql:agenda, 55/55 sobre main 662e79c el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema. 19-10-2026: CP-081 a CP-087 (mejoras de interfaz, SC-19), todos aprobados → 87 casos, 84 aprobados y 3 sin ejecutar (CP-024, CP-025 y CP-078); defectos 30 a 34 corregidos → 34 defectos: 31 corregidos y 3 abiertos (27 a 29). Evidencias en Plan de Pruebas/Mejoras_Interfaz_2026-10-19*. 19-10-2026 (SC-20, reserva con calendario): CP-088 a CP-091 aprobados → 91 casos, 88 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Flujo_Reservas_2026-10-19*. SC-21 (calendario al publicar horarios): CP-092 y CP-093 aprobados → 93 casos, 90 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Publicar_Horario_2026-10-19*.</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       <c r="I18" s="43" t="n"/>
       <c r="J18" s="43" t="inlineStr">
         <is>
-          <t>FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx. Al 15-10-2026 registra 18 solicitudes (SC-01 a SC-18): 17 aceptadas y 1 rechazada (Google Places en FS-HU-03). Las SC-12 a SC-17 cubren el flujo y el espacio del profesional, el clima en su Inicio, el menú del usuario, la elección del perfil en una pantalla propia, el panel del administrador con FS-HU-12 en el Sprint 3 el límite de una reserva activa por usuario con cada profesional y el cambio del mapa a MapLibre GL JS con OpenFreeMap (SC-18, PR #27). El 19-10-2026 se agregó la SC-19 (mejoras de respuesta y movimiento de la interfaz, con los defectos 30 a 34): 19 solicitudes, 18 aceptadas y 1 rechazada. Se actualiza con cada cambio de alcance.</t>
+          <t>FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx. Al 15-10-2026 registra 18 solicitudes (SC-01 a SC-18): 17 aceptadas y 1 rechazada (Google Places en FS-HU-03). Las SC-12 a SC-17 cubren el flujo y el espacio del profesional, el clima en su Inicio, el menú del usuario, la elección del perfil en una pantalla propia, el panel del administrador con FS-HU-12 en el Sprint 3 el límite de una reserva activa por usuario con cada profesional y el cambio del mapa a MapLibre GL JS con OpenFreeMap (SC-18, PR #27). El 19-10-2026 se agregó la SC-19 (mejoras de respuesta y movimiento de la interfaz, con los defectos 30 a 34): 19 solicitudes, 18 aceptadas y 1 rechazada. Ese mismo día se agregó la SC-20 (reserva con calendario en FS-HU-14): 20 solicitudes, 19 aceptadas y 1 rechazada. Luego, la SC-21 (calendario al publicar horarios en FS-HU-13): 21 solicitudes, 20 aceptadas y 1 rechazada. Se actualiza con cada cambio de alcance.</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
       <c r="F22" s="43" t="n"/>
       <c r="G22" s="43" t="inlineStr">
         <is>
-          <t>Sprint 1: pruebas unitarias y de componentes con Jest (backend) y Vitest (frontend), todas aprobadas. Al 15-10-2026: 233 pruebas en el backend y 189 en el frontend, todas aprobadas. Al 19-10-2026: 233 en el backend y 195 en el frontend (mejoras de interfaz, SC-19), todas aprobadas.</t>
+          <t>Sprint 1: pruebas unitarias y de componentes con Jest (backend) y Vitest (frontend), todas aprobadas. Al 15-10-2026: 233 pruebas en el backend y 189 en el frontend, todas aprobadas. Al 19-10-2026: 233 en el backend y 208 en el frontend (mejoras de interfaz, SC-19; reserva con calendario, SC-20, y calendario al publicar horarios, SC-21), todas aprobadas.</t>
         </is>
       </c>
     </row>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
@@ -1549,7 +1549,7 @@
       <c r="I16" s="43" t="n"/>
       <c r="J16" s="43" t="inlineStr">
         <is>
-          <t>Planilla de Casos de Prueba: 80 casos (CP-001 a CP-080), 77 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 29 defectos: 26 corregidos y 3 abiertos (27 a 29, del mapa nuevo del PR #27). El 15-10-2026 se repitieron CP-076 y CP-077 con MapLibre (189/189 en el frontend); CP-078 sigue pendiente con el mapa nuevo. Comprobaciones con MySQL real: npm run test:mysql:agenda, 55/55 sobre main 662e79c el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema. 19-10-2026: CP-081 a CP-087 (mejoras de interfaz, SC-19), todos aprobados → 87 casos, 84 aprobados y 3 sin ejecutar (CP-024, CP-025 y CP-078); defectos 30 a 34 corregidos → 34 defectos: 31 corregidos y 3 abiertos (27 a 29). Evidencias en Plan de Pruebas/Mejoras_Interfaz_2026-10-19*. 19-10-2026 (SC-20, reserva con calendario): CP-088 a CP-091 aprobados → 91 casos, 88 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Flujo_Reservas_2026-10-19*. SC-21 (calendario al publicar horarios): CP-092 y CP-093 aprobados → 93 casos, 90 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Publicar_Horario_2026-10-19*.</t>
+          <t>Planilla de Casos de Prueba: 80 casos (CP-001 a CP-080), 77 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 29 defectos: 26 corregidos y 3 abiertos (27 a 29, del mapa nuevo del PR #27). El 15-10-2026 se repitieron CP-076 y CP-077 con MapLibre (189/189 en el frontend); CP-078 sigue pendiente con el mapa nuevo. Comprobaciones con MySQL real: npm run test:mysql:agenda, 55/55 sobre main 662e79c el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema. 19-10-2026: CP-081 a CP-087 (mejoras de interfaz, SC-19), todos aprobados → 87 casos, 84 aprobados y 3 sin ejecutar (CP-024, CP-025 y CP-078); defectos 30 a 34 corregidos → 34 defectos: 31 corregidos y 3 abiertos (27 a 29). Evidencias en Plan de Pruebas/Mejoras_Interfaz_2026-10-19*. 19-10-2026 (SC-20, reserva con calendario): CP-088 a CP-091 aprobados → 91 casos, 88 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Flujo_Reservas_2026-10-19*. SC-21 (calendario al publicar horarios): CP-092 y CP-093 aprobados → 93 casos, 90 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Publicar_Horario_2026-10-19*. Defecto 35 (mapa que se veía de lejos por una ubicación fuera de Chile) corregido con CP-094 → 94 casos, 91 aprobados y 3 sin ejecutar; 35 defectos: 32 corregidos y 3 abiertos. Evidencias en Plan de Pruebas/Mapa_Chile_2026-10-19*. SC-22 (detalle del profesional en el mapa): CP-095 y CP-096 aprobados y defecto 28 corregido → 96 casos, 93 aprobados y 3 sin ejecutar; 35 defectos: 33 corregidos y 2 abiertos (27 y 29). Evidencias en Plan de Pruebas/Detalle_Mapa_2026-10-19*. SC-23 (buscador general del Inicio): CP-097 y CP-098 aprobados → 98 casos, 95 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Buscador_Inicio_2026-10-19*. SC-24 (dirección de atención y coordenadas en Chile en la ficha profesional): CP-099 y CP-100 aprobados → 100 casos, 97 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Direccion_Ficha_2026-10-19*.</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       <c r="I18" s="43" t="n"/>
       <c r="J18" s="43" t="inlineStr">
         <is>
-          <t>FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx. Al 15-10-2026 registra 18 solicitudes (SC-01 a SC-18): 17 aceptadas y 1 rechazada (Google Places en FS-HU-03). Las SC-12 a SC-17 cubren el flujo y el espacio del profesional, el clima en su Inicio, el menú del usuario, la elección del perfil en una pantalla propia, el panel del administrador con FS-HU-12 en el Sprint 3 el límite de una reserva activa por usuario con cada profesional y el cambio del mapa a MapLibre GL JS con OpenFreeMap (SC-18, PR #27). El 19-10-2026 se agregó la SC-19 (mejoras de respuesta y movimiento de la interfaz, con los defectos 30 a 34): 19 solicitudes, 18 aceptadas y 1 rechazada. Ese mismo día se agregó la SC-20 (reserva con calendario en FS-HU-14): 20 solicitudes, 19 aceptadas y 1 rechazada. Luego, la SC-21 (calendario al publicar horarios en FS-HU-13): 21 solicitudes, 20 aceptadas y 1 rechazada. Se actualiza con cada cambio de alcance.</t>
+          <t>FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx. Al 15-10-2026 registra 18 solicitudes (SC-01 a SC-18): 17 aceptadas y 1 rechazada (Google Places en FS-HU-03). Las SC-12 a SC-17 cubren el flujo y el espacio del profesional, el clima en su Inicio, el menú del usuario, la elección del perfil en una pantalla propia, el panel del administrador con FS-HU-12 en el Sprint 3 el límite de una reserva activa por usuario con cada profesional y el cambio del mapa a MapLibre GL JS con OpenFreeMap (SC-18, PR #27). El 19-10-2026 se agregó la SC-19 (mejoras de respuesta y movimiento de la interfaz, con los defectos 30 a 34): 19 solicitudes, 18 aceptadas y 1 rechazada. Ese mismo día se agregó la SC-20 (reserva con calendario en FS-HU-14): 20 solicitudes, 19 aceptadas y 1 rechazada. Luego, la SC-21 (calendario al publicar horarios en FS-HU-13): 21 solicitudes, 20 aceptadas y 1 rechazada. Luego, la SC-22 (detalle del profesional en la ventana del mapa, FS-HU-06): 22 solicitudes, 21 aceptadas y 1 rechazada. Luego, la SC-23 (buscador general del Inicio, FS-HU-21): 23 solicitudes, 22 aceptadas y 1 rechazada. Luego, la SC-24 (dirección de atención del profesional, FS-HU-04 y FS-HU-06): 24 solicitudes, 23 aceptadas y 1 rechazada. Se actualiza con cada cambio de alcance.</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       <c r="F5" s="43" t="n"/>
       <c r="G5" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.23: Vista Física como diagrama de despliegue UML (Ilustración 10) y Vista Lógica por capas.</t>
+          <t>DAS v1.24: Vista Física como diagrama de despliegue UML (Ilustración 10) y Vista Lógica por capas.</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1815,7 @@
       <c r="F6" s="43" t="n"/>
       <c r="G6" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.23, Vista Física: tabla de nodos y diagrama de despliegue UML (Nginx, Node.js/Express, MySQL 8, MapLibre GL JS con OpenFreeMap, API de Claude, Google Identity Services y servidor SMTP).</t>
+          <t>DAS v1.24, Vista Física: tabla de nodos y diagrama de despliegue UML (Nginx, Node.js/Express, MySQL 8, MapLibre GL JS con OpenFreeMap, API de Claude, Google Identity Services y servidor SMTP).</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       <c r="F7" s="43" t="n"/>
       <c r="G7" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.23, Vista Física: tabla de comunicación y rutas del diagrama de despliegue (HTTPS/REST/JSON, JWT, TCP 3306, proxy Nginx, verificación de Google y SMTP con TLS).</t>
+          <t>DAS v1.24, Vista Física: tabla de comunicación y rutas del diagrama de despliegue (HTTPS/REST/JSON, JWT, TCP 3306, proxy Nginx, verificación de Google y SMTP con TLS).</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       <c r="F8" s="43" t="n"/>
       <c r="G8" s="43" t="inlineStr">
         <is>
-          <t>Diagrama entidad-relación de las doce tablas implementadas al 12-10-2026 (Ilustración 4 del DAS v1.23, generado desde Diagramas (Miro)/Actualización Sprint 3); el modelo completo de quince tablas está en el diccionario de datos.</t>
+          <t>Diagrama entidad-relación de las doce tablas implementadas al 12-10-2026 (Ilustración 4 del DAS v1.24, generado desde Diagramas (Miro)/Actualización Sprint 3); el modelo completo de quince tablas está en el diccionario de datos.</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
       <c r="F9" s="43" t="n"/>
       <c r="G9" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.23, Vista Lógica &gt; Diccionario de datos: 15 tablas con tipos, PK, FK, restricciones e índices.</t>
+          <t>DAS v1.24, Vista Lógica &gt; Diccionario de datos: 15 tablas con tipos, PK, FK, restricciones e índices.</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       <c r="F10" s="43" t="n"/>
       <c r="G10" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.23, Ilustración 1 (casos de uso CU-01 a CU-09 con «include» y «extend», actualizada al 15-10-2026) y tabla de casos de uso.</t>
+          <t>DAS v1.24, Ilustración 1 (casos de uso CU-01 a CU-09 con «include» y «extend», actualizada al 15-10-2026) y tabla de casos de uso.</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
       <c r="F11" s="43" t="n"/>
       <c r="G11" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.23, Vista de Procesos: secuencias del registro de comida (Ilustración 5), de la elección del perfil y el asistente (Ilustración 6, en tres partes), de la reserva con reservas simultáneas (Ilustración 7) y de la recuperación de contraseña (Ilustración 8); flujos de la verificación administrativa (Ilustración 11) y de la disponibilidad y las reservas (Ilustración 12).</t>
+          <t>DAS v1.24, Vista de Procesos: secuencias del registro de comida (Ilustración 5), de la elección del perfil y el asistente (Ilustración 6, en tres partes), de la reserva con reservas simultáneas (Ilustración 7) y de la recuperación de contraseña (Ilustración 8); flujos de la verificación administrativa (Ilustración 11) y de la disponibilidad y las reservas (Ilustración 12).</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       <c r="F12" s="43" t="n"/>
       <c r="G12" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.23, Ilustración 13: diagrama UML de componentes e interfaces (13_Componentes_UML), fusionado el 12-10-2026 (PR #22); complementa la Vista de Desarrollo (Ilustración 9).</t>
+          <t>DAS v1.24, Ilustración 13: diagrama UML de componentes e interfaces (13_Componentes_UML), fusionado el 12-10-2026 (PR #22); complementa la Vista de Desarrollo (Ilustración 9).</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       <c r="F13" s="43" t="n"/>
       <c r="G13" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.23, Ilustración 2: asociaciones del modelo de clases del dominio (los atributos están en el diccionario de datos) y diagrama de estados de la reserva (Ilustración 3).</t>
+          <t>DAS v1.24, Ilustración 2: asociaciones del modelo de clases del dominio (los atributos están en el diccionario de datos) y diagrama de estados de la reserva (Ilustración 3).</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
       <c r="F22" s="43" t="n"/>
       <c r="G22" s="43" t="inlineStr">
         <is>
-          <t>Sprint 1: pruebas unitarias y de componentes con Jest (backend) y Vitest (frontend), todas aprobadas. Al 15-10-2026: 233 pruebas en el backend y 189 en el frontend, todas aprobadas. Al 19-10-2026: 233 en el backend y 208 en el frontend (mejoras de interfaz, SC-19; reserva con calendario, SC-20, y calendario al publicar horarios, SC-21), todas aprobadas.</t>
+          <t>Sprint 1: pruebas unitarias y de componentes con Jest (backend) y Vitest (frontend), todas aprobadas. Al 15-10-2026: 233 pruebas en el backend y 189 en el frontend, todas aprobadas. Al 19-10-2026: 241 en el backend y 231 en el frontend (mejoras de interfaz, SC-19; reserva con calendario, SC-20, y calendario al publicar horarios, SC-21; mapa limitado a Chile, defecto 35; detalle en el mapa, SC-22; buscador general, SC-23; dirección del profesional, SC-24), todas aprobadas.</t>
         </is>
       </c>
     </row>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
@@ -1549,7 +1549,7 @@
       <c r="I16" s="43" t="n"/>
       <c r="J16" s="43" t="inlineStr">
         <is>
-          <t>Planilla de Casos de Prueba: 80 casos (CP-001 a CP-080), 77 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 29 defectos: 26 corregidos y 3 abiertos (27 a 29, del mapa nuevo del PR #27). El 15-10-2026 se repitieron CP-076 y CP-077 con MapLibre (189/189 en el frontend); CP-078 sigue pendiente con el mapa nuevo. Comprobaciones con MySQL real: npm run test:mysql:agenda, 55/55 sobre main 662e79c el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema. 19-10-2026: CP-081 a CP-087 (mejoras de interfaz, SC-19), todos aprobados → 87 casos, 84 aprobados y 3 sin ejecutar (CP-024, CP-025 y CP-078); defectos 30 a 34 corregidos → 34 defectos: 31 corregidos y 3 abiertos (27 a 29). Evidencias en Plan de Pruebas/Mejoras_Interfaz_2026-10-19*. 19-10-2026 (SC-20, reserva con calendario): CP-088 a CP-091 aprobados → 91 casos, 88 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Flujo_Reservas_2026-10-19*. SC-21 (calendario al publicar horarios): CP-092 y CP-093 aprobados → 93 casos, 90 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Publicar_Horario_2026-10-19*. Defecto 35 (mapa que se veía de lejos por una ubicación fuera de Chile) corregido con CP-094 → 94 casos, 91 aprobados y 3 sin ejecutar; 35 defectos: 32 corregidos y 3 abiertos. Evidencias en Plan de Pruebas/Mapa_Chile_2026-10-19*. SC-22 (detalle del profesional en el mapa): CP-095 y CP-096 aprobados y defecto 28 corregido → 96 casos, 93 aprobados y 3 sin ejecutar; 35 defectos: 33 corregidos y 2 abiertos (27 y 29). Evidencias en Plan de Pruebas/Detalle_Mapa_2026-10-19*. SC-23 (buscador general del Inicio): CP-097 y CP-098 aprobados → 98 casos, 95 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Buscador_Inicio_2026-10-19*. SC-24 (dirección de atención y coordenadas en Chile en la ficha profesional): CP-099 y CP-100 aprobados → 100 casos, 97 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Direccion_Ficha_2026-10-19*.</t>
+          <t>Planilla de Casos de Prueba: 80 casos (CP-001 a CP-080), 77 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 29 defectos: 26 corregidos y 3 abiertos (27 a 29, del mapa nuevo del PR #27). El 15-10-2026 se repitieron CP-076 y CP-077 con MapLibre (189/189 en el frontend); CP-078 sigue pendiente con el mapa nuevo. Comprobaciones con MySQL real: npm run test:mysql:agenda, 55/55 sobre main 662e79c el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema. 19-10-2026: CP-081 a CP-087 (mejoras de interfaz, SC-19), todos aprobados → 87 casos, 84 aprobados y 3 sin ejecutar (CP-024, CP-025 y CP-078); defectos 30 a 34 corregidos → 34 defectos: 31 corregidos y 3 abiertos (27 a 29). Evidencias en Plan de Pruebas/Mejoras_Interfaz_2026-10-19*. 19-10-2026 (SC-20, reserva con calendario): CP-088 a CP-091 aprobados → 91 casos, 88 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Flujo_Reservas_2026-10-19*. SC-21 (calendario al publicar horarios): CP-092 y CP-093 aprobados → 93 casos, 90 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Publicar_Horario_2026-10-19*. Defecto 35 (mapa que se veía de lejos por una ubicación fuera de Chile) corregido con CP-094 → 94 casos, 91 aprobados y 3 sin ejecutar; 35 defectos: 32 corregidos y 3 abiertos. Evidencias en Plan de Pruebas/Mapa_Chile_2026-10-19*. SC-22 (detalle del profesional en el mapa): CP-095 y CP-096 aprobados y defecto 28 corregido → 96 casos, 93 aprobados y 3 sin ejecutar; 35 defectos: 33 corregidos y 2 abiertos (27 y 29). Evidencias en Plan de Pruebas/Detalle_Mapa_2026-10-19*. SC-23 (buscador general del Inicio): CP-097 y CP-098 aprobados → 98 casos, 95 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Buscador_Inicio_2026-10-19*. SC-24 (dirección de atención y coordenadas en Chile en la ficha profesional): CP-099 y CP-100 aprobados → 100 casos, 97 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Direccion_Ficha_2026-10-19*. 21-10-2026: corregidos los defectos 27 y 29 del mapa (CP-101 y CP-102 aprobados) → 102 casos, 99 aprobados y 3 sin ejecutar; 35 defectos, todos corregidos. Evidencias en Plan de Pruebas/Defectos_Mapa_2026-10-21*.</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
       <c r="F22" s="43" t="n"/>
       <c r="G22" s="43" t="inlineStr">
         <is>
-          <t>Sprint 1: pruebas unitarias y de componentes con Jest (backend) y Vitest (frontend), todas aprobadas. Al 15-10-2026: 233 pruebas en el backend y 189 en el frontend, todas aprobadas. Al 19-10-2026: 241 en el backend y 231 en el frontend (mejoras de interfaz, SC-19; reserva con calendario, SC-20, y calendario al publicar horarios, SC-21; mapa limitado a Chile, defecto 35; detalle en el mapa, SC-22; buscador general, SC-23; dirección del profesional, SC-24), todas aprobadas.</t>
+          <t>Sprint 1: pruebas unitarias y de componentes con Jest (backend) y Vitest (frontend), todas aprobadas. Al 15-10-2026: 233 pruebas en el backend y 189 en el frontend, todas aprobadas. Al 19-10-2026: 241 en el backend y 231 en el frontend (mejoras de interfaz, SC-19; reserva con calendario, SC-20, y calendario al publicar horarios, SC-21; mapa limitado a Chile, defecto 35; detalle en el mapa, SC-22; buscador general, SC-23; dirección del profesional, SC-24), todas aprobadas. Al 21-10-2026: 241 en el backend y 233 en el frontend (defectos 27 y 29 del mapa), todas aprobadas.</t>
         </is>
       </c>
     </row>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
@@ -1549,7 +1549,7 @@
       <c r="I16" s="43" t="n"/>
       <c r="J16" s="43" t="inlineStr">
         <is>
-          <t>Planilla de Casos de Prueba: 80 casos (CP-001 a CP-080), 77 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 29 defectos: 26 corregidos y 3 abiertos (27 a 29, del mapa nuevo del PR #27). El 15-10-2026 se repitieron CP-076 y CP-077 con MapLibre (189/189 en el frontend); CP-078 sigue pendiente con el mapa nuevo. Comprobaciones con MySQL real: npm run test:mysql:agenda, 55/55 sobre main 662e79c el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema. 19-10-2026: CP-081 a CP-087 (mejoras de interfaz, SC-19), todos aprobados → 87 casos, 84 aprobados y 3 sin ejecutar (CP-024, CP-025 y CP-078); defectos 30 a 34 corregidos → 34 defectos: 31 corregidos y 3 abiertos (27 a 29). Evidencias en Plan de Pruebas/Mejoras_Interfaz_2026-10-19*. 19-10-2026 (SC-20, reserva con calendario): CP-088 a CP-091 aprobados → 91 casos, 88 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Flujo_Reservas_2026-10-19*. SC-21 (calendario al publicar horarios): CP-092 y CP-093 aprobados → 93 casos, 90 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Publicar_Horario_2026-10-19*. Defecto 35 (mapa que se veía de lejos por una ubicación fuera de Chile) corregido con CP-094 → 94 casos, 91 aprobados y 3 sin ejecutar; 35 defectos: 32 corregidos y 3 abiertos. Evidencias en Plan de Pruebas/Mapa_Chile_2026-10-19*. SC-22 (detalle del profesional en el mapa): CP-095 y CP-096 aprobados y defecto 28 corregido → 96 casos, 93 aprobados y 3 sin ejecutar; 35 defectos: 33 corregidos y 2 abiertos (27 y 29). Evidencias en Plan de Pruebas/Detalle_Mapa_2026-10-19*. SC-23 (buscador general del Inicio): CP-097 y CP-098 aprobados → 98 casos, 95 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Buscador_Inicio_2026-10-19*. SC-24 (dirección de atención y coordenadas en Chile en la ficha profesional): CP-099 y CP-100 aprobados → 100 casos, 97 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Direccion_Ficha_2026-10-19*. 21-10-2026: corregidos los defectos 27 y 29 del mapa (CP-101 y CP-102 aprobados) → 102 casos, 99 aprobados y 3 sin ejecutar; 35 defectos, todos corregidos. Evidencias en Plan de Pruebas/Defectos_Mapa_2026-10-21*.</t>
+          <t>Planilla de Casos de Prueba: 80 casos (CP-001 a CP-080), 77 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 29 defectos: 26 corregidos y 3 abiertos (27 a 29, del mapa nuevo del PR #27). El 15-10-2026 se repitieron CP-076 y CP-077 con MapLibre (189/189 en el frontend); CP-078 sigue pendiente con el mapa nuevo. Comprobaciones con MySQL real: npm run test:mysql:agenda, 55/55 sobre main 662e79c el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema. 19-10-2026: CP-081 a CP-087 (mejoras de interfaz, SC-19), todos aprobados → 87 casos, 84 aprobados y 3 sin ejecutar (CP-024, CP-025 y CP-078); defectos 30 a 34 corregidos → 34 defectos: 31 corregidos y 3 abiertos (27 a 29). Evidencias en Plan de Pruebas/Mejoras_Interfaz_2026-10-19*. 19-10-2026 (SC-20, reserva con calendario): CP-088 a CP-091 aprobados → 91 casos, 88 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Flujo_Reservas_2026-10-19*. SC-21 (calendario al publicar horarios): CP-092 y CP-093 aprobados → 93 casos, 90 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Publicar_Horario_2026-10-19*. Defecto 35 (mapa que se veía de lejos por una ubicación fuera de Chile) corregido con CP-094 → 94 casos, 91 aprobados y 3 sin ejecutar; 35 defectos: 32 corregidos y 3 abiertos. Evidencias en Plan de Pruebas/Mapa_Chile_2026-10-19*. SC-22 (detalle del profesional en el mapa): CP-095 y CP-096 aprobados y defecto 28 corregido → 96 casos, 93 aprobados y 3 sin ejecutar; 35 defectos: 33 corregidos y 2 abiertos (27 y 29). Evidencias en Plan de Pruebas/Detalle_Mapa_2026-10-19*. SC-23 (buscador general del Inicio): CP-097 y CP-098 aprobados → 98 casos, 95 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Buscador_Inicio_2026-10-19*. SC-24 (dirección de atención y coordenadas en Chile en la ficha profesional): CP-099 y CP-100 aprobados → 100 casos, 97 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Direccion_Ficha_2026-10-19*. 21-10-2026: corregidos los defectos 27 y 29 del mapa (CP-101 y CP-102 aprobados) → 102 casos, 99 aprobados y 3 sin ejecutar; 35 defectos, todos corregidos. Evidencias en Plan de Pruebas/Defectos_Mapa_2026-10-21*. 21-10-2026: asistente IA (FS-HU-07, SC-25): CP-103 a CP-108 aprobados y CP-109 (respuesta real de Groq) pendiente de la clave → 109 casos, 105 aprobados y 4 sin ejecutar. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-21*.</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       <c r="I18" s="43" t="n"/>
       <c r="J18" s="43" t="inlineStr">
         <is>
-          <t>FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx. Al 15-10-2026 registra 18 solicitudes (SC-01 a SC-18): 17 aceptadas y 1 rechazada (Google Places en FS-HU-03). Las SC-12 a SC-17 cubren el flujo y el espacio del profesional, el clima en su Inicio, el menú del usuario, la elección del perfil en una pantalla propia, el panel del administrador con FS-HU-12 en el Sprint 3 el límite de una reserva activa por usuario con cada profesional y el cambio del mapa a MapLibre GL JS con OpenFreeMap (SC-18, PR #27). El 19-10-2026 se agregó la SC-19 (mejoras de respuesta y movimiento de la interfaz, con los defectos 30 a 34): 19 solicitudes, 18 aceptadas y 1 rechazada. Ese mismo día se agregó la SC-20 (reserva con calendario en FS-HU-14): 20 solicitudes, 19 aceptadas y 1 rechazada. Luego, la SC-21 (calendario al publicar horarios en FS-HU-13): 21 solicitudes, 20 aceptadas y 1 rechazada. Luego, la SC-22 (detalle del profesional en la ventana del mapa, FS-HU-06): 22 solicitudes, 21 aceptadas y 1 rechazada. Luego, la SC-23 (buscador general del Inicio, FS-HU-21): 23 solicitudes, 22 aceptadas y 1 rechazada. Luego, la SC-24 (dirección de atención del profesional, FS-HU-04 y FS-HU-06): 24 solicitudes, 23 aceptadas y 1 rechazada. Se actualiza con cada cambio de alcance.</t>
+          <t>FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx. Al 15-10-2026 registra 18 solicitudes (SC-01 a SC-18): 17 aceptadas y 1 rechazada (Google Places en FS-HU-03). Las SC-12 a SC-17 cubren el flujo y el espacio del profesional, el clima en su Inicio, el menú del usuario, la elección del perfil en una pantalla propia, el panel del administrador con FS-HU-12 en el Sprint 3 el límite de una reserva activa por usuario con cada profesional y el cambio del mapa a MapLibre GL JS con OpenFreeMap (SC-18, PR #27). El 19-10-2026 se agregó la SC-19 (mejoras de respuesta y movimiento de la interfaz, con los defectos 30 a 34): 19 solicitudes, 18 aceptadas y 1 rechazada. Ese mismo día se agregó la SC-20 (reserva con calendario en FS-HU-14): 20 solicitudes, 19 aceptadas y 1 rechazada. Luego, la SC-21 (calendario al publicar horarios en FS-HU-13): 21 solicitudes, 20 aceptadas y 1 rechazada. Luego, la SC-22 (detalle del profesional en la ventana del mapa, FS-HU-06): 22 solicitudes, 21 aceptadas y 1 rechazada. Luego, la SC-23 (buscador general del Inicio, FS-HU-21): 23 solicitudes, 22 aceptadas y 1 rechazada. Luego, la SC-24 (dirección de atención del profesional, FS-HU-04 y FS-HU-06): 24 solicitudes, 23 aceptadas y 1 rechazada. Luego, la SC-25 (proveedor del asistente IA: Groq en vez de la API de Claude, FS-HU-07 y FS-HU-08): 25 solicitudes, 24 aceptadas y 1 rechazada. Se actualiza con cada cambio de alcance.</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       <c r="F5" s="43" t="n"/>
       <c r="G5" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.24: Vista Física como diagrama de despliegue UML (Ilustración 10) y Vista Lógica por capas.</t>
+          <t>DAS v1.25: Vista Física como diagrama de despliegue UML (Ilustración 10) y Vista Lógica por capas.</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1815,7 @@
       <c r="F6" s="43" t="n"/>
       <c r="G6" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.24, Vista Física: tabla de nodos y diagrama de despliegue UML (Nginx, Node.js/Express, MySQL 8, MapLibre GL JS con OpenFreeMap, API de Claude, Google Identity Services y servidor SMTP).</t>
+          <t>DAS v1.25, Vista Física: tabla de nodos y diagrama de despliegue UML (Nginx, Node.js/Express, MySQL 8, MapLibre GL JS con OpenFreeMap, Groq (API de IA), Google Identity Services y servidor SMTP).</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       <c r="F7" s="43" t="n"/>
       <c r="G7" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.24, Vista Física: tabla de comunicación y rutas del diagrama de despliegue (HTTPS/REST/JSON, JWT, TCP 3306, proxy Nginx, verificación de Google y SMTP con TLS).</t>
+          <t>DAS v1.25, Vista Física: tabla de comunicación y rutas del diagrama de despliegue (HTTPS/REST/JSON, JWT, TCP 3306, proxy Nginx, verificación de Google y SMTP con TLS).</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       <c r="F8" s="43" t="n"/>
       <c r="G8" s="43" t="inlineStr">
         <is>
-          <t>Diagrama entidad-relación de las doce tablas implementadas al 12-10-2026 (Ilustración 4 del DAS v1.24, generado desde Diagramas (Miro)/Actualización Sprint 3); el modelo completo de quince tablas está en el diccionario de datos.</t>
+          <t>Diagrama entidad-relación de las quince tablas implementadas al 21-10-2026 (Ilustración 4 del DAS v1.25, generado desde Diagramas (Miro)/Actualización Sprint 3); el modelo completo de dieciséis tablas está en el diccionario de datos.</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
       <c r="F9" s="43" t="n"/>
       <c r="G9" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.24, Vista Lógica &gt; Diccionario de datos: 15 tablas con tipos, PK, FK, restricciones e índices.</t>
+          <t>DAS v1.25, Vista Lógica &gt; Diccionario de datos: 16 tablas con tipos, PK, FK, restricciones e índices.</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       <c r="F10" s="43" t="n"/>
       <c r="G10" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.24, Ilustración 1 (casos de uso CU-01 a CU-09 con «include» y «extend», actualizada al 15-10-2026) y tabla de casos de uso.</t>
+          <t>DAS v1.25, Ilustración 1 (casos de uso CU-01 a CU-09 con «include» y «extend», actualizada al 15-10-2026) y tabla de casos de uso.</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
       <c r="F11" s="43" t="n"/>
       <c r="G11" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.24, Vista de Procesos: secuencias del registro de comida (Ilustración 5), de la elección del perfil y el asistente (Ilustración 6, en tres partes), de la reserva con reservas simultáneas (Ilustración 7) y de la recuperación de contraseña (Ilustración 8); flujos de la verificación administrativa (Ilustración 11) y de la disponibilidad y las reservas (Ilustración 12).</t>
+          <t>DAS v1.25, Vista de Procesos: secuencias del registro de comida (Ilustración 5), de la elección del perfil y el asistente (Ilustración 6, en tres partes), de la reserva con reservas simultáneas (Ilustración 7) y de la recuperación de contraseña (Ilustración 8); flujos de la verificación administrativa (Ilustración 11) y de la disponibilidad y las reservas (Ilustración 12).</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       <c r="F12" s="43" t="n"/>
       <c r="G12" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.24, Ilustración 13: diagrama UML de componentes e interfaces (13_Componentes_UML), fusionado el 12-10-2026 (PR #22); complementa la Vista de Desarrollo (Ilustración 9).</t>
+          <t>DAS v1.25, Ilustración 13: diagrama UML de componentes e interfaces (13_Componentes_UML), fusionado el 12-10-2026 (PR #22); complementa la Vista de Desarrollo (Ilustración 9).</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       <c r="F13" s="43" t="n"/>
       <c r="G13" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.24, Ilustración 2: asociaciones del modelo de clases del dominio (los atributos están en el diccionario de datos) y diagrama de estados de la reserva (Ilustración 3).</t>
+          <t>DAS v1.25, Ilustración 2: asociaciones del modelo de clases del dominio (los atributos están en el diccionario de datos) y diagrama de estados de la reserva (Ilustración 3).</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
       <c r="F22" s="43" t="n"/>
       <c r="G22" s="43" t="inlineStr">
         <is>
-          <t>Sprint 1: pruebas unitarias y de componentes con Jest (backend) y Vitest (frontend), todas aprobadas. Al 15-10-2026: 233 pruebas en el backend y 189 en el frontend, todas aprobadas. Al 19-10-2026: 241 en el backend y 231 en el frontend (mejoras de interfaz, SC-19; reserva con calendario, SC-20, y calendario al publicar horarios, SC-21; mapa limitado a Chile, defecto 35; detalle en el mapa, SC-22; buscador general, SC-23; dirección del profesional, SC-24), todas aprobadas. Al 21-10-2026: 241 en el backend y 233 en el frontend (defectos 27 y 29 del mapa), todas aprobadas.</t>
+          <t>Sprint 1: pruebas unitarias y de componentes con Jest (backend) y Vitest (frontend), todas aprobadas. Al 15-10-2026: 233 pruebas en el backend y 189 en el frontend, todas aprobadas. Al 19-10-2026: 241 en el backend y 231 en el frontend (mejoras de interfaz, SC-19; reserva con calendario, SC-20, y calendario al publicar horarios, SC-21; mapa limitado a Chile, defecto 35; detalle en el mapa, SC-22; buscador general, SC-23; dirección del profesional, SC-24), todas aprobadas. Al 21-10-2026: 241 en el backend y 233 en el frontend (defectos 27 y 29 del mapa), todas aprobadas. Con el asistente IA (FS-HU-07, 21-10-2026): 267 en el backend y 245 en el frontend, todas aprobadas.</t>
         </is>
       </c>
     </row>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
@@ -1549,7 +1549,7 @@
       <c r="I16" s="43" t="n"/>
       <c r="J16" s="43" t="inlineStr">
         <is>
-          <t>Planilla de Casos de Prueba: 80 casos (CP-001 a CP-080), 77 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 29 defectos: 26 corregidos y 3 abiertos (27 a 29, del mapa nuevo del PR #27). El 15-10-2026 se repitieron CP-076 y CP-077 con MapLibre (189/189 en el frontend); CP-078 sigue pendiente con el mapa nuevo. Comprobaciones con MySQL real: npm run test:mysql:agenda, 55/55 sobre main 662e79c el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema. 19-10-2026: CP-081 a CP-087 (mejoras de interfaz, SC-19), todos aprobados → 87 casos, 84 aprobados y 3 sin ejecutar (CP-024, CP-025 y CP-078); defectos 30 a 34 corregidos → 34 defectos: 31 corregidos y 3 abiertos (27 a 29). Evidencias en Plan de Pruebas/Mejoras_Interfaz_2026-10-19*. 19-10-2026 (SC-20, reserva con calendario): CP-088 a CP-091 aprobados → 91 casos, 88 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Flujo_Reservas_2026-10-19*. SC-21 (calendario al publicar horarios): CP-092 y CP-093 aprobados → 93 casos, 90 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Publicar_Horario_2026-10-19*. Defecto 35 (mapa que se veía de lejos por una ubicación fuera de Chile) corregido con CP-094 → 94 casos, 91 aprobados y 3 sin ejecutar; 35 defectos: 32 corregidos y 3 abiertos. Evidencias en Plan de Pruebas/Mapa_Chile_2026-10-19*. SC-22 (detalle del profesional en el mapa): CP-095 y CP-096 aprobados y defecto 28 corregido → 96 casos, 93 aprobados y 3 sin ejecutar; 35 defectos: 33 corregidos y 2 abiertos (27 y 29). Evidencias en Plan de Pruebas/Detalle_Mapa_2026-10-19*. SC-23 (buscador general del Inicio): CP-097 y CP-098 aprobados → 98 casos, 95 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Buscador_Inicio_2026-10-19*. SC-24 (dirección de atención y coordenadas en Chile en la ficha profesional): CP-099 y CP-100 aprobados → 100 casos, 97 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Direccion_Ficha_2026-10-19*. 21-10-2026: corregidos los defectos 27 y 29 del mapa (CP-101 y CP-102 aprobados) → 102 casos, 99 aprobados y 3 sin ejecutar; 35 defectos, todos corregidos. Evidencias en Plan de Pruebas/Defectos_Mapa_2026-10-21*. 21-10-2026: asistente IA (FS-HU-07, SC-25): CP-103 a CP-108 aprobados y CP-109 (respuesta real de Groq) pendiente de la clave → 109 casos, 105 aprobados y 4 sin ejecutar. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-21*.</t>
+          <t>Planilla de Casos de Prueba: 80 casos (CP-001 a CP-080), 77 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 29 defectos: 26 corregidos y 3 abiertos (27 a 29, del mapa nuevo del PR #27). El 15-10-2026 se repitieron CP-076 y CP-077 con MapLibre (189/189 en el frontend); CP-078 sigue pendiente con el mapa nuevo. Comprobaciones con MySQL real: npm run test:mysql:agenda, 55/55 sobre main 662e79c el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema. 19-10-2026: CP-081 a CP-087 (mejoras de interfaz, SC-19), todos aprobados → 87 casos, 84 aprobados y 3 sin ejecutar (CP-024, CP-025 y CP-078); defectos 30 a 34 corregidos → 34 defectos: 31 corregidos y 3 abiertos (27 a 29). Evidencias en Plan de Pruebas/Mejoras_Interfaz_2026-10-19*. 19-10-2026 (SC-20, reserva con calendario): CP-088 a CP-091 aprobados → 91 casos, 88 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Flujo_Reservas_2026-10-19*. SC-21 (calendario al publicar horarios): CP-092 y CP-093 aprobados → 93 casos, 90 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Publicar_Horario_2026-10-19*. Defecto 35 (mapa que se veía de lejos por una ubicación fuera de Chile) corregido con CP-094 → 94 casos, 91 aprobados y 3 sin ejecutar; 35 defectos: 32 corregidos y 3 abiertos. Evidencias en Plan de Pruebas/Mapa_Chile_2026-10-19*. SC-22 (detalle del profesional en el mapa): CP-095 y CP-096 aprobados y defecto 28 corregido → 96 casos, 93 aprobados y 3 sin ejecutar; 35 defectos: 33 corregidos y 2 abiertos (27 y 29). Evidencias en Plan de Pruebas/Detalle_Mapa_2026-10-19*. SC-23 (buscador general del Inicio): CP-097 y CP-098 aprobados → 98 casos, 95 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Buscador_Inicio_2026-10-19*. SC-24 (dirección de atención y coordenadas en Chile en la ficha profesional): CP-099 y CP-100 aprobados → 100 casos, 97 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Direccion_Ficha_2026-10-19*. 21-10-2026: corregidos los defectos 27 y 29 del mapa (CP-101 y CP-102 aprobados) → 102 casos, 99 aprobados y 3 sin ejecutar; 35 defectos, todos corregidos. Evidencias en Plan de Pruebas/Defectos_Mapa_2026-10-21*. 21-10-2026: asistente IA (FS-HU-07, SC-25): CP-103 a CP-108 aprobados y CP-109 (respuesta real de Groq) pendiente de la clave → 109 casos, 105 aprobados y 4 sin ejecutar. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-21*. 22-10-2026: CP-109 aprobado con Groq real (modelo openai/gpt-oss-120b) y defecto 36 corregido → 109 casos, 106 aprobados y 3 sin ejecutar; 36 defectos, todos corregidos. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-22_groq_real*.</t>
         </is>
       </c>
     </row>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
@@ -1549,7 +1549,7 @@
       <c r="I16" s="43" t="n"/>
       <c r="J16" s="43" t="inlineStr">
         <is>
-          <t>Planilla de Casos de Prueba: 80 casos (CP-001 a CP-080), 77 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 29 defectos: 26 corregidos y 3 abiertos (27 a 29, del mapa nuevo del PR #27). El 15-10-2026 se repitieron CP-076 y CP-077 con MapLibre (189/189 en el frontend); CP-078 sigue pendiente con el mapa nuevo. Comprobaciones con MySQL real: npm run test:mysql:agenda, 55/55 sobre main 662e79c el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema. 19-10-2026: CP-081 a CP-087 (mejoras de interfaz, SC-19), todos aprobados → 87 casos, 84 aprobados y 3 sin ejecutar (CP-024, CP-025 y CP-078); defectos 30 a 34 corregidos → 34 defectos: 31 corregidos y 3 abiertos (27 a 29). Evidencias en Plan de Pruebas/Mejoras_Interfaz_2026-10-19*. 19-10-2026 (SC-20, reserva con calendario): CP-088 a CP-091 aprobados → 91 casos, 88 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Flujo_Reservas_2026-10-19*. SC-21 (calendario al publicar horarios): CP-092 y CP-093 aprobados → 93 casos, 90 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Publicar_Horario_2026-10-19*. Defecto 35 (mapa que se veía de lejos por una ubicación fuera de Chile) corregido con CP-094 → 94 casos, 91 aprobados y 3 sin ejecutar; 35 defectos: 32 corregidos y 3 abiertos. Evidencias en Plan de Pruebas/Mapa_Chile_2026-10-19*. SC-22 (detalle del profesional en el mapa): CP-095 y CP-096 aprobados y defecto 28 corregido → 96 casos, 93 aprobados y 3 sin ejecutar; 35 defectos: 33 corregidos y 2 abiertos (27 y 29). Evidencias en Plan de Pruebas/Detalle_Mapa_2026-10-19*. SC-23 (buscador general del Inicio): CP-097 y CP-098 aprobados → 98 casos, 95 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Buscador_Inicio_2026-10-19*. SC-24 (dirección de atención y coordenadas en Chile en la ficha profesional): CP-099 y CP-100 aprobados → 100 casos, 97 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Direccion_Ficha_2026-10-19*. 21-10-2026: corregidos los defectos 27 y 29 del mapa (CP-101 y CP-102 aprobados) → 102 casos, 99 aprobados y 3 sin ejecutar; 35 defectos, todos corregidos. Evidencias en Plan de Pruebas/Defectos_Mapa_2026-10-21*. 21-10-2026: asistente IA (FS-HU-07, SC-25): CP-103 a CP-108 aprobados y CP-109 (respuesta real de Groq) pendiente de la clave → 109 casos, 105 aprobados y 4 sin ejecutar. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-21*. 22-10-2026: CP-109 aprobado con Groq real (modelo openai/gpt-oss-120b) y defecto 36 corregido → 109 casos, 106 aprobados y 3 sin ejecutar; 36 defectos, todos corregidos. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-22_groq_real*.</t>
+          <t>Planilla de Casos de Prueba: 80 casos (CP-001 a CP-080), 77 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 29 defectos: 26 corregidos y 3 abiertos (27 a 29, del mapa nuevo del PR #27). El 15-10-2026 se repitieron CP-076 y CP-077 con MapLibre (189/189 en el frontend); CP-078 sigue pendiente con el mapa nuevo. Comprobaciones con MySQL real: npm run test:mysql:agenda, 55/55 sobre main 662e79c el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema. 19-10-2026: CP-081 a CP-087 (mejoras de interfaz, SC-19), todos aprobados → 87 casos, 84 aprobados y 3 sin ejecutar (CP-024, CP-025 y CP-078); defectos 30 a 34 corregidos → 34 defectos: 31 corregidos y 3 abiertos (27 a 29). Evidencias en Plan de Pruebas/Mejoras_Interfaz_2026-10-19*. 19-10-2026 (SC-20, reserva con calendario): CP-088 a CP-091 aprobados → 91 casos, 88 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Flujo_Reservas_2026-10-19*. SC-21 (calendario al publicar horarios): CP-092 y CP-093 aprobados → 93 casos, 90 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Publicar_Horario_2026-10-19*. Defecto 35 (mapa que se veía de lejos por una ubicación fuera de Chile) corregido con CP-094 → 94 casos, 91 aprobados y 3 sin ejecutar; 35 defectos: 32 corregidos y 3 abiertos. Evidencias en Plan de Pruebas/Mapa_Chile_2026-10-19*. SC-22 (detalle del profesional en el mapa): CP-095 y CP-096 aprobados y defecto 28 corregido → 96 casos, 93 aprobados y 3 sin ejecutar; 35 defectos: 33 corregidos y 2 abiertos (27 y 29). Evidencias en Plan de Pruebas/Detalle_Mapa_2026-10-19*. SC-23 (buscador general del Inicio): CP-097 y CP-098 aprobados → 98 casos, 95 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Buscador_Inicio_2026-10-19*. SC-24 (dirección de atención y coordenadas en Chile en la ficha profesional): CP-099 y CP-100 aprobados → 100 casos, 97 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Direccion_Ficha_2026-10-19*. 21-10-2026: corregidos los defectos 27 y 29 del mapa (CP-101 y CP-102 aprobados) → 102 casos, 99 aprobados y 3 sin ejecutar; 35 defectos, todos corregidos. Evidencias en Plan de Pruebas/Defectos_Mapa_2026-10-21*. 21-10-2026: asistente IA (FS-HU-07, SC-25): CP-103 a CP-108 aprobados y CP-109 (respuesta real de Groq) pendiente de la clave → 109 casos, 105 aprobados y 4 sin ejecutar. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-21*. 22-10-2026: CP-109 aprobado con Groq real (modelo openai/gpt-oss-120b) y defecto 36 corregido → 109 casos, 106 aprobados y 3 sin ejecutar; 36 defectos, todos corregidos. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-22_groq_real*. 22-10-2026: FS-HU-08 (recomendación de profesional) y SC-26 (el SAMU solo en situaciones críticas): CP-110 a CP-114 aprobados → 114 casos, 111 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Recomendacion_Profesional_2026-10-22*.</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       <c r="I18" s="43" t="n"/>
       <c r="J18" s="43" t="inlineStr">
         <is>
-          <t>FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx. Al 15-10-2026 registra 18 solicitudes (SC-01 a SC-18): 17 aceptadas y 1 rechazada (Google Places en FS-HU-03). Las SC-12 a SC-17 cubren el flujo y el espacio del profesional, el clima en su Inicio, el menú del usuario, la elección del perfil en una pantalla propia, el panel del administrador con FS-HU-12 en el Sprint 3 el límite de una reserva activa por usuario con cada profesional y el cambio del mapa a MapLibre GL JS con OpenFreeMap (SC-18, PR #27). El 19-10-2026 se agregó la SC-19 (mejoras de respuesta y movimiento de la interfaz, con los defectos 30 a 34): 19 solicitudes, 18 aceptadas y 1 rechazada. Ese mismo día se agregó la SC-20 (reserva con calendario en FS-HU-14): 20 solicitudes, 19 aceptadas y 1 rechazada. Luego, la SC-21 (calendario al publicar horarios en FS-HU-13): 21 solicitudes, 20 aceptadas y 1 rechazada. Luego, la SC-22 (detalle del profesional en la ventana del mapa, FS-HU-06): 22 solicitudes, 21 aceptadas y 1 rechazada. Luego, la SC-23 (buscador general del Inicio, FS-HU-21): 23 solicitudes, 22 aceptadas y 1 rechazada. Luego, la SC-24 (dirección de atención del profesional, FS-HU-04 y FS-HU-06): 24 solicitudes, 23 aceptadas y 1 rechazada. Luego, la SC-25 (proveedor del asistente IA: Groq en vez de la API de Claude, FS-HU-07 y FS-HU-08): 25 solicitudes, 24 aceptadas y 1 rechazada. Se actualiza con cada cambio de alcance.</t>
+          <t>FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx. Al 15-10-2026 registra 18 solicitudes (SC-01 a SC-18): 17 aceptadas y 1 rechazada (Google Places en FS-HU-03). Las SC-12 a SC-17 cubren el flujo y el espacio del profesional, el clima en su Inicio, el menú del usuario, la elección del perfil en una pantalla propia, el panel del administrador con FS-HU-12 en el Sprint 3 el límite de una reserva activa por usuario con cada profesional y el cambio del mapa a MapLibre GL JS con OpenFreeMap (SC-18, PR #27). El 19-10-2026 se agregó la SC-19 (mejoras de respuesta y movimiento de la interfaz, con los defectos 30 a 34): 19 solicitudes, 18 aceptadas y 1 rechazada. Ese mismo día se agregó la SC-20 (reserva con calendario en FS-HU-14): 20 solicitudes, 19 aceptadas y 1 rechazada. Luego, la SC-21 (calendario al publicar horarios en FS-HU-13): 21 solicitudes, 20 aceptadas y 1 rechazada. Luego, la SC-22 (detalle del profesional en la ventana del mapa, FS-HU-06): 22 solicitudes, 21 aceptadas y 1 rechazada. Luego, la SC-23 (buscador general del Inicio, FS-HU-21): 23 solicitudes, 22 aceptadas y 1 rechazada. Luego, la SC-24 (dirección de atención del profesional, FS-HU-04 y FS-HU-06): 24 solicitudes, 23 aceptadas y 1 rechazada. Luego, la SC-25 (proveedor del asistente IA: Groq en vez de la API de Claude, FS-HU-07 y FS-HU-08): 25 solicitudes, 24 aceptadas y 1 rechazada. Luego, la SC-26 (el asistente nombra el SAMU solo en situaciones críticas, FS-HU-07): 26 solicitudes, 25 aceptadas y 1 rechazada. Se actualiza con cada cambio de alcance.</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       <c r="F5" s="43" t="n"/>
       <c r="G5" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.25: Vista Física como diagrama de despliegue UML (Ilustración 10) y Vista Lógica por capas.</t>
+          <t>DAS v1.26: Vista Física como diagrama de despliegue UML (Ilustración 10) y Vista Lógica por capas.</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1815,7 @@
       <c r="F6" s="43" t="n"/>
       <c r="G6" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.25, Vista Física: tabla de nodos y diagrama de despliegue UML (Nginx, Node.js/Express, MySQL 8, MapLibre GL JS con OpenFreeMap, Groq (API de IA), Google Identity Services y servidor SMTP).</t>
+          <t>DAS v1.26, Vista Física: tabla de nodos y diagrama de despliegue UML (Nginx, Node.js/Express, MySQL 8, MapLibre GL JS con OpenFreeMap, Groq (API de IA), Google Identity Services y servidor SMTP).</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       <c r="F7" s="43" t="n"/>
       <c r="G7" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.25, Vista Física: tabla de comunicación y rutas del diagrama de despliegue (HTTPS/REST/JSON, JWT, TCP 3306, proxy Nginx, verificación de Google y SMTP con TLS).</t>
+          <t>DAS v1.26, Vista Física: tabla de comunicación y rutas del diagrama de despliegue (HTTPS/REST/JSON, JWT, TCP 3306, proxy Nginx, verificación de Google y SMTP con TLS).</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       <c r="F8" s="43" t="n"/>
       <c r="G8" s="43" t="inlineStr">
         <is>
-          <t>Diagrama entidad-relación de las quince tablas implementadas al 21-10-2026 (Ilustración 4 del DAS v1.25, generado desde Diagramas (Miro)/Actualización Sprint 3); el modelo completo de dieciséis tablas está en el diccionario de datos.</t>
+          <t>Diagrama entidad-relación de las quince tablas implementadas al 21-10-2026 (Ilustración 4 del DAS v1.26, generado desde Diagramas (Miro)/Actualización Sprint 3); el modelo completo de dieciséis tablas está en el diccionario de datos.</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
       <c r="F9" s="43" t="n"/>
       <c r="G9" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.25, Vista Lógica &gt; Diccionario de datos: 16 tablas con tipos, PK, FK, restricciones e índices.</t>
+          <t>DAS v1.26, Vista Lógica &gt; Diccionario de datos: 16 tablas con tipos, PK, FK, restricciones e índices.</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       <c r="F10" s="43" t="n"/>
       <c r="G10" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.25, Ilustración 1 (casos de uso CU-01 a CU-09 con «include» y «extend», actualizada al 15-10-2026) y tabla de casos de uso.</t>
+          <t>DAS v1.26, Ilustración 1 (casos de uso CU-01 a CU-09 con «include» y «extend», actualizada al 15-10-2026) y tabla de casos de uso.</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
       <c r="F11" s="43" t="n"/>
       <c r="G11" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.25, Vista de Procesos: secuencias del registro de comida (Ilustración 5), de la elección del perfil y el asistente (Ilustración 6, en tres partes), de la reserva con reservas simultáneas (Ilustración 7) y de la recuperación de contraseña (Ilustración 8); flujos de la verificación administrativa (Ilustración 11) y de la disponibilidad y las reservas (Ilustración 12).</t>
+          <t>DAS v1.26, Vista de Procesos: secuencias del registro de comida (Ilustración 5), de la elección del perfil y el asistente (Ilustración 6, en tres partes), de la reserva con reservas simultáneas (Ilustración 7) y de la recuperación de contraseña (Ilustración 8); flujos de la verificación administrativa (Ilustración 11) y de la disponibilidad y las reservas (Ilustración 12).</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       <c r="F12" s="43" t="n"/>
       <c r="G12" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.25, Ilustración 13: diagrama UML de componentes e interfaces (13_Componentes_UML), fusionado el 12-10-2026 (PR #22); complementa la Vista de Desarrollo (Ilustración 9).</t>
+          <t>DAS v1.26, Ilustración 13: diagrama UML de componentes e interfaces (13_Componentes_UML), fusionado el 12-10-2026 (PR #22); complementa la Vista de Desarrollo (Ilustración 9).</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       <c r="F13" s="43" t="n"/>
       <c r="G13" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.25, Ilustración 2: asociaciones del modelo de clases del dominio (los atributos están en el diccionario de datos) y diagrama de estados de la reserva (Ilustración 3).</t>
+          <t>DAS v1.26, Ilustración 2: asociaciones del modelo de clases del dominio (los atributos están en el diccionario de datos) y diagrama de estados de la reserva (Ilustración 3).</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
       <c r="F22" s="43" t="n"/>
       <c r="G22" s="43" t="inlineStr">
         <is>
-          <t>Sprint 1: pruebas unitarias y de componentes con Jest (backend) y Vitest (frontend), todas aprobadas. Al 15-10-2026: 233 pruebas en el backend y 189 en el frontend, todas aprobadas. Al 19-10-2026: 241 en el backend y 231 en el frontend (mejoras de interfaz, SC-19; reserva con calendario, SC-20, y calendario al publicar horarios, SC-21; mapa limitado a Chile, defecto 35; detalle en el mapa, SC-22; buscador general, SC-23; dirección del profesional, SC-24), todas aprobadas. Al 21-10-2026: 241 en el backend y 233 en el frontend (defectos 27 y 29 del mapa), todas aprobadas. Con el asistente IA (FS-HU-07, 21-10-2026): 267 en el backend y 245 en el frontend, todas aprobadas.</t>
+          <t>Sprint 1: pruebas unitarias y de componentes con Jest (backend) y Vitest (frontend), todas aprobadas. Al 15-10-2026: 233 pruebas en el backend y 189 en el frontend, todas aprobadas. Al 19-10-2026: 241 en el backend y 231 en el frontend (mejoras de interfaz, SC-19; reserva con calendario, SC-20, y calendario al publicar horarios, SC-21; mapa limitado a Chile, defecto 35; detalle en el mapa, SC-22; buscador general, SC-23; dirección del profesional, SC-24), todas aprobadas. Al 21-10-2026: 241 en el backend y 233 en el frontend (defectos 27 y 29 del mapa), todas aprobadas. Con el asistente IA (FS-HU-07, 21-10-2026): 267 en el backend y 245 en el frontend, todas aprobadas. Con la recomendación de profesional (FS-HU-08) y la SC-26, 22-10-2026: 295 en el backend y 250 en el frontend, todas aprobadas.</t>
         </is>
       </c>
     </row>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
@@ -1549,7 +1549,7 @@
       <c r="I16" s="43" t="n"/>
       <c r="J16" s="43" t="inlineStr">
         <is>
-          <t>Planilla de Casos de Prueba: 80 casos (CP-001 a CP-080), 77 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 29 defectos: 26 corregidos y 3 abiertos (27 a 29, del mapa nuevo del PR #27). El 15-10-2026 se repitieron CP-076 y CP-077 con MapLibre (189/189 en el frontend); CP-078 sigue pendiente con el mapa nuevo. Comprobaciones con MySQL real: npm run test:mysql:agenda, 55/55 sobre main 662e79c el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema. 19-10-2026: CP-081 a CP-087 (mejoras de interfaz, SC-19), todos aprobados → 87 casos, 84 aprobados y 3 sin ejecutar (CP-024, CP-025 y CP-078); defectos 30 a 34 corregidos → 34 defectos: 31 corregidos y 3 abiertos (27 a 29). Evidencias en Plan de Pruebas/Mejoras_Interfaz_2026-10-19*. 19-10-2026 (SC-20, reserva con calendario): CP-088 a CP-091 aprobados → 91 casos, 88 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Flujo_Reservas_2026-10-19*. SC-21 (calendario al publicar horarios): CP-092 y CP-093 aprobados → 93 casos, 90 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Publicar_Horario_2026-10-19*. Defecto 35 (mapa que se veía de lejos por una ubicación fuera de Chile) corregido con CP-094 → 94 casos, 91 aprobados y 3 sin ejecutar; 35 defectos: 32 corregidos y 3 abiertos. Evidencias en Plan de Pruebas/Mapa_Chile_2026-10-19*. SC-22 (detalle del profesional en el mapa): CP-095 y CP-096 aprobados y defecto 28 corregido → 96 casos, 93 aprobados y 3 sin ejecutar; 35 defectos: 33 corregidos y 2 abiertos (27 y 29). Evidencias en Plan de Pruebas/Detalle_Mapa_2026-10-19*. SC-23 (buscador general del Inicio): CP-097 y CP-098 aprobados → 98 casos, 95 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Buscador_Inicio_2026-10-19*. SC-24 (dirección de atención y coordenadas en Chile en la ficha profesional): CP-099 y CP-100 aprobados → 100 casos, 97 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Direccion_Ficha_2026-10-19*. 21-10-2026: corregidos los defectos 27 y 29 del mapa (CP-101 y CP-102 aprobados) → 102 casos, 99 aprobados y 3 sin ejecutar; 35 defectos, todos corregidos. Evidencias en Plan de Pruebas/Defectos_Mapa_2026-10-21*. 21-10-2026: asistente IA (FS-HU-07, SC-25): CP-103 a CP-108 aprobados y CP-109 (respuesta real de Groq) pendiente de la clave → 109 casos, 105 aprobados y 4 sin ejecutar. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-21*. 22-10-2026: CP-109 aprobado con Groq real (modelo openai/gpt-oss-120b) y defecto 36 corregido → 109 casos, 106 aprobados y 3 sin ejecutar; 36 defectos, todos corregidos. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-22_groq_real*. 22-10-2026: FS-HU-08 (recomendación de profesional) y SC-26 (el SAMU solo en situaciones críticas): CP-110 a CP-114 aprobados → 114 casos, 111 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Recomendacion_Profesional_2026-10-22*.</t>
+          <t>Planilla de Casos de Prueba: 80 casos (CP-001 a CP-080), 77 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 29 defectos: 26 corregidos y 3 abiertos (27 a 29, del mapa nuevo del PR #27). El 15-10-2026 se repitieron CP-076 y CP-077 con MapLibre (189/189 en el frontend); CP-078 sigue pendiente con el mapa nuevo. Comprobaciones con MySQL real: npm run test:mysql:agenda, 55/55 sobre main 662e79c el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema. 19-10-2026: CP-081 a CP-087 (mejoras de interfaz, SC-19), todos aprobados → 87 casos, 84 aprobados y 3 sin ejecutar (CP-024, CP-025 y CP-078); defectos 30 a 34 corregidos → 34 defectos: 31 corregidos y 3 abiertos (27 a 29). Evidencias en Plan de Pruebas/Mejoras_Interfaz_2026-10-19*. 19-10-2026 (SC-20, reserva con calendario): CP-088 a CP-091 aprobados → 91 casos, 88 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Flujo_Reservas_2026-10-19*. SC-21 (calendario al publicar horarios): CP-092 y CP-093 aprobados → 93 casos, 90 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Publicar_Horario_2026-10-19*. Defecto 35 (mapa que se veía de lejos por una ubicación fuera de Chile) corregido con CP-094 → 94 casos, 91 aprobados y 3 sin ejecutar; 35 defectos: 32 corregidos y 3 abiertos. Evidencias en Plan de Pruebas/Mapa_Chile_2026-10-19*. SC-22 (detalle del profesional en el mapa): CP-095 y CP-096 aprobados y defecto 28 corregido → 96 casos, 93 aprobados y 3 sin ejecutar; 35 defectos: 33 corregidos y 2 abiertos (27 y 29). Evidencias en Plan de Pruebas/Detalle_Mapa_2026-10-19*. SC-23 (buscador general del Inicio): CP-097 y CP-098 aprobados → 98 casos, 95 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Buscador_Inicio_2026-10-19*. SC-24 (dirección de atención y coordenadas en Chile en la ficha profesional): CP-099 y CP-100 aprobados → 100 casos, 97 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Direccion_Ficha_2026-10-19*. 21-10-2026: corregidos los defectos 27 y 29 del mapa (CP-101 y CP-102 aprobados) → 102 casos, 99 aprobados y 3 sin ejecutar; 35 defectos, todos corregidos. Evidencias en Plan de Pruebas/Defectos_Mapa_2026-10-21*. 21-10-2026: asistente IA (FS-HU-07, SC-25): CP-103 a CP-108 aprobados y CP-109 (respuesta real de Groq) pendiente de la clave → 109 casos, 105 aprobados y 4 sin ejecutar. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-21*. 22-10-2026: CP-109 aprobado con Groq real (modelo openai/gpt-oss-120b) y defecto 36 corregido → 109 casos, 106 aprobados y 3 sin ejecutar; 36 defectos, todos corregidos. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-22_groq_real*. 22-10-2026: FS-HU-08 (recomendación de profesional) y SC-26 (el SAMU solo en situaciones críticas): CP-110 a CP-114 aprobados → 114 casos, 111 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Recomendacion_Profesional_2026-10-22*. 22-10-2026: SC-27 (lista y mapa juntos en Profesionales, FS-HU-06) y defecto 37 (mapa en una pestaña oculta): CP-115 a CP-120 aprobados → 120 casos, 117 aprobados y 3 sin ejecutar; 37 defectos, todos corregidos. Evidencias en Plan de Pruebas/Lista_y_Mapa_2026-10-22*.</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       <c r="I18" s="43" t="n"/>
       <c r="J18" s="43" t="inlineStr">
         <is>
-          <t>FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx. Al 15-10-2026 registra 18 solicitudes (SC-01 a SC-18): 17 aceptadas y 1 rechazada (Google Places en FS-HU-03). Las SC-12 a SC-17 cubren el flujo y el espacio del profesional, el clima en su Inicio, el menú del usuario, la elección del perfil en una pantalla propia, el panel del administrador con FS-HU-12 en el Sprint 3 el límite de una reserva activa por usuario con cada profesional y el cambio del mapa a MapLibre GL JS con OpenFreeMap (SC-18, PR #27). El 19-10-2026 se agregó la SC-19 (mejoras de respuesta y movimiento de la interfaz, con los defectos 30 a 34): 19 solicitudes, 18 aceptadas y 1 rechazada. Ese mismo día se agregó la SC-20 (reserva con calendario en FS-HU-14): 20 solicitudes, 19 aceptadas y 1 rechazada. Luego, la SC-21 (calendario al publicar horarios en FS-HU-13): 21 solicitudes, 20 aceptadas y 1 rechazada. Luego, la SC-22 (detalle del profesional en la ventana del mapa, FS-HU-06): 22 solicitudes, 21 aceptadas y 1 rechazada. Luego, la SC-23 (buscador general del Inicio, FS-HU-21): 23 solicitudes, 22 aceptadas y 1 rechazada. Luego, la SC-24 (dirección de atención del profesional, FS-HU-04 y FS-HU-06): 24 solicitudes, 23 aceptadas y 1 rechazada. Luego, la SC-25 (proveedor del asistente IA: Groq en vez de la API de Claude, FS-HU-07 y FS-HU-08): 25 solicitudes, 24 aceptadas y 1 rechazada. Luego, la SC-26 (el asistente nombra el SAMU solo en situaciones críticas, FS-HU-07): 26 solicitudes, 25 aceptadas y 1 rechazada. Se actualiza con cada cambio de alcance.</t>
+          <t>FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx. Al 15-10-2026 registra 18 solicitudes (SC-01 a SC-18): 17 aceptadas y 1 rechazada (Google Places en FS-HU-03). Las SC-12 a SC-17 cubren el flujo y el espacio del profesional, el clima en su Inicio, el menú del usuario, la elección del perfil en una pantalla propia, el panel del administrador con FS-HU-12 en el Sprint 3 el límite de una reserva activa por usuario con cada profesional y el cambio del mapa a MapLibre GL JS con OpenFreeMap (SC-18, PR #27). El 19-10-2026 se agregó la SC-19 (mejoras de respuesta y movimiento de la interfaz, con los defectos 30 a 34): 19 solicitudes, 18 aceptadas y 1 rechazada. Ese mismo día se agregó la SC-20 (reserva con calendario en FS-HU-14): 20 solicitudes, 19 aceptadas y 1 rechazada. Luego, la SC-21 (calendario al publicar horarios en FS-HU-13): 21 solicitudes, 20 aceptadas y 1 rechazada. Luego, la SC-22 (detalle del profesional en la ventana del mapa, FS-HU-06): 22 solicitudes, 21 aceptadas y 1 rechazada. Luego, la SC-23 (buscador general del Inicio, FS-HU-21): 23 solicitudes, 22 aceptadas y 1 rechazada. Luego, la SC-24 (dirección de atención del profesional, FS-HU-04 y FS-HU-06): 24 solicitudes, 23 aceptadas y 1 rechazada. Luego, la SC-25 (proveedor del asistente IA: Groq en vez de la API de Claude, FS-HU-07 y FS-HU-08): 25 solicitudes, 24 aceptadas y 1 rechazada. Luego, la SC-26 (el asistente nombra el SAMU solo en situaciones críticas, FS-HU-07): 26 solicitudes, 25 aceptadas y 1 rechazada. Luego, la SC-27 (lista y mapa juntos en Profesionales, FS-HU-06 y FS-HU-22): 27 solicitudes, 26 aceptadas y 1 rechazada. Se actualiza con cada cambio de alcance.</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       <c r="F5" s="43" t="n"/>
       <c r="G5" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.26: Vista Física como diagrama de despliegue UML (Ilustración 10) y Vista Lógica por capas.</t>
+          <t>DAS v1.27: Vista Física como diagrama de despliegue UML (Ilustración 10) y Vista Lógica por capas.</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1815,7 @@
       <c r="F6" s="43" t="n"/>
       <c r="G6" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.26, Vista Física: tabla de nodos y diagrama de despliegue UML (Nginx, Node.js/Express, MySQL 8, MapLibre GL JS con OpenFreeMap, Groq (API de IA), Google Identity Services y servidor SMTP).</t>
+          <t>DAS v1.27, Vista Física: tabla de nodos y diagrama de despliegue UML (Nginx, Node.js/Express, MySQL 8, MapLibre GL JS con OpenFreeMap, Groq (API de IA), Google Identity Services y servidor SMTP).</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       <c r="F7" s="43" t="n"/>
       <c r="G7" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.26, Vista Física: tabla de comunicación y rutas del diagrama de despliegue (HTTPS/REST/JSON, JWT, TCP 3306, proxy Nginx, verificación de Google y SMTP con TLS).</t>
+          <t>DAS v1.27, Vista Física: tabla de comunicación y rutas del diagrama de despliegue (HTTPS/REST/JSON, JWT, TCP 3306, proxy Nginx, verificación de Google y SMTP con TLS).</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       <c r="F8" s="43" t="n"/>
       <c r="G8" s="43" t="inlineStr">
         <is>
-          <t>Diagrama entidad-relación de las quince tablas implementadas al 21-10-2026 (Ilustración 4 del DAS v1.26, generado desde Diagramas (Miro)/Actualización Sprint 3); el modelo completo de dieciséis tablas está en el diccionario de datos.</t>
+          <t>Diagrama entidad-relación de las quince tablas implementadas al 21-10-2026 (Ilustración 4 del DAS v1.27, generado desde Diagramas (Miro)/Actualización Sprint 3); el modelo completo de dieciséis tablas está en el diccionario de datos.</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
       <c r="F9" s="43" t="n"/>
       <c r="G9" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.26, Vista Lógica &gt; Diccionario de datos: 16 tablas con tipos, PK, FK, restricciones e índices.</t>
+          <t>DAS v1.27, Vista Lógica &gt; Diccionario de datos: 16 tablas con tipos, PK, FK, restricciones e índices.</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       <c r="F10" s="43" t="n"/>
       <c r="G10" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.26, Ilustración 1 (casos de uso CU-01 a CU-09 con «include» y «extend», actualizada al 15-10-2026) y tabla de casos de uso.</t>
+          <t>DAS v1.27, Ilustración 1 (casos de uso CU-01 a CU-09 con «include» y «extend», actualizada al 15-10-2026) y tabla de casos de uso.</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
       <c r="F11" s="43" t="n"/>
       <c r="G11" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.26, Vista de Procesos: secuencias del registro de comida (Ilustración 5), de la elección del perfil y el asistente (Ilustración 6, en tres partes), de la reserva con reservas simultáneas (Ilustración 7) y de la recuperación de contraseña (Ilustración 8); flujos de la verificación administrativa (Ilustración 11) y de la disponibilidad y las reservas (Ilustración 12).</t>
+          <t>DAS v1.27, Vista de Procesos: secuencias del registro de comida (Ilustración 5), de la elección del perfil y el asistente (Ilustración 6, en tres partes), de la reserva con reservas simultáneas (Ilustración 7) y de la recuperación de contraseña (Ilustración 8); flujos de la verificación administrativa (Ilustración 11) y de la disponibilidad y las reservas (Ilustración 12).</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       <c r="F12" s="43" t="n"/>
       <c r="G12" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.26, Ilustración 13: diagrama UML de componentes e interfaces (13_Componentes_UML), fusionado el 12-10-2026 (PR #22); complementa la Vista de Desarrollo (Ilustración 9).</t>
+          <t>DAS v1.27, Ilustración 13: diagrama UML de componentes e interfaces (13_Componentes_UML), fusionado el 12-10-2026 (PR #22); complementa la Vista de Desarrollo (Ilustración 9).</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       <c r="F13" s="43" t="n"/>
       <c r="G13" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.26, Ilustración 2: asociaciones del modelo de clases del dominio (los atributos están en el diccionario de datos) y diagrama de estados de la reserva (Ilustración 3).</t>
+          <t>DAS v1.27, Ilustración 2: asociaciones del modelo de clases del dominio (los atributos están en el diccionario de datos) y diagrama de estados de la reserva (Ilustración 3).</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
       <c r="F22" s="43" t="n"/>
       <c r="G22" s="43" t="inlineStr">
         <is>
-          <t>Sprint 1: pruebas unitarias y de componentes con Jest (backend) y Vitest (frontend), todas aprobadas. Al 15-10-2026: 233 pruebas en el backend y 189 en el frontend, todas aprobadas. Al 19-10-2026: 241 en el backend y 231 en el frontend (mejoras de interfaz, SC-19; reserva con calendario, SC-20, y calendario al publicar horarios, SC-21; mapa limitado a Chile, defecto 35; detalle en el mapa, SC-22; buscador general, SC-23; dirección del profesional, SC-24), todas aprobadas. Al 21-10-2026: 241 en el backend y 233 en el frontend (defectos 27 y 29 del mapa), todas aprobadas. Con el asistente IA (FS-HU-07, 21-10-2026): 267 en el backend y 245 en el frontend, todas aprobadas. Con la recomendación de profesional (FS-HU-08) y la SC-26, 22-10-2026: 295 en el backend y 250 en el frontend, todas aprobadas.</t>
+          <t>Sprint 1: pruebas unitarias y de componentes con Jest (backend) y Vitest (frontend), todas aprobadas. Al 15-10-2026: 233 pruebas en el backend y 189 en el frontend, todas aprobadas. Al 19-10-2026: 241 en el backend y 231 en el frontend (mejoras de interfaz, SC-19; reserva con calendario, SC-20, y calendario al publicar horarios, SC-21; mapa limitado a Chile, defecto 35; detalle en el mapa, SC-22; buscador general, SC-23; dirección del profesional, SC-24), todas aprobadas. Al 21-10-2026: 241 en el backend y 233 en el frontend (defectos 27 y 29 del mapa), todas aprobadas. Con el asistente IA (FS-HU-07, 21-10-2026): 267 en el backend y 245 en el frontend, todas aprobadas. Con la recomendación de profesional (FS-HU-08) y la SC-26, 22-10-2026: 295 en el backend y 250 en el frontend, todas aprobadas. Con la lista y el mapa juntos (SC-27) y el defecto 37, 22-10-2026: 295 en el backend y 264 en el frontend, todas aprobadas.</t>
         </is>
       </c>
     </row>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
@@ -1549,7 +1549,7 @@
       <c r="I16" s="43" t="n"/>
       <c r="J16" s="43" t="inlineStr">
         <is>
-          <t>Planilla de Casos de Prueba: 80 casos (CP-001 a CP-080), 77 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 29 defectos: 26 corregidos y 3 abiertos (27 a 29, del mapa nuevo del PR #27). El 15-10-2026 se repitieron CP-076 y CP-077 con MapLibre (189/189 en el frontend); CP-078 sigue pendiente con el mapa nuevo. Comprobaciones con MySQL real: npm run test:mysql:agenda, 55/55 sobre main 662e79c el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema. 19-10-2026: CP-081 a CP-087 (mejoras de interfaz, SC-19), todos aprobados → 87 casos, 84 aprobados y 3 sin ejecutar (CP-024, CP-025 y CP-078); defectos 30 a 34 corregidos → 34 defectos: 31 corregidos y 3 abiertos (27 a 29). Evidencias en Plan de Pruebas/Mejoras_Interfaz_2026-10-19*. 19-10-2026 (SC-20, reserva con calendario): CP-088 a CP-091 aprobados → 91 casos, 88 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Flujo_Reservas_2026-10-19*. SC-21 (calendario al publicar horarios): CP-092 y CP-093 aprobados → 93 casos, 90 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Publicar_Horario_2026-10-19*. Defecto 35 (mapa que se veía de lejos por una ubicación fuera de Chile) corregido con CP-094 → 94 casos, 91 aprobados y 3 sin ejecutar; 35 defectos: 32 corregidos y 3 abiertos. Evidencias en Plan de Pruebas/Mapa_Chile_2026-10-19*. SC-22 (detalle del profesional en el mapa): CP-095 y CP-096 aprobados y defecto 28 corregido → 96 casos, 93 aprobados y 3 sin ejecutar; 35 defectos: 33 corregidos y 2 abiertos (27 y 29). Evidencias en Plan de Pruebas/Detalle_Mapa_2026-10-19*. SC-23 (buscador general del Inicio): CP-097 y CP-098 aprobados → 98 casos, 95 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Buscador_Inicio_2026-10-19*. SC-24 (dirección de atención y coordenadas en Chile en la ficha profesional): CP-099 y CP-100 aprobados → 100 casos, 97 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Direccion_Ficha_2026-10-19*. 21-10-2026: corregidos los defectos 27 y 29 del mapa (CP-101 y CP-102 aprobados) → 102 casos, 99 aprobados y 3 sin ejecutar; 35 defectos, todos corregidos. Evidencias en Plan de Pruebas/Defectos_Mapa_2026-10-21*. 21-10-2026: asistente IA (FS-HU-07, SC-25): CP-103 a CP-108 aprobados y CP-109 (respuesta real de Groq) pendiente de la clave → 109 casos, 105 aprobados y 4 sin ejecutar. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-21*. 22-10-2026: CP-109 aprobado con Groq real (modelo openai/gpt-oss-120b) y defecto 36 corregido → 109 casos, 106 aprobados y 3 sin ejecutar; 36 defectos, todos corregidos. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-22_groq_real*. 22-10-2026: FS-HU-08 (recomendación de profesional) y SC-26 (el SAMU solo en situaciones críticas): CP-110 a CP-114 aprobados → 114 casos, 111 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Recomendacion_Profesional_2026-10-22*. 22-10-2026: SC-27 (lista y mapa juntos en Profesionales, FS-HU-06) y defecto 37 (mapa en una pestaña oculta): CP-115 a CP-120 aprobados → 120 casos, 117 aprobados y 3 sin ejecutar; 37 defectos, todos corregidos. Evidencias en Plan de Pruebas/Lista_y_Mapa_2026-10-22*.</t>
+          <t>Planilla de Casos de Prueba: 80 casos (CP-001 a CP-080), 77 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 29 defectos: 26 corregidos y 3 abiertos (27 a 29, del mapa nuevo del PR #27). El 15-10-2026 se repitieron CP-076 y CP-077 con MapLibre (189/189 en el frontend); CP-078 sigue pendiente con el mapa nuevo. Comprobaciones con MySQL real: npm run test:mysql:agenda, 55/55 sobre main 662e79c el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema. 19-10-2026: CP-081 a CP-087 (mejoras de interfaz, SC-19), todos aprobados → 87 casos, 84 aprobados y 3 sin ejecutar (CP-024, CP-025 y CP-078); defectos 30 a 34 corregidos → 34 defectos: 31 corregidos y 3 abiertos (27 a 29). Evidencias en Plan de Pruebas/Mejoras_Interfaz_2026-10-19*. 19-10-2026 (SC-20, reserva con calendario): CP-088 a CP-091 aprobados → 91 casos, 88 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Flujo_Reservas_2026-10-19*. SC-21 (calendario al publicar horarios): CP-092 y CP-093 aprobados → 93 casos, 90 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Publicar_Horario_2026-10-19*. Defecto 35 (mapa que se veía de lejos por una ubicación fuera de Chile) corregido con CP-094 → 94 casos, 91 aprobados y 3 sin ejecutar; 35 defectos: 32 corregidos y 3 abiertos. Evidencias en Plan de Pruebas/Mapa_Chile_2026-10-19*. SC-22 (detalle del profesional en el mapa): CP-095 y CP-096 aprobados y defecto 28 corregido → 96 casos, 93 aprobados y 3 sin ejecutar; 35 defectos: 33 corregidos y 2 abiertos (27 y 29). Evidencias en Plan de Pruebas/Detalle_Mapa_2026-10-19*. SC-23 (buscador general del Inicio): CP-097 y CP-098 aprobados → 98 casos, 95 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Buscador_Inicio_2026-10-19*. SC-24 (dirección de atención y coordenadas en Chile en la ficha profesional): CP-099 y CP-100 aprobados → 100 casos, 97 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Direccion_Ficha_2026-10-19*. 21-10-2026: corregidos los defectos 27 y 29 del mapa (CP-101 y CP-102 aprobados) → 102 casos, 99 aprobados y 3 sin ejecutar; 35 defectos, todos corregidos. Evidencias en Plan de Pruebas/Defectos_Mapa_2026-10-21*. 21-10-2026: asistente IA (FS-HU-07, SC-25): CP-103 a CP-108 aprobados y CP-109 (respuesta real de Groq) pendiente de la clave → 109 casos, 105 aprobados y 4 sin ejecutar. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-21*. 22-10-2026: CP-109 aprobado con Groq real (modelo openai/gpt-oss-120b) y defecto 36 corregido → 109 casos, 106 aprobados y 3 sin ejecutar; 36 defectos, todos corregidos. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-22_groq_real*. 22-10-2026: FS-HU-08 (recomendación de profesional) y SC-26 (el SAMU solo en situaciones críticas): CP-110 a CP-114 aprobados → 114 casos, 111 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Recomendacion_Profesional_2026-10-22*. 22-10-2026: SC-27 (lista y mapa juntos en Profesionales, FS-HU-06) y defecto 37 (mapa en una pestaña oculta): CP-115 a CP-120 aprobados → 120 casos, 117 aprobados y 3 sin ejecutar; 37 defectos, todos corregidos. Evidencias en Plan de Pruebas/Lista_y_Mapa_2026-10-22*. 22-10-2026: defecto 38 (la red de seguridad del asistente no reconocía formas directas de riesgo suicida), encontrado en la revisión previa de los PR #28 a #30 y corregido en el PR #29: CP-121 aprobado → 121 casos, 118 aprobados y 3 sin ejecutar; 38 defectos, todos corregidos. 23-10-2026: defecto 39 (el límite diario del asistente se podía superar con mensajes simultáneos), informado por Nicolás Silva en la revisión del PR #29 y corregido en ese PR: CP-122 aprobado → 122 casos, 119 aprobados y 3 sin ejecutar; 39 defectos, todos corregidos.</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
       <c r="F22" s="43" t="n"/>
       <c r="G22" s="43" t="inlineStr">
         <is>
-          <t>Sprint 1: pruebas unitarias y de componentes con Jest (backend) y Vitest (frontend), todas aprobadas. Al 15-10-2026: 233 pruebas en el backend y 189 en el frontend, todas aprobadas. Al 19-10-2026: 241 en el backend y 231 en el frontend (mejoras de interfaz, SC-19; reserva con calendario, SC-20, y calendario al publicar horarios, SC-21; mapa limitado a Chile, defecto 35; detalle en el mapa, SC-22; buscador general, SC-23; dirección del profesional, SC-24), todas aprobadas. Al 21-10-2026: 241 en el backend y 233 en el frontend (defectos 27 y 29 del mapa), todas aprobadas. Con el asistente IA (FS-HU-07, 21-10-2026): 267 en el backend y 245 en el frontend, todas aprobadas. Con la recomendación de profesional (FS-HU-08) y la SC-26, 22-10-2026: 295 en el backend y 250 en el frontend, todas aprobadas. Con la lista y el mapa juntos (SC-27) y el defecto 37, 22-10-2026: 295 en el backend y 264 en el frontend, todas aprobadas.</t>
+          <t>Sprint 1: pruebas unitarias y de componentes con Jest (backend) y Vitest (frontend), todas aprobadas. Al 15-10-2026: 233 pruebas en el backend y 189 en el frontend, todas aprobadas. Al 19-10-2026: 241 en el backend y 231 en el frontend (mejoras de interfaz, SC-19; reserva con calendario, SC-20, y calendario al publicar horarios, SC-21; mapa limitado a Chile, defecto 35; detalle en el mapa, SC-22; buscador general, SC-23; dirección del profesional, SC-24), todas aprobadas. Al 21-10-2026: 241 en el backend y 233 en el frontend (defectos 27 y 29 del mapa), todas aprobadas. Con el asistente IA (FS-HU-07, 21-10-2026): 267 en el backend y 245 en el frontend, todas aprobadas. Con la recomendación de profesional (FS-HU-08) y la SC-26, 22-10-2026: 295 en el backend y 250 en el frontend, todas aprobadas. Con la lista y el mapa juntos (SC-27) y el defecto 37, 22-10-2026: 295 en el backend y 264 en el frontend, todas aprobadas. Con la corrección del defecto 38, 22-10-2026: 296 en el backend y 264 en el frontend, todas aprobadas. Con la corrección del defecto 39 (pruebas con mensajes simultáneos), 23-10-2026: 304 en el backend, todas aprobadas; el frontend no cambia.</t>
         </is>
       </c>
     </row>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
@@ -1549,7 +1549,7 @@
       <c r="I16" s="43" t="n"/>
       <c r="J16" s="43" t="inlineStr">
         <is>
-          <t>Planilla de Casos de Prueba: 80 casos (CP-001 a CP-080), 77 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 29 defectos: 26 corregidos y 3 abiertos (27 a 29, del mapa nuevo del PR #27). El 15-10-2026 se repitieron CP-076 y CP-077 con MapLibre (189/189 en el frontend); CP-078 sigue pendiente con el mapa nuevo. Comprobaciones con MySQL real: npm run test:mysql:agenda, 55/55 sobre main 662e79c el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema. 19-10-2026: CP-081 a CP-087 (mejoras de interfaz, SC-19), todos aprobados → 87 casos, 84 aprobados y 3 sin ejecutar (CP-024, CP-025 y CP-078); defectos 30 a 34 corregidos → 34 defectos: 31 corregidos y 3 abiertos (27 a 29). Evidencias en Plan de Pruebas/Mejoras_Interfaz_2026-10-19*. 19-10-2026 (SC-20, reserva con calendario): CP-088 a CP-091 aprobados → 91 casos, 88 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Flujo_Reservas_2026-10-19*. SC-21 (calendario al publicar horarios): CP-092 y CP-093 aprobados → 93 casos, 90 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Publicar_Horario_2026-10-19*. Defecto 35 (mapa que se veía de lejos por una ubicación fuera de Chile) corregido con CP-094 → 94 casos, 91 aprobados y 3 sin ejecutar; 35 defectos: 32 corregidos y 3 abiertos. Evidencias en Plan de Pruebas/Mapa_Chile_2026-10-19*. SC-22 (detalle del profesional en el mapa): CP-095 y CP-096 aprobados y defecto 28 corregido → 96 casos, 93 aprobados y 3 sin ejecutar; 35 defectos: 33 corregidos y 2 abiertos (27 y 29). Evidencias en Plan de Pruebas/Detalle_Mapa_2026-10-19*. SC-23 (buscador general del Inicio): CP-097 y CP-098 aprobados → 98 casos, 95 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Buscador_Inicio_2026-10-19*. SC-24 (dirección de atención y coordenadas en Chile en la ficha profesional): CP-099 y CP-100 aprobados → 100 casos, 97 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Direccion_Ficha_2026-10-19*. 21-10-2026: corregidos los defectos 27 y 29 del mapa (CP-101 y CP-102 aprobados) → 102 casos, 99 aprobados y 3 sin ejecutar; 35 defectos, todos corregidos. Evidencias en Plan de Pruebas/Defectos_Mapa_2026-10-21*. 21-10-2026: asistente IA (FS-HU-07, SC-25): CP-103 a CP-108 aprobados y CP-109 (respuesta real de Groq) pendiente de la clave → 109 casos, 105 aprobados y 4 sin ejecutar. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-21*. 22-10-2026: CP-109 aprobado con Groq real (modelo openai/gpt-oss-120b) y defecto 36 corregido → 109 casos, 106 aprobados y 3 sin ejecutar; 36 defectos, todos corregidos. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-22_groq_real*. 22-10-2026: FS-HU-08 (recomendación de profesional) y SC-26 (el SAMU solo en situaciones críticas): CP-110 a CP-114 aprobados → 114 casos, 111 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Recomendacion_Profesional_2026-10-22*. 22-10-2026: SC-27 (lista y mapa juntos en Profesionales, FS-HU-06) y defecto 37 (mapa en una pestaña oculta): CP-115 a CP-120 aprobados → 120 casos, 117 aprobados y 3 sin ejecutar; 37 defectos, todos corregidos. Evidencias en Plan de Pruebas/Lista_y_Mapa_2026-10-22*. 22-10-2026: defecto 38 (la red de seguridad del asistente no reconocía formas directas de riesgo suicida), encontrado en la revisión previa de los PR #28 a #30 y corregido en el PR #29: CP-121 aprobado → 121 casos, 118 aprobados y 3 sin ejecutar; 38 defectos, todos corregidos. 23-10-2026: defecto 39 (el límite diario del asistente se podía superar con mensajes simultáneos), informado por Nicolás Silva en la revisión del PR #29 y corregido en ese PR: CP-122 aprobado → 122 casos, 119 aprobados y 3 sin ejecutar; 39 defectos, todos corregidos.</t>
+          <t>Planilla de Casos de Prueba: 80 casos (CP-001 a CP-080), 77 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 29 defectos: 26 corregidos y 3 abiertos (27 a 29, del mapa nuevo del PR #27). El 15-10-2026 se repitieron CP-076 y CP-077 con MapLibre (189/189 en el frontend); CP-078 sigue pendiente con el mapa nuevo. Comprobaciones con MySQL real: npm run test:mysql:agenda, 55/55 sobre main 662e79c el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema. 19-10-2026: CP-081 a CP-087 (mejoras de interfaz, SC-19), todos aprobados → 87 casos, 84 aprobados y 3 sin ejecutar (CP-024, CP-025 y CP-078); defectos 30 a 34 corregidos → 34 defectos: 31 corregidos y 3 abiertos (27 a 29). Evidencias en Plan de Pruebas/Mejoras_Interfaz_2026-10-19*. 19-10-2026 (SC-20, reserva con calendario): CP-088 a CP-091 aprobados → 91 casos, 88 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Flujo_Reservas_2026-10-19*. SC-21 (calendario al publicar horarios): CP-092 y CP-093 aprobados → 93 casos, 90 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Publicar_Horario_2026-10-19*. Defecto 35 (mapa que se veía de lejos por una ubicación fuera de Chile) corregido con CP-094 → 94 casos, 91 aprobados y 3 sin ejecutar; 35 defectos: 32 corregidos y 3 abiertos. Evidencias en Plan de Pruebas/Mapa_Chile_2026-10-19*. SC-22 (detalle del profesional en el mapa): CP-095 y CP-096 aprobados y defecto 28 corregido → 96 casos, 93 aprobados y 3 sin ejecutar; 35 defectos: 33 corregidos y 2 abiertos (27 y 29). Evidencias en Plan de Pruebas/Detalle_Mapa_2026-10-19*. SC-23 (buscador general del Inicio): CP-097 y CP-098 aprobados → 98 casos, 95 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Buscador_Inicio_2026-10-19*. SC-24 (dirección de atención y coordenadas en Chile en la ficha profesional): CP-099 y CP-100 aprobados → 100 casos, 97 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Direccion_Ficha_2026-10-19*. 21-10-2026: corregidos los defectos 27 y 29 del mapa (CP-101 y CP-102 aprobados) → 102 casos, 99 aprobados y 3 sin ejecutar; 35 defectos, todos corregidos. Evidencias en Plan de Pruebas/Defectos_Mapa_2026-10-21*. 21-10-2026: asistente IA (FS-HU-07, SC-25): CP-103 a CP-108 aprobados y CP-109 (respuesta real de Groq) pendiente de la clave → 109 casos, 105 aprobados y 4 sin ejecutar. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-21*. 22-10-2026: CP-109 aprobado con Groq real (modelo openai/gpt-oss-120b) y defecto 36 corregido → 109 casos, 106 aprobados y 3 sin ejecutar; 36 defectos, todos corregidos. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-22_groq_real*. 22-10-2026: FS-HU-08 (recomendación de profesional) y SC-26 (el SAMU solo en situaciones críticas): CP-110 a CP-114 aprobados → 114 casos, 111 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Recomendacion_Profesional_2026-10-22*. 22-10-2026: SC-27 (lista y mapa juntos en Profesionales, FS-HU-06) y defecto 37 (mapa en una pestaña oculta): CP-115 a CP-120 aprobados → 120 casos, 117 aprobados y 3 sin ejecutar; 37 defectos, todos corregidos. Evidencias en Plan de Pruebas/Lista_y_Mapa_2026-10-22*. 22-10-2026: defecto 38 (la red de seguridad del asistente no reconocía formas directas de riesgo suicida), encontrado en la revisión previa de los PR #28 a #30 y corregido en el PR #29: CP-121 aprobado → 121 casos, 118 aprobados y 3 sin ejecutar; 38 defectos, todos corregidos. 23-10-2026: defecto 39 (el límite diario del asistente se podía superar con mensajes simultáneos), informado por Luis Méndez en la revisión del PR #29 y corregido en ese PR: CP-122 aprobado → 122 casos, 119 aprobados y 3 sin ejecutar; 39 defectos, todos corregidos. Luis Méndez agregó la comprobación con MySQL real npm run test:mysql:asistente (23 condiciones aprobadas; Plan de Pruebas/Asistente_Cupo_MySQL*). PR #29 y #30 fusionados en main el 23-10-2026.</t>
         </is>
       </c>
     </row>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
@@ -1549,7 +1549,7 @@
       <c r="I16" s="43" t="n"/>
       <c r="J16" s="43" t="inlineStr">
         <is>
-          <t>Planilla de Casos de Prueba: 80 casos (CP-001 a CP-080), 77 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 29 defectos: 26 corregidos y 3 abiertos (27 a 29, del mapa nuevo del PR #27). El 15-10-2026 se repitieron CP-076 y CP-077 con MapLibre (189/189 en el frontend); CP-078 sigue pendiente con el mapa nuevo. Comprobaciones con MySQL real: npm run test:mysql:agenda, 55/55 sobre main 662e79c el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema. 19-10-2026: CP-081 a CP-087 (mejoras de interfaz, SC-19), todos aprobados → 87 casos, 84 aprobados y 3 sin ejecutar (CP-024, CP-025 y CP-078); defectos 30 a 34 corregidos → 34 defectos: 31 corregidos y 3 abiertos (27 a 29). Evidencias en Plan de Pruebas/Mejoras_Interfaz_2026-10-19*. 19-10-2026 (SC-20, reserva con calendario): CP-088 a CP-091 aprobados → 91 casos, 88 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Flujo_Reservas_2026-10-19*. SC-21 (calendario al publicar horarios): CP-092 y CP-093 aprobados → 93 casos, 90 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Publicar_Horario_2026-10-19*. Defecto 35 (mapa que se veía de lejos por una ubicación fuera de Chile) corregido con CP-094 → 94 casos, 91 aprobados y 3 sin ejecutar; 35 defectos: 32 corregidos y 3 abiertos. Evidencias en Plan de Pruebas/Mapa_Chile_2026-10-19*. SC-22 (detalle del profesional en el mapa): CP-095 y CP-096 aprobados y defecto 28 corregido → 96 casos, 93 aprobados y 3 sin ejecutar; 35 defectos: 33 corregidos y 2 abiertos (27 y 29). Evidencias en Plan de Pruebas/Detalle_Mapa_2026-10-19*. SC-23 (buscador general del Inicio): CP-097 y CP-098 aprobados → 98 casos, 95 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Buscador_Inicio_2026-10-19*. SC-24 (dirección de atención y coordenadas en Chile en la ficha profesional): CP-099 y CP-100 aprobados → 100 casos, 97 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Direccion_Ficha_2026-10-19*. 21-10-2026: corregidos los defectos 27 y 29 del mapa (CP-101 y CP-102 aprobados) → 102 casos, 99 aprobados y 3 sin ejecutar; 35 defectos, todos corregidos. Evidencias en Plan de Pruebas/Defectos_Mapa_2026-10-21*. 21-10-2026: asistente IA (FS-HU-07, SC-25): CP-103 a CP-108 aprobados y CP-109 (respuesta real de Groq) pendiente de la clave → 109 casos, 105 aprobados y 4 sin ejecutar. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-21*. 22-10-2026: CP-109 aprobado con Groq real (modelo openai/gpt-oss-120b) y defecto 36 corregido → 109 casos, 106 aprobados y 3 sin ejecutar; 36 defectos, todos corregidos. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-22_groq_real*. 22-10-2026: FS-HU-08 (recomendación de profesional) y SC-26 (el SAMU solo en situaciones críticas): CP-110 a CP-114 aprobados → 114 casos, 111 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Recomendacion_Profesional_2026-10-22*. 22-10-2026: SC-27 (lista y mapa juntos en Profesionales, FS-HU-06) y defecto 37 (mapa en una pestaña oculta): CP-115 a CP-120 aprobados → 120 casos, 117 aprobados y 3 sin ejecutar; 37 defectos, todos corregidos. Evidencias en Plan de Pruebas/Lista_y_Mapa_2026-10-22*. 22-10-2026: defecto 38 (la red de seguridad del asistente no reconocía formas directas de riesgo suicida), encontrado en la revisión previa de los PR #28 a #30 y corregido en el PR #29: CP-121 aprobado → 121 casos, 118 aprobados y 3 sin ejecutar; 38 defectos, todos corregidos. 23-10-2026: defecto 39 (el límite diario del asistente se podía superar con mensajes simultáneos), informado por Luis Méndez en la revisión del PR #29 y corregido en ese PR: CP-122 aprobado → 122 casos, 119 aprobados y 3 sin ejecutar; 39 defectos, todos corregidos. Luis Méndez agregó la comprobación con MySQL real npm run test:mysql:asistente (23 condiciones aprobadas; Plan de Pruebas/Asistente_Cupo_MySQL*). PR #29 y #30 fusionados en main el 23-10-2026.</t>
+          <t>Planilla de Casos de Prueba: 80 casos (CP-001 a CP-080), 77 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 29 defectos: 26 corregidos y 3 abiertos (27 a 29, del mapa nuevo del PR #27). El 15-10-2026 se repitieron CP-076 y CP-077 con MapLibre (189/189 en el frontend); CP-078 sigue pendiente con el mapa nuevo. Comprobaciones con MySQL real: npm run test:mysql:agenda, 55/55 sobre main 662e79c el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema. 19-10-2026: CP-081 a CP-087 (mejoras de interfaz, SC-19), todos aprobados → 87 casos, 84 aprobados y 3 sin ejecutar (CP-024, CP-025 y CP-078); defectos 30 a 34 corregidos → 34 defectos: 31 corregidos y 3 abiertos (27 a 29). Evidencias en Plan de Pruebas/Mejoras_Interfaz_2026-10-19*. 19-10-2026 (SC-20, reserva con calendario): CP-088 a CP-091 aprobados → 91 casos, 88 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Flujo_Reservas_2026-10-19*. SC-21 (calendario al publicar horarios): CP-092 y CP-093 aprobados → 93 casos, 90 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Publicar_Horario_2026-10-19*. Defecto 35 (mapa que se veía de lejos por una ubicación fuera de Chile) corregido con CP-094 → 94 casos, 91 aprobados y 3 sin ejecutar; 35 defectos: 32 corregidos y 3 abiertos. Evidencias en Plan de Pruebas/Mapa_Chile_2026-10-19*. SC-22 (detalle del profesional en el mapa): CP-095 y CP-096 aprobados y defecto 28 corregido → 96 casos, 93 aprobados y 3 sin ejecutar; 35 defectos: 33 corregidos y 2 abiertos (27 y 29). Evidencias en Plan de Pruebas/Detalle_Mapa_2026-10-19*. SC-23 (buscador general del Inicio): CP-097 y CP-098 aprobados → 98 casos, 95 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Buscador_Inicio_2026-10-19*. SC-24 (dirección de atención y coordenadas en Chile en la ficha profesional): CP-099 y CP-100 aprobados → 100 casos, 97 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Direccion_Ficha_2026-10-19*. 21-10-2026: corregidos los defectos 27 y 29 del mapa (CP-101 y CP-102 aprobados) → 102 casos, 99 aprobados y 3 sin ejecutar; 35 defectos, todos corregidos. Evidencias en Plan de Pruebas/Defectos_Mapa_2026-10-21*. 21-10-2026: asistente IA (FS-HU-07, SC-25): CP-103 a CP-108 aprobados y CP-109 (respuesta real de Groq) pendiente de la clave → 109 casos, 105 aprobados y 4 sin ejecutar. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-21*. 22-10-2026: CP-109 aprobado con Groq real (modelo openai/gpt-oss-120b) y defecto 36 corregido → 109 casos, 106 aprobados y 3 sin ejecutar; 36 defectos, todos corregidos. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-22_groq_real*. 22-10-2026: FS-HU-08 (recomendación de profesional) y SC-26 (el SAMU solo en situaciones críticas): CP-110 a CP-114 aprobados → 114 casos, 111 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Recomendacion_Profesional_2026-10-22*. 22-10-2026: SC-27 (lista y mapa juntos en Profesionales, FS-HU-06) y defecto 37 (mapa en una pestaña oculta): CP-115 a CP-120 aprobados → 120 casos, 117 aprobados y 3 sin ejecutar; 37 defectos, todos corregidos. Evidencias en Plan de Pruebas/Lista_y_Mapa_2026-10-22*. 22-10-2026: defecto 38 (la red de seguridad del asistente no reconocía formas directas de riesgo suicida), encontrado en la revisión previa de los PR #28 a #30 y corregido en el PR #29: CP-121 aprobado → 121 casos, 118 aprobados y 3 sin ejecutar; 38 defectos, todos corregidos. 23-10-2026: defecto 39 (el límite diario del asistente se podía superar con mensajes simultáneos), informado por Luis Méndez en la revisión del PR #29 y corregido en ese PR: CP-122 aprobado → 122 casos, 119 aprobados y 3 sin ejecutar; 39 defectos, todos corregidos. Luis Méndez agregó la comprobación con MySQL real npm run test:mysql:asistente (23 condiciones aprobadas; Plan de Pruebas/Asistente_Cupo_MySQL*). PR #29 y #30 fusionados en main el 23-10-2026. 24-10-2026: CP-078 aprobado sobre main con el mapa real (FS-HU-06; evidencia Plan de Pruebas/Mapa_Real_CP078_2026-10-24*) → 122 casos, 120 aprobados y 2 sin ejecutar (CP-024 y CP-025, acceso con Google).</t>
         </is>
       </c>
     </row>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
@@ -1549,7 +1549,7 @@
       <c r="I16" s="43" t="n"/>
       <c r="J16" s="43" t="inlineStr">
         <is>
-          <t>Planilla de Casos de Prueba: 80 casos (CP-001 a CP-080), 77 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 29 defectos: 26 corregidos y 3 abiertos (27 a 29, del mapa nuevo del PR #27). El 15-10-2026 se repitieron CP-076 y CP-077 con MapLibre (189/189 en el frontend); CP-078 sigue pendiente con el mapa nuevo. Comprobaciones con MySQL real: npm run test:mysql:agenda, 55/55 sobre main 662e79c el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema. 19-10-2026: CP-081 a CP-087 (mejoras de interfaz, SC-19), todos aprobados → 87 casos, 84 aprobados y 3 sin ejecutar (CP-024, CP-025 y CP-078); defectos 30 a 34 corregidos → 34 defectos: 31 corregidos y 3 abiertos (27 a 29). Evidencias en Plan de Pruebas/Mejoras_Interfaz_2026-10-19*. 19-10-2026 (SC-20, reserva con calendario): CP-088 a CP-091 aprobados → 91 casos, 88 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Flujo_Reservas_2026-10-19*. SC-21 (calendario al publicar horarios): CP-092 y CP-093 aprobados → 93 casos, 90 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Publicar_Horario_2026-10-19*. Defecto 35 (mapa que se veía de lejos por una ubicación fuera de Chile) corregido con CP-094 → 94 casos, 91 aprobados y 3 sin ejecutar; 35 defectos: 32 corregidos y 3 abiertos. Evidencias en Plan de Pruebas/Mapa_Chile_2026-10-19*. SC-22 (detalle del profesional en el mapa): CP-095 y CP-096 aprobados y defecto 28 corregido → 96 casos, 93 aprobados y 3 sin ejecutar; 35 defectos: 33 corregidos y 2 abiertos (27 y 29). Evidencias en Plan de Pruebas/Detalle_Mapa_2026-10-19*. SC-23 (buscador general del Inicio): CP-097 y CP-098 aprobados → 98 casos, 95 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Buscador_Inicio_2026-10-19*. SC-24 (dirección de atención y coordenadas en Chile en la ficha profesional): CP-099 y CP-100 aprobados → 100 casos, 97 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Direccion_Ficha_2026-10-19*. 21-10-2026: corregidos los defectos 27 y 29 del mapa (CP-101 y CP-102 aprobados) → 102 casos, 99 aprobados y 3 sin ejecutar; 35 defectos, todos corregidos. Evidencias en Plan de Pruebas/Defectos_Mapa_2026-10-21*. 21-10-2026: asistente IA (FS-HU-07, SC-25): CP-103 a CP-108 aprobados y CP-109 (respuesta real de Groq) pendiente de la clave → 109 casos, 105 aprobados y 4 sin ejecutar. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-21*. 22-10-2026: CP-109 aprobado con Groq real (modelo openai/gpt-oss-120b) y defecto 36 corregido → 109 casos, 106 aprobados y 3 sin ejecutar; 36 defectos, todos corregidos. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-22_groq_real*. 22-10-2026: FS-HU-08 (recomendación de profesional) y SC-26 (el SAMU solo en situaciones críticas): CP-110 a CP-114 aprobados → 114 casos, 111 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Recomendacion_Profesional_2026-10-22*. 22-10-2026: SC-27 (lista y mapa juntos en Profesionales, FS-HU-06) y defecto 37 (mapa en una pestaña oculta): CP-115 a CP-120 aprobados → 120 casos, 117 aprobados y 3 sin ejecutar; 37 defectos, todos corregidos. Evidencias en Plan de Pruebas/Lista_y_Mapa_2026-10-22*. 22-10-2026: defecto 38 (la red de seguridad del asistente no reconocía formas directas de riesgo suicida), encontrado en la revisión previa de los PR #28 a #30 y corregido en el PR #29: CP-121 aprobado → 121 casos, 118 aprobados y 3 sin ejecutar; 38 defectos, todos corregidos. 23-10-2026: defecto 39 (el límite diario del asistente se podía superar con mensajes simultáneos), informado por Luis Méndez en la revisión del PR #29 y corregido en ese PR: CP-122 aprobado → 122 casos, 119 aprobados y 3 sin ejecutar; 39 defectos, todos corregidos. Luis Méndez agregó la comprobación con MySQL real npm run test:mysql:asistente (23 condiciones aprobadas; Plan de Pruebas/Asistente_Cupo_MySQL*). PR #29 y #30 fusionados en main el 23-10-2026. 24-10-2026: CP-078 aprobado sobre main con el mapa real (FS-HU-06; evidencia Plan de Pruebas/Mapa_Real_CP078_2026-10-24*) → 122 casos, 120 aprobados y 2 sin ejecutar (CP-024 y CP-025, acceso con Google).</t>
+          <t>Planilla de Casos de Prueba: 80 casos (CP-001 a CP-080), 77 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 29 defectos: 26 corregidos y 3 abiertos (27 a 29, del mapa nuevo del PR #27). El 15-10-2026 se repitieron CP-076 y CP-077 con MapLibre (189/189 en el frontend); CP-078 sigue pendiente con el mapa nuevo. Comprobaciones con MySQL real: npm run test:mysql:agenda, 55/55 sobre main 662e79c el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema. 19-10-2026: CP-081 a CP-087 (mejoras de interfaz, SC-19), todos aprobados → 87 casos, 84 aprobados y 3 sin ejecutar (CP-024, CP-025 y CP-078); defectos 30 a 34 corregidos → 34 defectos: 31 corregidos y 3 abiertos (27 a 29). Evidencias en Plan de Pruebas/Mejoras_Interfaz_2026-10-19*. 19-10-2026 (SC-20, reserva con calendario): CP-088 a CP-091 aprobados → 91 casos, 88 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Flujo_Reservas_2026-10-19*. SC-21 (calendario al publicar horarios): CP-092 y CP-093 aprobados → 93 casos, 90 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Publicar_Horario_2026-10-19*. Defecto 35 (mapa que se veía de lejos por una ubicación fuera de Chile) corregido con CP-094 → 94 casos, 91 aprobados y 3 sin ejecutar; 35 defectos: 32 corregidos y 3 abiertos. Evidencias en Plan de Pruebas/Mapa_Chile_2026-10-19*. SC-22 (detalle del profesional en el mapa): CP-095 y CP-096 aprobados y defecto 28 corregido → 96 casos, 93 aprobados y 3 sin ejecutar; 35 defectos: 33 corregidos y 2 abiertos (27 y 29). Evidencias en Plan de Pruebas/Detalle_Mapa_2026-10-19*. SC-23 (buscador general del Inicio): CP-097 y CP-098 aprobados → 98 casos, 95 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Buscador_Inicio_2026-10-19*. SC-24 (dirección de atención y coordenadas en Chile en la ficha profesional): CP-099 y CP-100 aprobados → 100 casos, 97 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Direccion_Ficha_2026-10-19*. 21-10-2026: corregidos los defectos 27 y 29 del mapa (CP-101 y CP-102 aprobados) → 102 casos, 99 aprobados y 3 sin ejecutar; 35 defectos, todos corregidos. Evidencias en Plan de Pruebas/Defectos_Mapa_2026-10-21*. 21-10-2026: asistente IA (FS-HU-07, SC-25): CP-103 a CP-108 aprobados y CP-109 (respuesta real de Groq) pendiente de la clave → 109 casos, 105 aprobados y 4 sin ejecutar. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-21*. 22-10-2026: CP-109 aprobado con Groq real (modelo openai/gpt-oss-120b) y defecto 36 corregido → 109 casos, 106 aprobados y 3 sin ejecutar; 36 defectos, todos corregidos. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-22_groq_real*. 22-10-2026: FS-HU-08 (recomendación de profesional) y SC-26 (el SAMU solo en situaciones críticas): CP-110 a CP-114 aprobados → 114 casos, 111 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Recomendacion_Profesional_2026-10-22*. 22-10-2026: SC-27 (lista y mapa juntos en Profesionales, FS-HU-06) y defecto 37 (mapa en una pestaña oculta): CP-115 a CP-120 aprobados → 120 casos, 117 aprobados y 3 sin ejecutar; 37 defectos, todos corregidos. Evidencias en Plan de Pruebas/Lista_y_Mapa_2026-10-22*. 22-10-2026: defecto 38 (la red de seguridad del asistente no reconocía formas directas de riesgo suicida), encontrado en la revisión previa de los PR #28 a #30 y corregido en el PR #29: CP-121 aprobado → 121 casos, 118 aprobados y 3 sin ejecutar; 38 defectos, todos corregidos. 23-10-2026: defecto 39 (el límite diario del asistente se podía superar con mensajes simultáneos), informado por Luis Méndez en la revisión del PR #29 y corregido en ese PR: CP-122 aprobado → 122 casos, 119 aprobados y 3 sin ejecutar; 39 defectos, todos corregidos. Luis Méndez agregó la comprobación con MySQL real npm run test:mysql:asistente (23 condiciones aprobadas; Plan de Pruebas/Asistente_Cupo_MySQL*). PR #29 y #30 fusionados en main el 23-10-2026. 24-10-2026: CP-078 aprobado sobre main con el mapa real (FS-HU-06; evidencia Plan de Pruebas/Mapa_Real_CP078_2026-10-24*) → 122 casos, 120 aprobados y 2 sin ejecutar (CP-024 y CP-025, acceso con Google). 24-10-2026: SC-28 (la ficha profesional se ubica con la comuna y la dirección, sin escribir coordenadas, FS-HU-04): CP-123 a CP-125 aprobados → 125 casos, 123 aprobados y 2 sin ejecutar (CP-024 y CP-025); 39 defectos, todos corregidos. Evidencias en Plan de Pruebas/Ubicacion_Direccion_2026-10-24*.</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       <c r="I18" s="43" t="n"/>
       <c r="J18" s="43" t="inlineStr">
         <is>
-          <t>FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx. Al 15-10-2026 registra 18 solicitudes (SC-01 a SC-18): 17 aceptadas y 1 rechazada (Google Places en FS-HU-03). Las SC-12 a SC-17 cubren el flujo y el espacio del profesional, el clima en su Inicio, el menú del usuario, la elección del perfil en una pantalla propia, el panel del administrador con FS-HU-12 en el Sprint 3 el límite de una reserva activa por usuario con cada profesional y el cambio del mapa a MapLibre GL JS con OpenFreeMap (SC-18, PR #27). El 19-10-2026 se agregó la SC-19 (mejoras de respuesta y movimiento de la interfaz, con los defectos 30 a 34): 19 solicitudes, 18 aceptadas y 1 rechazada. Ese mismo día se agregó la SC-20 (reserva con calendario en FS-HU-14): 20 solicitudes, 19 aceptadas y 1 rechazada. Luego, la SC-21 (calendario al publicar horarios en FS-HU-13): 21 solicitudes, 20 aceptadas y 1 rechazada. Luego, la SC-22 (detalle del profesional en la ventana del mapa, FS-HU-06): 22 solicitudes, 21 aceptadas y 1 rechazada. Luego, la SC-23 (buscador general del Inicio, FS-HU-21): 23 solicitudes, 22 aceptadas y 1 rechazada. Luego, la SC-24 (dirección de atención del profesional, FS-HU-04 y FS-HU-06): 24 solicitudes, 23 aceptadas y 1 rechazada. Luego, la SC-25 (proveedor del asistente IA: Groq en vez de la API de Claude, FS-HU-07 y FS-HU-08): 25 solicitudes, 24 aceptadas y 1 rechazada. Luego, la SC-26 (el asistente nombra el SAMU solo en situaciones críticas, FS-HU-07): 26 solicitudes, 25 aceptadas y 1 rechazada. Luego, la SC-27 (lista y mapa juntos en Profesionales, FS-HU-06 y FS-HU-22): 27 solicitudes, 26 aceptadas y 1 rechazada. Se actualiza con cada cambio de alcance.</t>
+          <t>FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/Matriz_Control_de_Cambio_FitSearch.xlsx. Al 15-10-2026 registra 18 solicitudes (SC-01 a SC-18): 17 aceptadas y 1 rechazada (Google Places en FS-HU-03). Las SC-12 a SC-17 cubren el flujo y el espacio del profesional, el clima en su Inicio, el menú del usuario, la elección del perfil en una pantalla propia, el panel del administrador con FS-HU-12 en el Sprint 3 el límite de una reserva activa por usuario con cada profesional y el cambio del mapa a MapLibre GL JS con OpenFreeMap (SC-18, PR #27). El 19-10-2026 se agregó la SC-19 (mejoras de respuesta y movimiento de la interfaz, con los defectos 30 a 34): 19 solicitudes, 18 aceptadas y 1 rechazada. Ese mismo día se agregó la SC-20 (reserva con calendario en FS-HU-14): 20 solicitudes, 19 aceptadas y 1 rechazada. Luego, la SC-21 (calendario al publicar horarios en FS-HU-13): 21 solicitudes, 20 aceptadas y 1 rechazada. Luego, la SC-22 (detalle del profesional en la ventana del mapa, FS-HU-06): 22 solicitudes, 21 aceptadas y 1 rechazada. Luego, la SC-23 (buscador general del Inicio, FS-HU-21): 23 solicitudes, 22 aceptadas y 1 rechazada. Luego, la SC-24 (dirección de atención del profesional, FS-HU-04 y FS-HU-06): 24 solicitudes, 23 aceptadas y 1 rechazada. Luego, la SC-25 (proveedor del asistente IA: Groq en vez de la API de Claude, FS-HU-07 y FS-HU-08): 25 solicitudes, 24 aceptadas y 1 rechazada. Luego, la SC-26 (el asistente nombra el SAMU solo en situaciones críticas, FS-HU-07): 26 solicitudes, 25 aceptadas y 1 rechazada. Luego, la SC-27 (lista y mapa juntos en Profesionales, FS-HU-06 y FS-HU-22): 27 solicitudes, 26 aceptadas y 1 rechazada. Luego, la SC-28 (ubicación de la ficha profesional por dirección, sin coordenadas, FS-HU-04): 28 solicitudes, 27 aceptadas y 1 rechazada. Se actualiza con cada cambio de alcance.</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       <c r="F5" s="43" t="n"/>
       <c r="G5" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.27: Vista Física como diagrama de despliegue UML (Ilustración 10) y Vista Lógica por capas.</t>
+          <t>DAS v1.28: Vista Física como diagrama de despliegue UML (Ilustración 10) y Vista Lógica por capas.</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1815,7 @@
       <c r="F6" s="43" t="n"/>
       <c r="G6" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.27, Vista Física: tabla de nodos y diagrama de despliegue UML (Nginx, Node.js/Express, MySQL 8, MapLibre GL JS con OpenFreeMap, Groq (API de IA), Google Identity Services y servidor SMTP).</t>
+          <t>DAS v1.28, Vista Física: tabla de nodos y diagrama de despliegue UML (Nginx, Node.js/Express, MySQL 8, MapLibre GL JS con OpenFreeMap, Nominatim (búsqueda de direcciones), Groq (API de IA), Google Identity Services y servidor SMTP).</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       <c r="F7" s="43" t="n"/>
       <c r="G7" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.27, Vista Física: tabla de comunicación y rutas del diagrama de despliegue (HTTPS/REST/JSON, JWT, TCP 3306, proxy Nginx, verificación de Google y SMTP con TLS).</t>
+          <t>DAS v1.28, Vista Física: tabla de comunicación y rutas del diagrama de despliegue (HTTPS/REST/JSON, JWT, TCP 3306, proxy Nginx, verificación de Google y SMTP con TLS).</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       <c r="F8" s="43" t="n"/>
       <c r="G8" s="43" t="inlineStr">
         <is>
-          <t>Diagrama entidad-relación de las quince tablas implementadas al 21-10-2026 (Ilustración 4 del DAS v1.27, generado desde Diagramas (Miro)/Actualización Sprint 3); el modelo completo de dieciséis tablas está en el diccionario de datos.</t>
+          <t>Diagrama entidad-relación de las quince tablas implementadas al 21-10-2026 (Ilustración 4 del DAS v1.28, generado desde Diagramas (Miro)/Actualización Sprint 3); el modelo completo de dieciséis tablas está en el diccionario de datos.</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
       <c r="F9" s="43" t="n"/>
       <c r="G9" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.27, Vista Lógica &gt; Diccionario de datos: 16 tablas con tipos, PK, FK, restricciones e índices.</t>
+          <t>DAS v1.28, Vista Lógica &gt; Diccionario de datos: 16 tablas con tipos, PK, FK, restricciones e índices.</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       <c r="F10" s="43" t="n"/>
       <c r="G10" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.27, Ilustración 1 (casos de uso CU-01 a CU-09 con «include» y «extend», actualizada al 15-10-2026) y tabla de casos de uso.</t>
+          <t>DAS v1.28, Ilustración 1 (casos de uso CU-01 a CU-09 con «include» y «extend», actualizada al 15-10-2026) y tabla de casos de uso.</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
       <c r="F11" s="43" t="n"/>
       <c r="G11" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.27, Vista de Procesos: secuencias del registro de comida (Ilustración 5), de la elección del perfil y el asistente (Ilustración 6, en tres partes), de la reserva con reservas simultáneas (Ilustración 7) y de la recuperación de contraseña (Ilustración 8); flujos de la verificación administrativa (Ilustración 11) y de la disponibilidad y las reservas (Ilustración 12).</t>
+          <t>DAS v1.28, Vista de Procesos: secuencias del registro de comida (Ilustración 5), de la elección del perfil y el asistente (Ilustración 6, en tres partes), de la reserva con reservas simultáneas (Ilustración 7) y de la recuperación de contraseña (Ilustración 8); flujos de la verificación administrativa (Ilustración 11) y de la disponibilidad y las reservas (Ilustración 12).</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       <c r="F12" s="43" t="n"/>
       <c r="G12" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.27, Ilustración 13: diagrama UML de componentes e interfaces (13_Componentes_UML), fusionado el 12-10-2026 (PR #22); complementa la Vista de Desarrollo (Ilustración 9).</t>
+          <t>DAS v1.28, Ilustración 13: diagrama UML de componentes e interfaces (13_Componentes_UML), fusionado el 12-10-2026 (PR #22); complementa la Vista de Desarrollo (Ilustración 9).</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       <c r="F13" s="43" t="n"/>
       <c r="G13" s="43" t="inlineStr">
         <is>
-          <t>DAS v1.27, Ilustración 2: asociaciones del modelo de clases del dominio (los atributos están en el diccionario de datos) y diagrama de estados de la reserva (Ilustración 3).</t>
+          <t>DAS v1.28, Ilustración 2: asociaciones del modelo de clases del dominio (los atributos están en el diccionario de datos) y diagrama de estados de la reserva (Ilustración 3).</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
       <c r="F22" s="43" t="n"/>
       <c r="G22" s="43" t="inlineStr">
         <is>
-          <t>Sprint 1: pruebas unitarias y de componentes con Jest (backend) y Vitest (frontend), todas aprobadas. Al 15-10-2026: 233 pruebas en el backend y 189 en el frontend, todas aprobadas. Al 19-10-2026: 241 en el backend y 231 en el frontend (mejoras de interfaz, SC-19; reserva con calendario, SC-20, y calendario al publicar horarios, SC-21; mapa limitado a Chile, defecto 35; detalle en el mapa, SC-22; buscador general, SC-23; dirección del profesional, SC-24), todas aprobadas. Al 21-10-2026: 241 en el backend y 233 en el frontend (defectos 27 y 29 del mapa), todas aprobadas. Con el asistente IA (FS-HU-07, 21-10-2026): 267 en el backend y 245 en el frontend, todas aprobadas. Con la recomendación de profesional (FS-HU-08) y la SC-26, 22-10-2026: 295 en el backend y 250 en el frontend, todas aprobadas. Con la lista y el mapa juntos (SC-27) y el defecto 37, 22-10-2026: 295 en el backend y 264 en el frontend, todas aprobadas. Con la corrección del defecto 38, 22-10-2026: 296 en el backend y 264 en el frontend, todas aprobadas. Con la corrección del defecto 39 (pruebas con mensajes simultáneos), 23-10-2026: 304 en el backend, todas aprobadas; el frontend no cambia.</t>
+          <t>Sprint 1: pruebas unitarias y de componentes con Jest (backend) y Vitest (frontend), todas aprobadas. Al 15-10-2026: 233 pruebas en el backend y 189 en el frontend, todas aprobadas. Al 19-10-2026: 241 en el backend y 231 en el frontend (mejoras de interfaz, SC-19; reserva con calendario, SC-20, y calendario al publicar horarios, SC-21; mapa limitado a Chile, defecto 35; detalle en el mapa, SC-22; buscador general, SC-23; dirección del profesional, SC-24), todas aprobadas. Al 21-10-2026: 241 en el backend y 233 en el frontend (defectos 27 y 29 del mapa), todas aprobadas. Con el asistente IA (FS-HU-07, 21-10-2026): 267 en el backend y 245 en el frontend, todas aprobadas. Con la recomendación de profesional (FS-HU-08) y la SC-26, 22-10-2026: 295 en el backend y 250 en el frontend, todas aprobadas. Con la lista y el mapa juntos (SC-27) y el defecto 37, 22-10-2026: 295 en el backend y 264 en el frontend, todas aprobadas. Con la corrección del defecto 38, 22-10-2026: 296 en el backend y 264 en el frontend, todas aprobadas. Con la corrección del defecto 39 (pruebas con mensajes simultáneos), 23-10-2026: 304 en el backend, todas aprobadas; el frontend no cambia. Con la ubicación de la ficha por dirección (SC-28), 24-10-2026: 316 en el backend y 277 en el frontend, todas aprobadas.</t>
         </is>
       </c>
     </row>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Control del proyecto/control-capstone-2026-FitSearch.xlsx
@@ -1549,7 +1549,7 @@
       <c r="I16" s="43" t="n"/>
       <c r="J16" s="43" t="inlineStr">
         <is>
-          <t>Planilla de Casos de Prueba: 80 casos (CP-001 a CP-080), 77 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 29 defectos: 26 corregidos y 3 abiertos (27 a 29, del mapa nuevo del PR #27). El 15-10-2026 se repitieron CP-076 y CP-077 con MapLibre (189/189 en el frontend); CP-078 sigue pendiente con el mapa nuevo. Comprobaciones con MySQL real: npm run test:mysql:agenda, 55/55 sobre main 662e79c el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema. 19-10-2026: CP-081 a CP-087 (mejoras de interfaz, SC-19), todos aprobados → 87 casos, 84 aprobados y 3 sin ejecutar (CP-024, CP-025 y CP-078); defectos 30 a 34 corregidos → 34 defectos: 31 corregidos y 3 abiertos (27 a 29). Evidencias en Plan de Pruebas/Mejoras_Interfaz_2026-10-19*. 19-10-2026 (SC-20, reserva con calendario): CP-088 a CP-091 aprobados → 91 casos, 88 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Flujo_Reservas_2026-10-19*. SC-21 (calendario al publicar horarios): CP-092 y CP-093 aprobados → 93 casos, 90 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Publicar_Horario_2026-10-19*. Defecto 35 (mapa que se veía de lejos por una ubicación fuera de Chile) corregido con CP-094 → 94 casos, 91 aprobados y 3 sin ejecutar; 35 defectos: 32 corregidos y 3 abiertos. Evidencias en Plan de Pruebas/Mapa_Chile_2026-10-19*. SC-22 (detalle del profesional en el mapa): CP-095 y CP-096 aprobados y defecto 28 corregido → 96 casos, 93 aprobados y 3 sin ejecutar; 35 defectos: 33 corregidos y 2 abiertos (27 y 29). Evidencias en Plan de Pruebas/Detalle_Mapa_2026-10-19*. SC-23 (buscador general del Inicio): CP-097 y CP-098 aprobados → 98 casos, 95 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Buscador_Inicio_2026-10-19*. SC-24 (dirección de atención y coordenadas en Chile en la ficha profesional): CP-099 y CP-100 aprobados → 100 casos, 97 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Direccion_Ficha_2026-10-19*. 21-10-2026: corregidos los defectos 27 y 29 del mapa (CP-101 y CP-102 aprobados) → 102 casos, 99 aprobados y 3 sin ejecutar; 35 defectos, todos corregidos. Evidencias en Plan de Pruebas/Defectos_Mapa_2026-10-21*. 21-10-2026: asistente IA (FS-HU-07, SC-25): CP-103 a CP-108 aprobados y CP-109 (respuesta real de Groq) pendiente de la clave → 109 casos, 105 aprobados y 4 sin ejecutar. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-21*. 22-10-2026: CP-109 aprobado con Groq real (modelo openai/gpt-oss-120b) y defecto 36 corregido → 109 casos, 106 aprobados y 3 sin ejecutar; 36 defectos, todos corregidos. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-22_groq_real*. 22-10-2026: FS-HU-08 (recomendación de profesional) y SC-26 (el SAMU solo en situaciones críticas): CP-110 a CP-114 aprobados → 114 casos, 111 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Recomendacion_Profesional_2026-10-22*. 22-10-2026: SC-27 (lista y mapa juntos en Profesionales, FS-HU-06) y defecto 37 (mapa en una pestaña oculta): CP-115 a CP-120 aprobados → 120 casos, 117 aprobados y 3 sin ejecutar; 37 defectos, todos corregidos. Evidencias en Plan de Pruebas/Lista_y_Mapa_2026-10-22*. 22-10-2026: defecto 38 (la red de seguridad del asistente no reconocía formas directas de riesgo suicida), encontrado en la revisión previa de los PR #28 a #30 y corregido en el PR #29: CP-121 aprobado → 121 casos, 118 aprobados y 3 sin ejecutar; 38 defectos, todos corregidos. 23-10-2026: defecto 39 (el límite diario del asistente se podía superar con mensajes simultáneos), informado por Luis Méndez en la revisión del PR #29 y corregido en ese PR: CP-122 aprobado → 122 casos, 119 aprobados y 3 sin ejecutar; 39 defectos, todos corregidos. Luis Méndez agregó la comprobación con MySQL real npm run test:mysql:asistente (23 condiciones aprobadas; Plan de Pruebas/Asistente_Cupo_MySQL*). PR #29 y #30 fusionados en main el 23-10-2026. 24-10-2026: CP-078 aprobado sobre main con el mapa real (FS-HU-06; evidencia Plan de Pruebas/Mapa_Real_CP078_2026-10-24*) → 122 casos, 120 aprobados y 2 sin ejecutar (CP-024 y CP-025, acceso con Google). 24-10-2026: SC-28 (la ficha profesional se ubica con la comuna y la dirección, sin escribir coordenadas, FS-HU-04): CP-123 a CP-125 aprobados → 125 casos, 123 aprobados y 2 sin ejecutar (CP-024 y CP-025); 39 defectos, todos corregidos. Evidencias en Plan de Pruebas/Ubicacion_Direccion_2026-10-24*.</t>
+          <t>Planilla de Casos de Prueba: 80 casos (CP-001 a CP-080), 77 aprobados y 3 sin ejecutar (CP-024 y CP-025, acceso con Google; CP-078, mapa real en main). Registro de Defectos con 29 defectos: 26 corregidos y 3 abiertos (27 a 29, del mapa nuevo del PR #27). El 15-10-2026 se repitieron CP-076 y CP-077 con MapLibre (189/189 en el frontend); CP-078 sigue pendiente con el mapa nuevo. Comprobaciones con MySQL real: npm run test:mysql:agenda, 55/55 sobre main 662e79c el 12-10-2026. Evidencias en FASE 2/Evidencias Proyecto/Evidencias de documentación/Sprint N/Capturas del sistema. 19-10-2026: CP-081 a CP-087 (mejoras de interfaz, SC-19), todos aprobados → 87 casos, 84 aprobados y 3 sin ejecutar (CP-024, CP-025 y CP-078); defectos 30 a 34 corregidos → 34 defectos: 31 corregidos y 3 abiertos (27 a 29). Evidencias en Plan de Pruebas/Mejoras_Interfaz_2026-10-19*. 19-10-2026 (SC-20, reserva con calendario): CP-088 a CP-091 aprobados → 91 casos, 88 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Flujo_Reservas_2026-10-19*. SC-21 (calendario al publicar horarios): CP-092 y CP-093 aprobados → 93 casos, 90 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Publicar_Horario_2026-10-19*. Defecto 35 (mapa que se veía de lejos por una ubicación fuera de Chile) corregido con CP-094 → 94 casos, 91 aprobados y 3 sin ejecutar; 35 defectos: 32 corregidos y 3 abiertos. Evidencias en Plan de Pruebas/Mapa_Chile_2026-10-19*. SC-22 (detalle del profesional en el mapa): CP-095 y CP-096 aprobados y defecto 28 corregido → 96 casos, 93 aprobados y 3 sin ejecutar; 35 defectos: 33 corregidos y 2 abiertos (27 y 29). Evidencias en Plan de Pruebas/Detalle_Mapa_2026-10-19*. SC-23 (buscador general del Inicio): CP-097 y CP-098 aprobados → 98 casos, 95 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Buscador_Inicio_2026-10-19*. SC-24 (dirección de atención y coordenadas en Chile en la ficha profesional): CP-099 y CP-100 aprobados → 100 casos, 97 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Direccion_Ficha_2026-10-19*. 21-10-2026: corregidos los defectos 27 y 29 del mapa (CP-101 y CP-102 aprobados) → 102 casos, 99 aprobados y 3 sin ejecutar; 35 defectos, todos corregidos. Evidencias en Plan de Pruebas/Defectos_Mapa_2026-10-21*. 21-10-2026: asistente IA (FS-HU-07, SC-25): CP-103 a CP-108 aprobados y CP-109 (respuesta real de Groq) pendiente de la clave → 109 casos, 105 aprobados y 4 sin ejecutar. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-21*. 22-10-2026: CP-109 aprobado con Groq real (modelo openai/gpt-oss-120b) y defecto 36 corregido → 109 casos, 106 aprobados y 3 sin ejecutar; 36 defectos, todos corregidos. Evidencias en Plan de Pruebas/Asistente_IA_2026-10-22_groq_real*. 22-10-2026: FS-HU-08 (recomendación de profesional) y SC-26 (el SAMU solo en situaciones críticas): CP-110 a CP-114 aprobados → 114 casos, 111 aprobados y 3 sin ejecutar. Evidencias en Plan de Pruebas/Recomendacion_Profesional_2026-10-22*. 22-10-2026: SC-27 (lista y mapa juntos en Profesionales, FS-HU-06) y defecto 37 (mapa en una pestaña oculta): CP-115 a CP-120 aprobados → 120 casos, 117 aprobados y 3 sin ejecutar; 37 defectos, todos corregidos. Evidencias en Plan de Pruebas/Lista_y_Mapa_2026-10-22*. 22-10-2026: defecto 38 (la red de seguridad del asistente no reconocía formas directas de riesgo suicida), encontrado en la revisión previa de los PR #28 a #30 y corregido en el PR #29: CP-121 aprobado → 121 casos, 118 aprobados y 3 sin ejecutar; 38 defectos, todos corregidos. 23-10-2026: defecto 39 (el límite diario del asistente se podía superar con mensajes simultáneos), informado por Luis Méndez en la revisión del PR #29 y corregido en ese PR: CP-122 aprobado → 122 casos, 119 aprobados y 3 sin ejecutar; 39 defectos, todos corregidos. Luis Méndez agregó la comprobación con MySQL real npm run test:mysql:asistente (23 condiciones aprobadas; Plan de Pruebas/Asistente_Cupo_MySQL*). PR #29 y #30 fusionados en main el 23-10-2026. 24-10-2026: CP-078 aprobado sobre main con el mapa real (FS-HU-06; evidencia Plan de Pruebas/Mapa_Real_CP078_2026-10-24*) → 122 casos, 120 aprobados y 2 sin ejecutar (CP-024 y CP-025, acceso con Google). 24-10-2026: SC-28 (la ficha profesional se ubica con la comuna y la dirección, sin escribir coordenadas, FS-HU-04): CP-123 a CP-125 aprobados → 125 casos, 123 aprobados y 2 sin ejecutar (CP-024 y CP-025); 39 defectos, todos corregidos. Evidencias en Plan de Pruebas/Ubicacion_Direccion_2026-10-24*. 26-10-2026: SC-29 (rediseño de la portada y del Inicio, PR #33 de Luis Méndez, aceptado por el PO) y defectos 40 y 41 de su revisión: CP-126 a CP-130 aprobados → 130 casos, 128 aprobados y 2 sin ejecutar (CP-024 y CP-025); 41 defectos, todos corregidos (40 y 41 en la rama de ajustes, pendiente de revisión). Evidencias en Plan de Pruebas/Portada_Inicio_Redisenados.md y Portada_Ajustes_2026-10-26.json.</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
       <c r="F22" s="43" t="n"/>
       <c r="G22" s="43" t="inlineStr">
         <is>
-          <t>Sprint 1: pruebas unitarias y de componentes con Jest (backend) y Vitest (frontend), todas aprobadas. Al 15-10-2026: 233 pruebas en el backend y 189 en el frontend, todas aprobadas. Al 19-10-2026: 241 en el backend y 231 en el frontend (mejoras de interfaz, SC-19; reserva con calendario, SC-20, y calendario al publicar horarios, SC-21; mapa limitado a Chile, defecto 35; detalle en el mapa, SC-22; buscador general, SC-23; dirección del profesional, SC-24), todas aprobadas. Al 21-10-2026: 241 en el backend y 233 en el frontend (defectos 27 y 29 del mapa), todas aprobadas. Con el asistente IA (FS-HU-07, 21-10-2026): 267 en el backend y 245 en el frontend, todas aprobadas. Con la recomendación de profesional (FS-HU-08) y la SC-26, 22-10-2026: 295 en el backend y 250 en el frontend, todas aprobadas. Con la lista y el mapa juntos (SC-27) y el defecto 37, 22-10-2026: 295 en el backend y 264 en el frontend, todas aprobadas. Con la corrección del defecto 38, 22-10-2026: 296 en el backend y 264 en el frontend, todas aprobadas. Con la corrección del defecto 39 (pruebas con mensajes simultáneos), 23-10-2026: 304 en el backend, todas aprobadas; el frontend no cambia. Con la ubicación de la ficha por dirección (SC-28), 24-10-2026: 316 en el backend y 277 en el frontend, todas aprobadas.</t>
+          <t>Sprint 1: pruebas unitarias y de componentes con Jest (backend) y Vitest (frontend), todas aprobadas. Al 15-10-2026: 233 pruebas en el backend y 189 en el frontend, todas aprobadas. Al 19-10-2026: 241 en el backend y 231 en el frontend (mejoras de interfaz, SC-19; reserva con calendario, SC-20, y calendario al publicar horarios, SC-21; mapa limitado a Chile, defecto 35; detalle en el mapa, SC-22; buscador general, SC-23; dirección del profesional, SC-24), todas aprobadas. Al 21-10-2026: 241 en el backend y 233 en el frontend (defectos 27 y 29 del mapa), todas aprobadas. Con el asistente IA (FS-HU-07, 21-10-2026): 267 en el backend y 245 en el frontend, todas aprobadas. Con la recomendación de profesional (FS-HU-08) y la SC-26, 22-10-2026: 295 en el backend y 250 en el frontend, todas aprobadas. Con la lista y el mapa juntos (SC-27) y el defecto 37, 22-10-2026: 295 en el backend y 264 en el frontend, todas aprobadas. Con la corrección del defecto 38, 22-10-2026: 296 en el backend y 264 en el frontend, todas aprobadas. Con la corrección del defecto 39 (pruebas con mensajes simultáneos), 23-10-2026: 304 en el backend, todas aprobadas; el frontend no cambia. Con la ubicación de la ficha por dirección (SC-28), 24-10-2026: 316 en el backend y 277 en el frontend, todas aprobadas. Con el rediseño de portada e Inicio (SC-29) y los defectos 40 y 41, 26-10-2026: 286 en el frontend, todas aprobadas; el backend no cambia.</t>
         </is>
       </c>
     </row>
